--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">24/06/2026</t>
+    <t xml:space="preserve">18/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">vcorvalan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1557,7 +1557,7 @@
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11" t="n">
-        <v>0.715931302042003</v>
+        <v>0.721975929584775</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -1615,7 +1615,7 @@
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15" t="n">
-        <v>0.512557629243557</v>
+        <v>0.5212492428998</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -1685,7 +1685,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.155661922178664</v>
+        <v>0.153979925743781</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1715,7 +1715,7 @@
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22" t="n">
-        <v>0.0000551084383052098</v>
+        <v>0.000121431265441804</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -1960,7 +1960,7 @@
         <v>285684.43920487</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>282483.955622755</v>
+        <v>282483.955622815</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>282294.983959635</v>
@@ -1984,7 +1984,7 @@
         <v>1.00046103871543</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.01179605107709</v>
+        <v>1.01179605107687</v>
       </c>
     </row>
     <row r="3">
@@ -2013,7 +2013,7 @@
         <v>285340.804386349</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>284815.242766705</v>
+        <v>284815.242766768</v>
       </c>
       <c r="J3" s="10" t="n">
         <v>284438.088812099</v>
@@ -2041,7 +2041,7 @@
         <v>0.999308938785785</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.00115293568459</v>
+        <v>1.00115293568436</v>
       </c>
     </row>
     <row r="4">
@@ -2070,7 +2070,7 @@
         <v>284470.468347331</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>287148.612532636</v>
+        <v>287148.612532703</v>
       </c>
       <c r="J4" s="10" t="n">
         <v>286598.799498723</v>
@@ -2098,7 +2098,7 @@
         <v>1.00252443782754</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.993174209838931</v>
+        <v>0.993174209838699</v>
       </c>
     </row>
     <row r="5">
@@ -2127,7 +2127,7 @@
         <v>285056.703379466</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>289486.352776063</v>
+        <v>289486.352776134</v>
       </c>
       <c r="J5" s="10" t="n">
         <v>288798.249491725</v>
@@ -2155,7 +2155,7 @@
         <v>0.996881092842427</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.981627062077099</v>
+        <v>0.98162706207686</v>
       </c>
     </row>
     <row r="6">
@@ -2184,7 +2184,7 @@
         <v>290673.079365178</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>291829.526342395</v>
+        <v>291829.526342469</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>291050.521247623</v>
@@ -2214,7 +2214,7 @@
         <v>0.9979510621121</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.993996433176315</v>
+        <v>0.993996433176064</v>
       </c>
     </row>
     <row r="7">
@@ -2243,7 +2243,7 @@
         <v>297333.983694748</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>294175.871880295</v>
+        <v>294175.871880371</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>293346.544165409</v>
@@ -2273,7 +2273,7 @@
         <v>1.00495324005029</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.01574187026694</v>
+        <v>1.01574187026668</v>
       </c>
     </row>
     <row r="8">
@@ -2302,7 +2302,7 @@
         <v>298338.509036201</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>296522.033027138</v>
+        <v>296522.033027217</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>295672.382579237</v>
@@ -2332,7 +2332,7 @@
         <v>0.999310471405389</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.0054321868084</v>
+        <v>1.00543218680813</v>
       </c>
     </row>
     <row r="9">
@@ -2361,7 +2361,7 @@
         <v>296554.107385995</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>298867.547719306</v>
+        <v>298867.547719386</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>298041.401853891</v>
@@ -2391,7 +2391,7 @@
         <v>0.997763136093149</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.990039763315664</v>
+        <v>0.990039763315399</v>
       </c>
     </row>
     <row r="10">
@@ -2420,7 +2420,7 @@
         <v>296207.924142963</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>301212.960620104</v>
+        <v>301212.960620184</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>300479.269421772</v>
@@ -2450,7 +2450,7 @@
         <v>1.00305934664891</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.986392239734317</v>
+        <v>0.986392239734055</v>
       </c>
     </row>
     <row r="11">
@@ -2479,7 +2479,7 @@
         <v>299499.92135201</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>303556.95589814</v>
+        <v>303556.955898219</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>303000.899487049</v>
@@ -2509,7 +2509,7 @@
         <v>0.99462528575941</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.98133213247672</v>
+        <v>0.981332132476465</v>
       </c>
     </row>
     <row r="12">
@@ -2538,7 +2538,7 @@
         <v>304816.47810658</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>305895.655950926</v>
+        <v>305895.655951002</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>305604.380541096</v>
@@ -2568,7 +2568,7 @@
         <v>1.00526111923555</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.0017146304033</v>
+        <v>1.00171463040306</v>
       </c>
     </row>
     <row r="13">
@@ -2597,7 +2597,7 @@
         <v>307991.10820172</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>308221.641450324</v>
+        <v>308221.641450394</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>308262.24755215</v>
@@ -2627,7 +2627,7 @@
         <v>0.99942684316382</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.998679325514468</v>
+        <v>0.998679325514241</v>
       </c>
     </row>
     <row r="14">
@@ -2656,7 +2656,7 @@
         <v>307864.733218995</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>310527.820879439</v>
+        <v>310527.820879501</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>310951.114355457</v>
@@ -2686,7 +2686,7 @@
         <v>0.999547953598189</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>0.990975826908505</v>
+        <v>0.990975826908309</v>
       </c>
     </row>
     <row r="15">
@@ -2715,7 +2715,7 @@
         <v>308739.245868716</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>312806.848308594</v>
+        <v>312806.848308644</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>313645.356453464</v>
@@ -2745,7 +2745,7 @@
         <v>1.00081826239076</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.987804062644216</v>
+        <v>0.98780406264406</v>
       </c>
     </row>
     <row r="16">
@@ -2774,7 +2774,7 @@
         <v>314007.629332199</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>315049.626397606</v>
+        <v>315049.626397639</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>316303.221597213</v>
@@ -2804,7 +2804,7 @@
         <v>0.99577591035529</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>0.992482475005891</v>
+        <v>0.992482475005785</v>
       </c>
     </row>
     <row r="17">
@@ -2833,7 +2833,7 @@
         <v>321887.695157495</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>317244.673448337</v>
+        <v>317244.67344835</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>318859.690133388</v>
@@ -2863,7 +2863,7 @@
         <v>1.0043935652066</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.01909332699331</v>
+        <v>1.01909332699327</v>
       </c>
     </row>
     <row r="18">
@@ -2892,10 +2892,10 @@
         <v>327936.667010804</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>319379.027516751</v>
+        <v>319379.027516738</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>321231.632465472</v>
+        <v>321231.632465473</v>
       </c>
       <c r="K18" s="11" t="n">
         <v>327298.004056778</v>
@@ -2922,7 +2922,7 @@
         <v>0.998052480804151</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.02479491719165</v>
+        <v>1.02479491719169</v>
       </c>
     </row>
     <row r="19">
@@ -2951,7 +2951,7 @@
         <v>329514.964258324</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>321443.51244399</v>
+        <v>321443.512443946</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>323358.130194958</v>
@@ -2981,7 +2981,7 @@
         <v>1.00260703748024</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.02778251646317</v>
+        <v>1.02778251646332</v>
       </c>
     </row>
     <row r="20">
@@ -3010,7 +3010,7 @@
         <v>330901.555524192</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>323433.901431535</v>
+        <v>323433.901431451</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>325208.596781295</v>
@@ -3040,7 +3040,7 @@
         <v>0.995793882687134</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.018785425103</v>
+        <v>1.01878542510326</v>
       </c>
     </row>
     <row r="21">
@@ -3069,7 +3069,7 @@
         <v>332302.217379835</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>325351.549249411</v>
+        <v>325351.549249283</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>326787.525143558</v>
@@ -3099,7 +3099,7 @@
         <v>1.00357975971416</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.025019798553</v>
+        <v>1.02501979855341</v>
       </c>
     </row>
     <row r="22">
@@ -3128,7 +3128,7 @@
         <v>333294.719506483</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>327201.60806973</v>
+        <v>327201.608069548</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>328120.913940731</v>
@@ -3158,7 +3158,7 @@
         <v>0.997183429393455</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.01575286673217</v>
+        <v>1.01575286673274</v>
       </c>
     </row>
     <row r="23">
@@ -3187,7 +3187,7 @@
         <v>331290.922220052</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>328994.317708488</v>
+        <v>328994.317708245</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>329268.283103432</v>
@@ -3217,7 +3217,7 @@
         <v>1.00348709509507</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.01049211878649</v>
+        <v>1.01049211878724</v>
       </c>
     </row>
     <row r="24">
@@ -3246,7 +3246,7 @@
         <v>327970.113392138</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>330743.139458764</v>
+        <v>330743.13945845</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>330310.327849557</v>
@@ -3276,7 +3276,7 @@
         <v>1</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.991615771467963</v>
+        <v>0.991615771468903</v>
       </c>
     </row>
     <row r="25">
@@ -3305,7 +3305,7 @@
         <v>326990.187117292</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>332463.692018295</v>
+        <v>332463.692017903</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>331343.632807333</v>
@@ -3335,7 +3335,7 @@
         <v>0.997481089023311</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.981059092394799</v>
+        <v>0.981059092395956</v>
       </c>
     </row>
     <row r="26">
@@ -3364,7 +3364,7 @@
         <v>327370.941931502</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>334169.860943532</v>
+        <v>334169.860943053</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>332453.081532702</v>
@@ -3394,7 +3394,7 @@
         <v>1.00536347685521</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.984908655353679</v>
+        <v>0.984908655355093</v>
       </c>
     </row>
     <row r="27">
@@ -3423,7 +3423,7 @@
         <v>326147.212558088</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>335871.596063378</v>
+        <v>335871.596062802</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>333697.672057297</v>
@@ -3453,7 +3453,7 @@
         <v>0.996551430987198</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.967698594334003</v>
+        <v>0.967698594335662</v>
       </c>
     </row>
     <row r="28">
@@ -3482,7 +3482,7 @@
         <v>326044.54700968</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>337575.695286396</v>
+        <v>337575.695285717</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>335119.770947094</v>
@@ -3512,7 +3512,7 @@
         <v>1.00174562212335</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.967527289863213</v>
+        <v>0.967527289865162</v>
       </c>
     </row>
     <row r="29">
@@ -3541,7 +3541,7 @@
         <v>332763.639378441</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>339282.17581823</v>
+        <v>339282.175817439</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>336718.368764721</v>
@@ -3571,7 +3571,7 @@
         <v>0.995551500331859</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.976424239322791</v>
+        <v>0.976424239325068</v>
       </c>
     </row>
     <row r="30">
@@ -3600,7 +3600,7 @@
         <v>343187.168381237</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>340984.203615957</v>
+        <v>340984.203615048</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>338449.92570599</v>
@@ -3630,7 +3630,7 @@
         <v>1.00354258138292</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.01002607511607</v>
+        <v>1.01002607511876</v>
       </c>
     </row>
     <row r="31">
@@ -3659,7 +3659,7 @@
         <v>352724.681542238</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>342669.945364542</v>
+        <v>342669.945363512</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>340243.726825086</v>
@@ -3689,7 +3689,7 @@
         <v>0.996913237538612</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.02616499927348</v>
+        <v>1.02616499927656</v>
       </c>
     </row>
     <row r="32">
@@ -3718,7 +3718,7 @@
         <v>353387.797369463</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>344329.704457227</v>
+        <v>344329.704456074</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>342058.822231937</v>
@@ -3748,7 +3748,7 @@
         <v>1.00599607166605</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.03246025924132</v>
+        <v>1.03246025924478</v>
       </c>
     </row>
     <row r="33">
@@ -3777,7 +3777,7 @@
         <v>343392.460694242</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>345959.388011546</v>
+        <v>345959.388010272</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>343911.222923526</v>
@@ -3807,7 +3807,7 @@
         <v>0.999987305577951</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.992567663791675</v>
+        <v>0.99256766379533</v>
       </c>
     </row>
     <row r="34">
@@ -3836,7 +3836,7 @@
         <v>333104.883162749</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>347561.888789703</v>
+        <v>347561.888788313</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>345884.179465318</v>
@@ -3866,7 +3866,7 @@
         <v>0.993702135237003</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.952368612132201</v>
+        <v>0.95236861213601</v>
       </c>
     </row>
     <row r="35">
@@ -3895,7 +3895,7 @@
         <v>332714.377374735</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>349138.49249985</v>
+        <v>349138.492498354</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>348058.326815788</v>
@@ -3925,7 +3925,7 @@
         <v>1.00316322292748</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.955972584780785</v>
+        <v>0.955972584784883</v>
       </c>
     </row>
     <row r="36">
@@ -3954,10 +3954,10 @@
         <v>338498.644473076</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>350680.13806568</v>
+        <v>350680.138064091</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>350439.914204368</v>
+        <v>350439.914204369</v>
       </c>
       <c r="K36" s="11" t="n">
         <v>338566.156924386</v>
@@ -3984,7 +3984,7 @@
         <v>1.00019944674052</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.965455753473483</v>
+        <v>0.965455753477855</v>
       </c>
     </row>
     <row r="37">
@@ -4013,10 +4013,10 @@
         <v>347979.550422056</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>352168.157120022</v>
+        <v>352168.157118363</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>352963.733362019</v>
+        <v>352963.73336202</v>
       </c>
       <c r="K37" s="11" t="n">
         <v>346637.061288137</v>
@@ -4043,7 +4043,7 @@
         <v>0.996142045898126</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.9842941625469</v>
+        <v>0.984294162551536</v>
       </c>
     </row>
     <row r="38">
@@ -4072,10 +4072,10 @@
         <v>358541.643456487</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>353576.310057495</v>
+        <v>353576.310055795</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>355505.207233301</v>
+        <v>355505.207233302</v>
       </c>
       <c r="K38" s="11" t="n">
         <v>360131.033724994</v>
@@ -4102,7 +4102,7 @@
         <v>1.00443293072789</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>1.01853835644824</v>
+        <v>1.01853835645314</v>
       </c>
     </row>
     <row r="39">
@@ -4131,7 +4131,7 @@
         <v>362366.703625266</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>354874.900337821</v>
+        <v>354874.900336117</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>357908.125402406</v>
@@ -4161,7 +4161,7 @@
         <v>1.00151625597356</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>1.0226593764698</v>
+        <v>1.02265937647471</v>
       </c>
     </row>
     <row r="40">
@@ -4190,7 +4190,7 @@
         <v>362245.570448144</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>356038.328123016</v>
+        <v>356038.328121355</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>360039.406585983</v>
@@ -4220,7 +4220,7 @@
         <v>0.998134267168734</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>1.01553593653954</v>
+        <v>1.01553593654428</v>
       </c>
     </row>
     <row r="41">
@@ -4249,7 +4249,7 @@
         <v>364723.397409161</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>357046.019352575</v>
+        <v>357046.019351012</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>361791.00959519</v>
@@ -4279,7 +4279,7 @@
         <v>1.00322284927594</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.02479463742488</v>
+        <v>1.02479463742937</v>
       </c>
     </row>
     <row r="42">
@@ -4308,7 +4308,7 @@
         <v>368497.713638057</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>357880.857084034</v>
+        <v>357880.85708264</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>363062.54479323</v>
@@ -4338,7 +4338,7 @@
         <v>0.999748465691122</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.0294069004474</v>
+        <v>1.02940690045141</v>
       </c>
     </row>
     <row r="43">
@@ -4367,7 +4367,7 @@
         <v>375399.56719607</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>358531.257391555</v>
+        <v>358531.25739041</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>363774.161725059</v>
@@ -4397,7 +4397,7 @@
         <v>0.994527370073768</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.04131825773451</v>
+        <v>1.04131825773784</v>
       </c>
     </row>
     <row r="44">
@@ -4426,7 +4426,7 @@
         <v>382089.935726599</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>358992.213953508</v>
+        <v>358992.213952705</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>363872.72233077</v>
@@ -4456,7 +4456,7 @@
         <v>1.00703261237351</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.07182554713072</v>
+        <v>1.07182554713311</v>
       </c>
     </row>
     <row r="45">
@@ -4485,7 +4485,7 @@
         <v>378915.098444103</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>359267.979127573</v>
+        <v>359267.979127223</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>363352.943463281</v>
@@ -4515,7 +4515,7 @@
         <v>0.999641361114807</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.05430827894938</v>
+        <v>1.05430827895041</v>
       </c>
     </row>
     <row r="46">
@@ -4544,7 +4544,7 @@
         <v>370046.929067076</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>359378.920779048</v>
+        <v>359378.920779273</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>362314.06349454</v>
@@ -4574,7 +4574,7 @@
         <v>0.994538256865323</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.02406069614474</v>
+        <v>1.0240606961441</v>
       </c>
     </row>
     <row r="47">
@@ -4603,7 +4603,7 @@
         <v>360467.602791213</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>359357.601289245</v>
+        <v>359357.601290183</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>360932.452102955</v>
@@ -4633,7 +4633,7 @@
         <v>1.00796936386056</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.01108282939964</v>
+        <v>1.011082829397</v>
       </c>
     </row>
     <row r="48">
@@ -4662,7 +4662,7 @@
         <v>350284.101753595</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>359241.987356362</v>
+        <v>359241.987358166</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>359413.037788426</v>
@@ -4692,7 +4692,7 @@
         <v>0.993537962472264</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.96876357717469</v>
+        <v>0.968763577169825</v>
       </c>
     </row>
     <row r="49">
@@ -4721,7 +4721,7 @@
         <v>344341.392450618</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>359072.534865464</v>
+        <v>359072.5348683</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>357972.788291728</v>
@@ -4751,7 +4751,7 @@
         <v>1.00042552866671</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.959382537328603</v>
+        <v>0.959382537321024</v>
       </c>
     </row>
     <row r="50">
@@ -4780,7 +4780,7 @@
         <v>343038.137188109</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>358882.686304982</v>
+        <v>358882.686309031</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>356771.708928405</v>
@@ -4810,7 +4810,7 @@
         <v>1.00496537941978</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.960596498103945</v>
+        <v>0.960596498093108</v>
       </c>
     </row>
     <row r="51">
@@ -4839,7 +4839,7 @@
         <v>342533.362705206</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>358696.768778797</v>
+        <v>358696.768784249</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>355902.380670466</v>
@@ -4869,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.954938523342098</v>
+        <v>0.954938523327582</v>
       </c>
     </row>
     <row r="52">
@@ -4898,7 +4898,7 @@
         <v>345738.843049346</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>358530.271119158</v>
+        <v>358530.271126213</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>355397.233203749</v>
@@ -4928,7 +4928,7 @@
         <v>1.00137704659263</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.965650516661791</v>
+        <v>0.965650516642789</v>
       </c>
     </row>
     <row r="53">
@@ -4957,7 +4957,7 @@
         <v>352241.305163862</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>358388.580029518</v>
+        <v>358388.580038381</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>355221.851124268</v>
@@ -4987,7 +4987,7 @@
         <v>0.999366239739379</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.982224569191089</v>
+        <v>0.982224569166799</v>
       </c>
     </row>
     <row r="54">
@@ -5016,10 +5016,10 @@
         <v>356720.359659079</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>358269.385132348</v>
+        <v>358269.385143224</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>355295.907569743</v>
+        <v>355295.907569742</v>
       </c>
       <c r="K54" s="11" t="n">
         <v>357551.74757208</v>
@@ -5046,7 +5046,7 @@
         <v>1.00233064329099</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.997996933061967</v>
+        <v>0.99799693303167</v>
       </c>
     </row>
     <row r="55">
@@ -5075,7 +5075,7 @@
         <v>360288.803230216</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>358166.394480486</v>
+        <v>358166.394493577</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>355523.056765383</v>
@@ -5105,7 +5105,7 @@
         <v>0.995764246641171</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.00166490840707</v>
+        <v>1.00166490837046</v>
       </c>
     </row>
     <row r="56">
@@ -5134,7 +5134,7 @@
         <v>360482.886469362</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>358072.867603298</v>
+        <v>358072.867618793</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>355818.232136413</v>
@@ -5164,7 +5164,7 @@
         <v>1.00676178425865</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.01353782096295</v>
+        <v>1.01353782091909</v>
       </c>
     </row>
     <row r="57">
@@ -5193,7 +5193,7 @@
         <v>358110.320672532</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>357982.43672655</v>
+        <v>357982.436744618</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>356112.565367837</v>
@@ -5223,7 +5223,7 @@
         <v>0.99553202150249</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.995887660635028</v>
+        <v>0.995887660584763</v>
       </c>
     </row>
     <row r="58">
@@ -5252,10 +5252,10 @@
         <v>360331.469236293</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>357891.76377999</v>
+        <v>357891.763800773</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>356372.698953861</v>
+        <v>356372.69895386</v>
       </c>
       <c r="K58" s="11" t="n">
         <v>359214.420108457</v>
@@ -5282,7 +5282,7 @@
         <v>0.996899940129559</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.00369568808876</v>
+        <v>1.00369568803047</v>
       </c>
     </row>
     <row r="59">
@@ -5311,7 +5311,7 @@
         <v>366903.325694328</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>357796.590602576</v>
+        <v>357796.590626173</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>356567.26401915</v>
@@ -5341,7 +5341,7 @@
         <v>1.00550717037844</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.03109960941781</v>
+        <v>1.03109960934981</v>
       </c>
     </row>
     <row r="60">
@@ -5370,7 +5370,7 @@
         <v>370115.454503361</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>357693.485693472</v>
+        <v>357693.485719929</v>
       </c>
       <c r="J60" s="10" t="n">
         <v>356679.100294145</v>
@@ -5400,7 +5400,7 @@
         <v>0.995140302172879</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.02969950520418</v>
+        <v>1.02969950512802</v>
       </c>
     </row>
     <row r="61">
@@ -5429,7 +5429,7 @@
         <v>365416.806395414</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>357585.972135725</v>
+        <v>357585.97216502</v>
       </c>
       <c r="J61" s="10" t="n">
         <v>356752.830813296</v>
@@ -5459,7 +5459,7 @@
         <v>1.00654752764113</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.02859007818186</v>
+        <v>1.02859007809759</v>
       </c>
     </row>
     <row r="62">
@@ -5488,10 +5488,10 @@
         <v>353257.410748033</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>357484.212587099</v>
+        <v>357484.212619125</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>356891.26713575</v>
+        <v>356891.267135749</v>
       </c>
       <c r="K62" s="11" t="n">
         <v>352443.344553785</v>
@@ -5518,7 +5518,7 @@
         <v>0.997695543902323</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.985899047130408</v>
+        <v>0.985899047042084</v>
       </c>
     </row>
     <row r="63">
@@ -5547,7 +5547,7 @@
         <v>337044.713219182</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>357404.759337167</v>
+        <v>357404.759371714</v>
       </c>
       <c r="J63" s="10" t="n">
         <v>357252.503581765</v>
@@ -5577,7 +5577,7 @@
         <v>1.00334221977173</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.946185471482875</v>
+        <v>0.946185471391417</v>
       </c>
     </row>
     <row r="64">
@@ -5606,7 +5606,7 @@
         <v>332593.296431408</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>357361.014132984</v>
+        <v>357361.014169718</v>
       </c>
       <c r="J64" s="10" t="n">
         <v>357972.394858691</v>
@@ -5636,7 +5636,7 @@
         <v>0.989135603270764</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.920581311052218</v>
+        <v>0.92058131095759</v>
       </c>
     </row>
     <row r="65">
@@ -5665,10 +5665,10 @@
         <v>342073.449961899</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>357354.35774122</v>
+        <v>357354.357779662</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>359091.389109587</v>
+        <v>359091.389109586</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>344417.57157759</v>
@@ -5695,7 +5695,7 @@
         <v>1.00685268504747</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.963798437367882</v>
+        <v>0.963798437264201</v>
       </c>
     </row>
     <row r="66">
@@ -5724,7 +5724,7 @@
         <v>354399.556297719</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>357368.432714029</v>
+        <v>357368.432753533</v>
       </c>
       <c r="J66" s="10" t="n">
         <v>360504.971857764</v>
@@ -5754,7 +5754,7 @@
         <v>1.00118935997014</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.992871872450326</v>
+        <v>0.992871872340573</v>
       </c>
     </row>
     <row r="67">
@@ -5783,7 +5783,7 @@
         <v>364796.360074642</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>357378.796112216</v>
+        <v>357378.796151944</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>362035.259538877</v>
@@ -5813,7 +5813,7 @@
         <v>0.993573036357098</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.01419510915127</v>
+        <v>1.01419510903853</v>
       </c>
     </row>
     <row r="68">
@@ -5842,7 +5842,7 @@
         <v>372019.460486237</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>357359.412891727</v>
+        <v>357359.412930623</v>
       </c>
       <c r="J68" s="10" t="n">
         <v>363475.949054006</v>
@@ -5872,7 +5872,7 @@
         <v>1.00885012868129</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.05023644836017</v>
+        <v>1.05023644824586</v>
       </c>
     </row>
     <row r="69">
@@ -5901,10 +5901,10 @@
         <v>369996.847424842</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>357287.418652895</v>
+        <v>357287.418689665</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>364622.820142194</v>
+        <v>364622.820142195</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>369472.941943006</v>
@@ -5931,7 +5931,7 @@
         <v>0.998584027173522</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.03410566018824</v>
+        <v>1.03410566008182</v>
       </c>
     </row>
     <row r="70">
@@ -5960,10 +5960,10 @@
         <v>368433.755783655</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>357151.169288362</v>
+        <v>357151.169321443</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>365330.832200133</v>
+        <v>365330.832200134</v>
       </c>
       <c r="K70" s="11" t="n">
         <v>365846.353939529</v>
@@ -5990,7 +5990,7 @@
         <v>0.992977294280155</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.02434595039544</v>
+        <v>1.02434595030056</v>
       </c>
     </row>
     <row r="71">
@@ -6019,10 +6019,10 @@
         <v>377461.405183315</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>356946.636642824</v>
+        <v>356946.636670367</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>365479.195233517</v>
+        <v>365479.195233519</v>
       </c>
       <c r="K71" s="11" t="n">
         <v>378208.365597628</v>
@@ -6049,7 +6049,7 @@
         <v>1.00197890540346</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.05956556743264</v>
+        <v>1.05956556735089</v>
       </c>
     </row>
     <row r="72">
@@ -6078,10 +6078,10 @@
         <v>381959.884844545</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>356675.227051387</v>
+        <v>356675.227071231</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>364949.696856739</v>
+        <v>364949.696856742</v>
       </c>
       <c r="K72" s="11" t="n">
         <v>385097.277017122</v>
@@ -6108,7 +6108,7 @@
         <v>1.00821393108822</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.07968607800631</v>
+        <v>1.07968607794624</v>
       </c>
     </row>
     <row r="73">
@@ -6137,10 +6137,10 @@
         <v>379478.493938744</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>356351.63542975</v>
+        <v>356351.635439409</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>363687.77053601</v>
+        <v>363687.770536014</v>
       </c>
       <c r="K73" s="11" t="n">
         <v>370679.133906637</v>
@@ -6167,7 +6167,7 @@
         <v>0.987289442631454</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.05136352277318</v>
+        <v>1.05136352274468</v>
       </c>
     </row>
     <row r="74">
@@ -6196,10 +6196,10 @@
         <v>377691.66064559</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>356008.320474843</v>
+        <v>356008.320471493</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>361739.587638346</v>
+        <v>361739.58763835</v>
       </c>
       <c r="K74" s="11" t="n">
         <v>380028.85074581</v>
@@ -6226,7 +6226,7 @@
         <v>1.00618809029626</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.06747182267799</v>
+        <v>1.06747182268803</v>
       </c>
     </row>
     <row r="75">
@@ -6255,10 +6255,10 @@
         <v>372086.14075127</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>355689.180555685</v>
+        <v>355689.180536156</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>359206.156231937</v>
+        <v>359206.156231942</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>373012.106097125</v>
@@ -6285,7 +6285,7 @@
         <v>1.00248857789754</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.0487024247248</v>
+        <v>1.04870242478238</v>
       </c>
     </row>
     <row r="76">
@@ -6314,10 +6314,10 @@
         <v>361519.532084026</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>355453.126872713</v>
+        <v>355453.126833492</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>356279.930700512</v>
+        <v>356279.930700518</v>
       </c>
       <c r="K76" s="11" t="n">
         <v>359505.457165796</v>
@@ -6344,7 +6344,7 @@
         <v>0.994428862787525</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.01140046320238</v>
+        <v>1.01140046331398</v>
       </c>
     </row>
     <row r="77">
@@ -6373,10 +6373,10 @@
         <v>358299.904962271</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>355369.897454828</v>
+        <v>355369.897392071</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>353222.395177127</v>
+        <v>353222.395177134</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>357451.083452559</v>
@@ -6403,7 +6403,7 @@
         <v>0.997630974784095</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>1.00585639361307</v>
+        <v>1.0058563937907</v>
       </c>
     </row>
     <row r="78">
@@ -6432,10 +6432,10 @@
         <v>354000.663396406</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>355511.763037363</v>
+        <v>355511.762946921</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>350311.161427161</v>
+        <v>350311.161427169</v>
       </c>
       <c r="K78" s="11" t="n">
         <v>365527.148096089</v>
@@ -6462,7 +6462,7 @@
         <v>1.00891203463004</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.00462366284661</v>
+        <v>1.00462366310219</v>
       </c>
     </row>
     <row r="79">
@@ -6491,10 +6491,10 @@
         <v>339078.88804116</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>355952.295096902</v>
+        <v>355952.294974358</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>347844.984657374</v>
+        <v>347844.984657382</v>
       </c>
       <c r="K79" s="11" t="n">
         <v>338188.610243677</v>
@@ -6521,7 +6521,7 @@
         <v>0.99737442279988</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>0.950095321485738</v>
+        <v>0.950095321812827</v>
       </c>
     </row>
     <row r="80">
@@ -6550,10 +6550,10 @@
         <v>327611.800456159</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>356766.092464108</v>
+        <v>356766.092304836</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>346156.841915226</v>
+        <v>346156.841915234</v>
       </c>
       <c r="K80" s="11" t="n">
         <v>324654.814132488</v>
@@ -6580,7 +6580,7 @@
         <v>0.990974115341529</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.909993469082685</v>
+        <v>0.909993469488936</v>
       </c>
     </row>
     <row r="81">
@@ -6609,10 +6609,10 @@
         <v>326146.061960052</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>358016.651666612</v>
+        <v>358016.651465851</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>345531.428376109</v>
+        <v>345531.428376116</v>
       </c>
       <c r="K81" s="11" t="n">
         <v>338630.833598453</v>
@@ -6639,7 +6639,7 @@
         <v>1.00770166791766</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.917996213561508</v>
+        <v>0.917996214076283</v>
       </c>
     </row>
     <row r="82">
@@ -6668,10 +6668,10 @@
         <v>325272.179419449</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>359747.399683088</v>
+        <v>359747.399436043</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>346145.929076502</v>
+        <v>346145.929076507</v>
       </c>
       <c r="K82" s="11" t="n">
         <v>324622.055794528</v>
@@ -6698,7 +6698,7 @@
         <v>0.998001293482641</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.902361090255264</v>
+        <v>0.902361090874933</v>
       </c>
     </row>
     <row r="83">
@@ -6727,10 +6727,10 @@
         <v>328709.244678886</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>361983.414291558</v>
+        <v>361983.413993523</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>348093.161564113</v>
+        <v>348093.161564115</v>
       </c>
       <c r="K83" s="11" t="n">
         <v>326509.110206825</v>
@@ -6757,7 +6757,7 @@
         <v>0.993306745983946</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.902000194804063</v>
+        <v>0.902000195546714</v>
       </c>
     </row>
     <row r="84">
@@ -6786,10 +6786,10 @@
         <v>340224.194523046</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>364727.819930109</v>
+        <v>364727.819576629</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>351358.324020238</v>
+        <v>351358.324020235</v>
       </c>
       <c r="K84" s="11" t="n">
         <v>342224.446725735</v>
@@ -6816,7 +6816,7 @@
         <v>1.00587921798299</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.938300913791861</v>
+        <v>0.938300914701226</v>
       </c>
     </row>
     <row r="85">
@@ -6845,10 +6845,10 @@
         <v>348079.280310373</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>367961.56959678</v>
+        <v>367961.569183827</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>355818.69436939</v>
+        <v>355818.69436938</v>
       </c>
       <c r="K85" s="11" t="n">
         <v>349010.307845754</v>
@@ -6875,7 +6875,7 @@
         <v>1.00267475712588</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.948496627591319</v>
+        <v>0.948496628655792</v>
       </c>
     </row>
     <row r="86">
@@ -6904,10 +6904,10 @@
         <v>353836.163763914</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>371651.551681356</v>
+        <v>371651.551205556</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>361305.881149607</v>
+        <v>361305.881149588</v>
       </c>
       <c r="K86" s="11" t="n">
         <v>351350.466059895</v>
@@ -6934,7 +6934,7 @@
         <v>0.992975003805214</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.945376023510142</v>
+        <v>0.945376024720443</v>
       </c>
     </row>
     <row r="87">
@@ -6963,10 +6963,10 @@
         <v>364755.318896553</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>375752.810035026</v>
+        <v>375752.809493917</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>367617.450966309</v>
+        <v>367617.450966278</v>
       </c>
       <c r="K87" s="11" t="n">
         <v>366408.402200179</v>
@@ -6993,7 +6993,7 @@
         <v>1.00453203344266</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.975131502452432</v>
+        <v>0.975131503856687</v>
       </c>
     </row>
     <row r="88">
@@ -7022,10 +7022,10 @@
         <v>378303.712625868</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>380207.700330468</v>
+        <v>380207.699722795</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>374501.193349469</v>
+        <v>374501.193349424</v>
       </c>
       <c r="K88" s="11" t="n">
         <v>377494.761701028</v>
@@ -7052,7 +7052,7 @@
         <v>0.997861636304797</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.99286458788951</v>
+        <v>0.992864589476372</v>
       </c>
     </row>
     <row r="89">
@@ -7081,10 +7081,10 @@
         <v>389765.083737746</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>384952.737985461</v>
+        <v>384952.737311516</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>381698.852585228</v>
+        <v>381698.852585165</v>
       </c>
       <c r="K89" s="11" t="n">
         <v>390433.610227195</v>
@@ -7111,7 +7111,7 @@
         <v>1.00171520363763</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>1.01423777960489</v>
+        <v>1.01423778138053</v>
       </c>
     </row>
     <row r="90">
@@ -7140,10 +7140,10 @@
         <v>401055.607921127</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>389922.742831142</v>
+        <v>389922.742093144</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>388967.140801485</v>
+        <v>388967.140801403</v>
       </c>
       <c r="K90" s="11" t="n">
         <v>400031.872276562</v>
@@ -7170,7 +7170,7 @@
         <v>0.997447397257774</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>1.02592598054687</v>
+        <v>1.02592598248861</v>
       </c>
     </row>
     <row r="91">
@@ -7199,10 +7199,10 @@
         <v>409029.445827794</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>395055.960243798</v>
+        <v>395055.959446313</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>396106.443914349</v>
+        <v>396106.443914245</v>
       </c>
       <c r="K91" s="11" t="n">
         <v>410201.166441417</v>
@@ -7229,7 +7229,7 @@
         <v>1.00286463633749</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>1.03833686293018</v>
+        <v>1.03833686502624</v>
       </c>
     </row>
     <row r="92">
@@ -7258,10 +7258,10 @@
         <v>410309.333992197</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>400296.953805621</v>
+        <v>400296.952956023</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>402972.471497305</v>
+        <v>402972.471497177</v>
       </c>
       <c r="K92" s="11" t="n">
         <v>410910.806821399</v>
@@ -7288,7 +7288,7 @@
         <v>1.00146590091761</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>1.02651494825247</v>
+        <v>1.02651495043117</v>
       </c>
     </row>
     <row r="93">
@@ -7317,10 +7317,10 @@
         <v>409913.621396463</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>405599.752852675</v>
+        <v>405599.751961646</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>409491.406736472</v>
+        <v>409491.406736322</v>
       </c>
       <c r="K93" s="11" t="n">
         <v>408087.826349299</v>
@@ -7347,7 +7347,7 @@
         <v>0.99554590296135</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>1.00613430723053</v>
+        <v>1.00613430944082</v>
       </c>
     </row>
     <row r="94">
@@ -7376,10 +7376,10 @@
         <v>415049.750870997</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>410925.020379159</v>
+        <v>410925.019461219</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>415629.12449459</v>
+        <v>415629.124494419</v>
       </c>
       <c r="K94" s="11" t="n">
         <v>415850.74506037</v>
@@ -7406,7 +7406,7 @@
         <v>1.00192987512387</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.01198691838396</v>
+        <v>1.01198692064457</v>
       </c>
     </row>
     <row r="95">
@@ -7435,10 +7435,10 @@
         <v>423625.21344142</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>416234.974425209</v>
+        <v>416234.973499273</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>421344.481732464</v>
+        <v>421344.481732278</v>
       </c>
       <c r="K95" s="11" t="n">
         <v>423452.493299921</v>
@@ -7465,7 +7465,7 @@
         <v>0.999592280780231</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.01734001061463</v>
+        <v>1.01734001287775</v>
       </c>
     </row>
     <row r="96">
@@ -7494,10 +7494,10 @@
         <v>430592.388294132</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>421494.911608885</v>
+        <v>421494.910698836</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>426597.443513727</v>
+        <v>426597.443513535</v>
       </c>
       <c r="K96" s="11" t="n">
         <v>431054.779420915</v>
@@ -7524,7 +7524,7 @@
         <v>1.00107384881701</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.02268086173458</v>
+        <v>1.02268086394265</v>
       </c>
     </row>
     <row r="97">
@@ -7553,10 +7553,10 @@
         <v>436858.365102814</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>426674.639497544</v>
+        <v>426674.638632814</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>431358.514959849</v>
+        <v>431358.514959665</v>
       </c>
       <c r="K97" s="11" t="n">
         <v>436467.027944467</v>
@@ -7583,7 +7583,7 @@
         <v>0.999104201293582</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.02295048156238</v>
+        <v>1.02295048363556</v>
       </c>
     </row>
     <row r="98">
@@ -7612,10 +7612,10 @@
         <v>444117.892457186</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>431749.940575927</v>
+        <v>431749.939792063</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>435620.487871838</v>
+        <v>435620.487871679</v>
       </c>
       <c r="K98" s="11" t="n">
         <v>443795.99016597</v>
@@ -7642,7 +7642,7 @@
         <v>0.999275187294447</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.02790052402549</v>
+        <v>1.0279005258917</v>
       </c>
     </row>
     <row r="99">
@@ -7671,10 +7671,10 @@
         <v>450989.582453002</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>436702.717571551</v>
+        <v>436702.716910757</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>439401.696615621</v>
+        <v>439401.696615515</v>
       </c>
       <c r="K99" s="11" t="n">
         <v>451818.777986187</v>
@@ -7701,7 +7701,7 @@
         <v>1.00183861349674</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.03461407453266</v>
+        <v>1.03461407609818</v>
       </c>
     </row>
     <row r="100">
@@ -7730,10 +7730,10 @@
         <v>456279.911013051</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>441522.40199293</v>
+        <v>441522.401504557</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>442761.3530686</v>
+        <v>442761.353068579</v>
       </c>
       <c r="K100" s="11" t="n">
         <v>451476.953294478</v>
@@ -7760,7 +7760,7 @@
         <v>0.997401110119194</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.03073838997821</v>
+        <v>1.03073839111832</v>
       </c>
     </row>
     <row r="101">
@@ -7789,10 +7789,10 @@
         <v>457513.638957149</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>446207.872886336</v>
+        <v>446207.872627295</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>445820.754515028</v>
+        <v>445820.754515133</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>458811.120946735</v>
@@ -7819,7 +7819,7 @@
         <v>1.00283594166186</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.02824523910543</v>
+        <v>1.02824523970236</v>
       </c>
     </row>
     <row r="102">
@@ -7848,10 +7848,10 @@
         <v>449809.913939866</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>450766.491602901</v>
+        <v>450766.491637967</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>448762.861922662</v>
+        <v>448762.861922942</v>
       </c>
       <c r="K102" s="11" t="n">
         <v>451435.755328579</v>
@@ -7878,7 +7878,7 @@
         <v>1.00277742148344</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.00064941396678</v>
+        <v>1.00064941388894</v>
       </c>
     </row>
     <row r="103">
@@ -7907,10 +7907,10 @@
         <v>437134.935307832</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>455213.496523796</v>
+        <v>455213.49692577</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>451835.588091418</v>
+        <v>451835.588091929</v>
       </c>
       <c r="K103" s="11" t="n">
         <v>435460.48737933</v>
@@ -7937,7 +7937,7 @@
         <v>0.996492461639749</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>0.95691729502766</v>
+        <v>0.956917294182658</v>
       </c>
     </row>
     <row r="104">
@@ -7966,10 +7966,10 @@
         <v>431217.531936571</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>459564.308988976</v>
+        <v>459564.309838665</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>455298.32763989</v>
+        <v>455298.327640694</v>
       </c>
       <c r="K104" s="11" t="n">
         <v>431360.130054406</v>
@@ -7996,7 +7996,7 @@
         <v>1.00033068719909</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>0.93862843919142</v>
+        <v>0.938628437455988</v>
       </c>
     </row>
     <row r="105">
@@ -8025,10 +8025,10 @@
         <v>436762.485230905</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>463822.092945413</v>
+        <v>463822.094331378</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>459329.305584985</v>
+        <v>459329.305586147</v>
       </c>
       <c r="K105" s="11" t="n">
         <v>435799.091109637</v>
@@ -8055,7 +8055,7 @@
         <v>0.997794237935158</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>0.939582434166035</v>
+        <v>0.939582431358432</v>
       </c>
     </row>
     <row r="106">
@@ -8084,10 +8084,10 @@
         <v>447666.430741407</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>467972.384728248</v>
+        <v>467972.386746271</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>463987.055955679</v>
+        <v>463987.055957265</v>
       </c>
       <c r="K106" s="11" t="n">
         <v>448988.703096293</v>
@@ -8114,7 +8114,7 @@
         <v>1.00295370004111</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.959434184042764</v>
+        <v>0.959434179905424</v>
       </c>
     </row>
     <row r="107">
@@ -8143,10 +8143,10 @@
         <v>458155.610156058</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>471983.206296471</v>
+        <v>471983.209048693</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>469212.461708575</v>
+        <v>469212.461710643</v>
       </c>
       <c r="K107" s="11" t="n">
         <v>457790.588486101</v>
@@ -8173,7 +8173,7 @@
         <v>0.999203280147913</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.969929824576313</v>
+        <v>0.969929818920471</v>
       </c>
     </row>
     <row r="108">
@@ -8202,10 +8202,10 @@
         <v>467135.994843473</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>475810.714808054</v>
+        <v>475810.718401709</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>474871.414035975</v>
+        <v>474871.41403857</v>
       </c>
       <c r="K108" s="11" t="n">
         <v>467074.459917332</v>
@@ -8232,7 +8232,7 @@
         <v>0.999868271923336</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.981639222029191</v>
+        <v>0.981639214615166</v>
       </c>
     </row>
     <row r="109">
@@ -8261,10 +8261,10 @@
         <v>476668.53884325</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>479402.197034839</v>
+        <v>479402.201580536</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>480772.694764073</v>
+        <v>480772.694767214</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>476738.782523127</v>
@@ -8291,7 +8291,7 @@
         <v>1.00014736378459</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.994444300572285</v>
+        <v>0.994444291142954</v>
       </c>
     </row>
     <row r="110">
@@ -8320,10 +8320,10 @@
         <v>485545.679474004</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>482699.47958936</v>
+        <v>482699.485198836</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>486686.100948467</v>
+        <v>486686.100952136</v>
       </c>
       <c r="K110" s="11" t="n">
         <v>485843.974347272</v>
@@ -8350,7 +8350,7 @@
         <v>1.00061434976332</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>1.00651439434032</v>
+        <v>1.00651438264356</v>
       </c>
     </row>
     <row r="111">
@@ -8379,10 +8379,10 @@
         <v>495321.718474781</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>485642.724450079</v>
+        <v>485642.731233362</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>492361.260083551</v>
+        <v>492361.260087676</v>
       </c>
       <c r="K111" s="11" t="n">
         <v>494407.10545474</v>
@@ -8409,7 +8409,7 @@
         <v>0.998153497038536</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>1.01804697272997</v>
+        <v>1.01804695851026</v>
       </c>
     </row>
     <row r="112">
@@ -8438,10 +8438,10 @@
         <v>505624.920127526</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>488174.058904685</v>
+        <v>488174.066966582</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>497543.589030712</v>
+        <v>497543.589035152</v>
       </c>
       <c r="K112" s="11" t="n">
         <v>506507.737994057</v>
@@ -8468,7 +8468,7 @@
         <v>1.00174599358415</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>1.0375556192611</v>
+        <v>1.03755560212651</v>
       </c>
     </row>
     <row r="113">
@@ -8497,10 +8497,10 @@
         <v>513826.620962883</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>490241.087978994</v>
+        <v>490241.097414854</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>501988.733878195</v>
+        <v>501988.733882714</v>
       </c>
       <c r="K113" s="11" t="n">
         <v>513769.275840799</v>
@@ -8527,7 +8527,7 @@
         <v>0.999888395969099</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>1.04799309653705</v>
+        <v>1.04799307636592</v>
       </c>
     </row>
     <row r="114">
@@ -8556,10 +8556,10 @@
         <v>521028.173614831</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>491802.875248251</v>
+        <v>491802.886138929</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>505497.161459061</v>
+        <v>505497.161463309</v>
       </c>
       <c r="K114" s="11" t="n">
         <v>515013.015787655</v>
@@ -8586,7 +8586,7 @@
         <v>1</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>1.05942482209326</v>
+        <v>1.05942479863293</v>
       </c>
     </row>
     <row r="115">
@@ -8615,10 +8615,10 @@
         <v>526357.985138881</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>492833.189405117</v>
+        <v>492833.201811073</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>507928.241316182</v>
+        <v>507928.241319673</v>
       </c>
       <c r="K115" s="11" t="n">
         <v>527580.251263439</v>
@@ -8645,7 +8645,7 @@
         <v>1.00232211946825</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.07050471154401</v>
+        <v>1.07050468459649</v>
       </c>
     </row>
     <row r="116">
@@ -8674,10 +8674,10 @@
         <v>522900.172314508</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>493324.06495373</v>
+        <v>493324.078908224</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>509218.998053213</v>
+        <v>509218.9980553</v>
       </c>
       <c r="K116" s="11" t="n">
         <v>523655.331164013</v>
@@ -8704,7 +8704,7 @@
         <v>1.0014441740307</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.06148345147754</v>
+        <v>1.06148342145171</v>
       </c>
     </row>
     <row r="117">
@@ -8733,10 +8733,10 @@
         <v>512622.376606041</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>493289.253311892</v>
+        <v>493289.26881323</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>509404.716323541</v>
+        <v>509404.716323404</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>511369.68752324</v>
@@ -8763,7 +8763,7 @@
         <v>0.997556312131565</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.03665280378593</v>
+        <v>1.0366527712097</v>
       </c>
     </row>
     <row r="118">
@@ -8792,10 +8792,10 @@
         <v>503892.850307578</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>492761.462938785</v>
+        <v>492761.479941596</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>508592.862446109</v>
+        <v>508592.862442742</v>
       </c>
       <c r="K118" s="11" t="n">
         <v>504314.051060214</v>
@@ -8822,7 +8822,7 @@
         <v>1.00083589348882</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.02344458524116</v>
+        <v>1.02344454992705</v>
       </c>
     </row>
     <row r="119">
@@ -8851,10 +8851,10 @@
         <v>498764.219123197</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>491784.702564973</v>
+        <v>491784.720970523</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>506900.727595859</v>
+        <v>506900.727588068</v>
       </c>
       <c r="K119" s="11" t="n">
         <v>499018.720223509</v>
@@ -8881,7 +8881,7 @@
         <v>1.000510263348</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.01470972484668</v>
+        <v>1.01470968687012</v>
       </c>
     </row>
     <row r="120">
@@ -8910,10 +8910,10 @@
         <v>499613.110810719</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>490410.201288595</v>
+        <v>490410.22093416</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>504424.208890802</v>
+        <v>504424.208877226</v>
       </c>
       <c r="K120" s="11" t="n">
         <v>497750.34656903</v>
@@ -8940,7 +8940,7 @@
         <v>0.996271586550909</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.01496735847082</v>
+        <v>1.01496731781179</v>
       </c>
     </row>
     <row r="121">
@@ -8960,7 +8960,7 @@
         <v>511259.942382052</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5018.29812512343</v>
+        <v>5018.29812512344</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
@@ -8969,10 +8969,10 @@
         <v>504696.22975018</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>488693.709468828</v>
+        <v>488693.730116188</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>501219.793412088</v>
+        <v>501219.793391237</v>
       </c>
       <c r="K121" s="11" t="n">
         <v>506241.644256929</v>
@@ -8999,7 +8999,7 @@
         <v>1.00306206865764</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>1.03590783848471</v>
+        <v>1.0359077947175</v>
       </c>
     </row>
     <row r="122">
@@ -9028,10 +9028,10 @@
         <v>503615.456241012</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>486695.56505565</v>
+        <v>486695.586378813</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>497310.598929259</v>
+        <v>497310.598899579</v>
       </c>
       <c r="K122" s="11" t="n">
         <v>504856.252536742</v>
@@ -9058,7 +9058,7 @@
         <v>1.00246377723391</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>1.03731426539507</v>
+        <v>1.03731421994814</v>
       </c>
     </row>
     <row r="123">
@@ -9087,10 +9087,10 @@
         <v>496922.135204726</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>484487.073458278</v>
+        <v>484487.095030575</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>492744.852466081</v>
+        <v>492744.852426061</v>
       </c>
       <c r="K123" s="11" t="n">
         <v>495004.884416586</v>
@@ -9117,7 +9117,7 @@
         <v>0.996141748068135</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>1.02170916735349</v>
+        <v>1.02170912186081</v>
       </c>
     </row>
     <row r="124">
@@ -9146,10 +9146,10 @@
         <v>494767.383727409</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>482150.890515609</v>
+        <v>482150.911796366</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>487608.509314355</v>
+        <v>487608.509262676</v>
       </c>
       <c r="K124" s="11" t="n">
         <v>494996.716741666</v>
@@ -9176,7 +9176,7 @@
         <v>1.00046351684003</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>1.02664275121906</v>
+        <v>1.026642705906</v>
       </c>
     </row>
     <row r="125">
@@ -9196,7 +9196,7 @@
         <v>501389.215538927</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>4359.41896307207</v>
+        <v>4359.41896307226</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>1</v>
@@ -9205,10 +9205,10 @@
         <v>496803.496841033</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>479776.245698388</v>
+        <v>479776.266019444</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>481998.824925638</v>
+        <v>481998.824861371</v>
       </c>
       <c r="K125" s="11" t="n">
         <v>497029.796575855</v>
@@ -9223,19 +9223,19 @@
         <v>497029.796575855</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.004098847466878</v>
+        <v>0.00409884746687756</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>-0.0181965426700432</v>
+        <v>-0.0181965426700436</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.0041072592310758</v>
+        <v>0.00410725923107536</v>
       </c>
       <c r="R125" s="18" t="n">
         <v>1.00045551155791</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.03596166136227</v>
+        <v>1.03596161748383</v>
       </c>
     </row>
     <row r="126">
@@ -9255,7 +9255,7 @@
         <v>467327.980201225</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>-29097.4880235757</v>
+        <v>-29097.4880235759</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>1</v>
@@ -9264,10 +9264,10 @@
         <v>497163.376366567</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>477460.397118748</v>
+        <v>477460.415671156</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>476049.995788621</v>
+        <v>476049.995711486</v>
       </c>
       <c r="K126" s="11" t="n">
         <v>496425.468224801</v>
@@ -9282,19 +9282,19 @@
         <v>496425.468224801</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>-0.00121661930236443</v>
+        <v>-0.00121661930236354</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>-0.0166993758512033</v>
+        <v>-0.0166993758512028</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>-0.0012158795211421</v>
+        <v>-0.00121587952114122</v>
       </c>
       <c r="R126" s="18" t="n">
         <v>0.998515763274522</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.03972072075611</v>
+        <v>1.03972068035627</v>
       </c>
     </row>
     <row r="127">
@@ -9314,7 +9314,7 @@
         <v>513476.440667766</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>21889.3778089025</v>
+        <v>21889.3778089022</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
@@ -9323,10 +9323,10 @@
         <v>489881.398318818</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>475311.386358125</v>
+        <v>475311.402179447</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>469971.373250248</v>
+        <v>469971.373160936</v>
       </c>
       <c r="K127" s="11" t="n">
         <v>491587.062858864</v>
@@ -9341,19 +9341,19 @@
         <v>491587.062858864</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>-0.00979429691824366</v>
+        <v>-0.00979429691824344</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>-0.00690462188418628</v>
+        <v>-0.00690462188418561</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>-0.00974648900113662</v>
+        <v>-0.00974648900113639</v>
       </c>
       <c r="R127" s="18" t="n">
         <v>1.00348179078834</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.03424213466764</v>
+        <v>1.03424210024163</v>
       </c>
     </row>
     <row r="128">
@@ -9373,7 +9373,7 @@
         <v>474407.554522122</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>3539.24899491714</v>
+        <v>3539.24899491728</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
@@ -9382,10 +9382,10 @@
         <v>471132.771689078</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>473449.108167392</v>
+        <v>473449.12013011</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>464074.186019642</v>
+        <v>464074.1859202</v>
       </c>
       <c r="K128" s="11" t="n">
         <v>470868.305527205</v>
@@ -9400,19 +9400,19 @@
         <v>470868.305527205</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>-0.043060612127851</v>
+        <v>-0.0430606121278519</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>-0.0487445883950237</v>
+        <v>-0.0487445883950239</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>-0.0421466692210477</v>
+        <v>-0.0421466692210486</v>
       </c>
       <c r="R128" s="18" t="n">
         <v>0.999438658956105</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>0.994548933358061</v>
+        <v>0.994548908228626</v>
       </c>
     </row>
     <row r="129">
@@ -9432,46 +9432,46 @@
         <v>448693.775149267</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>2841.32727727668</v>
+        <v>2841.32727727756</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>445533.431675265</v>
+        <v>445533.431675264</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>472003.629595239</v>
+        <v>472003.636396861</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>458777.74125397</v>
+        <v>458777.741148249</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>445852.44787199</v>
+        <v>445852.447871989</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>445852.44787199</v>
+        <v>445852.447871989</v>
       </c>
       <c r="M129" s="13" t="n">
-        <v>445852.44787199</v>
+        <v>445852.447871989</v>
       </c>
       <c r="N129" s="14" t="n">
-        <v>445852.44787199</v>
+        <v>445852.447871989</v>
       </c>
       <c r="O129" s="15" t="n">
-        <v>-0.0545903859054259</v>
+        <v>-0.0545903859054277</v>
       </c>
       <c r="P129" s="16" t="n">
-        <v>-0.102966359474697</v>
+        <v>-0.102966359474699</v>
       </c>
       <c r="Q129" s="17" t="n">
-        <v>-0.0531270789763737</v>
+        <v>-0.0531270789763754</v>
       </c>
       <c r="R129" s="18" t="n">
         <v>1.00071603200578</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>0.944595380027746</v>
+        <v>0.944595366416024</v>
       </c>
     </row>
     <row r="130">
@@ -9491,7 +9491,7 @@
         <v>390971.781617488</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>-29496.4285185237</v>
+        <v>-29496.4285185244</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>0.284622345843011</v>
@@ -9500,10 +9500,10 @@
         <v>425765.319878363</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>471103.404688702</v>
+        <v>471103.40484429</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>454535.316707937</v>
+        <v>454535.316602086</v>
       </c>
       <c r="K130" s="11" t="n">
         <v>420468.210136012</v>
@@ -9518,19 +9518,19 @@
         <v>424257.644077307</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>-0.0496471411020735</v>
+        <v>-0.0496471411020711</v>
       </c>
       <c r="P130" s="16" t="n">
         <v>-0.145374943001138</v>
       </c>
       <c r="Q130" s="17" t="n">
-        <v>-0.0484348665074122</v>
+        <v>-0.0484348665074099</v>
       </c>
       <c r="R130" s="18" t="n">
-        <v>0.996458904164654</v>
+        <v>0.996458904164655</v>
       </c>
       <c r="S130" s="19" t="n">
-        <v>0.900561617374958</v>
+        <v>0.900561617077538</v>
       </c>
     </row>
     <row r="131">
@@ -9550,7 +9550,7 @@
         <v>444096.358125271</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>24896.3321999549</v>
+        <v>24896.3321999539</v>
       </c>
       <c r="G131" s="7" t="n">
         <v>1</v>
@@ -9559,37 +9559,37 @@
         <v>419507.29676177</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>470860.543006244</v>
+        <v>470860.534844156</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>451735.563669338</v>
+        <v>451735.563572337</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>419200.025925316</v>
+        <v>419200.025925317</v>
       </c>
       <c r="L131" s="12" t="n">
-        <v>419200.025925316</v>
+        <v>419200.025925317</v>
       </c>
       <c r="M131" s="13" t="n">
-        <v>419200.025925316</v>
+        <v>419200.025925317</v>
       </c>
       <c r="N131" s="14" t="n">
-        <v>419200.025925316</v>
+        <v>419200.025925317</v>
       </c>
       <c r="O131" s="15" t="n">
-        <v>-0.0119927269609204</v>
+        <v>-0.0119927269609184</v>
       </c>
       <c r="P131" s="16" t="n">
-        <v>-0.147251712672371</v>
+        <v>-0.14725171267237</v>
       </c>
       <c r="Q131" s="17" t="n">
-        <v>-0.0119211008277552</v>
+        <v>-0.0119211008277532</v>
       </c>
       <c r="R131" s="18" t="n">
-        <v>0.999267543523495</v>
+        <v>0.999267543523497</v>
       </c>
       <c r="S131" s="19" t="n">
-        <v>0.890284888279027</v>
+        <v>0.890284903711589</v>
       </c>
     </row>
     <row r="132">
@@ -9609,46 +9609,46 @@
         <v>428054.007663138</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>2785.14180577655</v>
+        <v>2785.14180577698</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>424956.232144147</v>
+        <v>424956.232144146</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>471357.875505942</v>
+        <v>471357.857167744</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>450615.745062815</v>
+        <v>450615.744987</v>
       </c>
       <c r="K132" s="11" t="n">
-        <v>425268.865857362</v>
+        <v>425268.865857361</v>
       </c>
       <c r="L132" s="12" t="n">
-        <v>425268.865857362</v>
+        <v>425268.865857361</v>
       </c>
       <c r="M132" s="13" t="n">
-        <v>425268.865857362</v>
+        <v>425268.865857361</v>
       </c>
       <c r="N132" s="14" t="n">
-        <v>425268.865857362</v>
+        <v>425268.865857361</v>
       </c>
       <c r="O132" s="15" t="n">
-        <v>0.0143733995963923</v>
+        <v>0.014373399596389</v>
       </c>
       <c r="P132" s="16" t="n">
-        <v>-0.0968411743465897</v>
+        <v>-0.0968411743465903</v>
       </c>
       <c r="Q132" s="17" t="n">
-        <v>0.0144771935990462</v>
+        <v>0.0144771935990429</v>
       </c>
       <c r="R132" s="18" t="n">
         <v>1.00073568450011</v>
       </c>
       <c r="S132" s="19" t="n">
-        <v>0.902220771003116</v>
+        <v>0.902220806104054</v>
       </c>
     </row>
     <row r="133">
@@ -9668,46 +9668,46 @@
         <v>433362.880156828</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>-559.10082797262</v>
+        <v>-559.100827970594</v>
       </c>
       <c r="G133" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>433334.880013431</v>
+        <v>433334.880013429</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>472645.945322699</v>
+        <v>472645.914768259</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>451250.446124289</v>
+        <v>451250.44608584</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>433921.9809848</v>
+        <v>433921.980984798</v>
       </c>
       <c r="L133" s="12" t="n">
-        <v>433921.9809848</v>
+        <v>433921.980984798</v>
       </c>
       <c r="M133" s="13" t="n">
-        <v>433921.9809848</v>
+        <v>433921.980984798</v>
       </c>
       <c r="N133" s="14" t="n">
-        <v>433921.9809848</v>
+        <v>433921.980984798</v>
       </c>
       <c r="O133" s="15" t="n">
-        <v>0.020143156176232</v>
+        <v>0.0201431561762281</v>
       </c>
       <c r="P133" s="16" t="n">
-        <v>-0.0267587784795896</v>
+        <v>-0.0267587784795923</v>
       </c>
       <c r="Q133" s="17" t="n">
-        <v>0.0203473986039251</v>
+        <v>0.0203473986039211</v>
       </c>
       <c r="R133" s="18" t="n">
         <v>1.00135484355968</v>
       </c>
       <c r="S133" s="19" t="n">
-        <v>0.918069826429041</v>
+        <v>0.918069885778136</v>
       </c>
     </row>
     <row r="134">
@@ -9727,19 +9727,19 @@
         <v>412150.09254573</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>-28461.5490949431</v>
+        <v>-28461.5490949426</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>439922.402854178</v>
+        <v>439922.40285417</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>474746.489960389</v>
+        <v>474746.444979343</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>453587.517693655</v>
+        <v>453587.517712973</v>
       </c>
       <c r="K134" s="11" t="n">
         <v>440611.641640673</v>
@@ -9754,19 +9754,19 @@
         <v>440611.641640673</v>
       </c>
       <c r="O134" s="15" t="n">
-        <v>0.0152991056389095</v>
+        <v>0.015299105638913</v>
       </c>
       <c r="P134" s="16" t="n">
-        <v>0.0385473256443813</v>
+        <v>0.0385473256443798</v>
       </c>
       <c r="Q134" s="17" t="n">
-        <v>0.0154167360701345</v>
+        <v>0.015416736070138</v>
       </c>
       <c r="R134" s="18" t="n">
-        <v>1.00156672809119</v>
+        <v>1.00156672809121</v>
       </c>
       <c r="S134" s="19" t="n">
-        <v>0.928098787370572</v>
+        <v>0.928098875305625</v>
       </c>
     </row>
     <row r="135">
@@ -9786,46 +9786,46 @@
         <v>478511.050017991</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>29725.1757736966</v>
+        <v>29725.1757737</v>
       </c>
       <c r="G135" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>451101.618074033</v>
+        <v>451101.618074011</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>477657.044445174</v>
+        <v>477656.982676017</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>457488.16828511</v>
+        <v>457488.168387011</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>448785.874244294</v>
+        <v>448785.874244291</v>
       </c>
       <c r="L135" s="12" t="n">
-        <v>448785.874244294</v>
+        <v>448785.874244291</v>
       </c>
       <c r="M135" s="13" t="n">
-        <v>448785.874244294</v>
+        <v>448785.874244291</v>
       </c>
       <c r="N135" s="14" t="n">
-        <v>448785.874244294</v>
+        <v>448785.874244291</v>
       </c>
       <c r="O135" s="15" t="n">
-        <v>0.0183820229498127</v>
+        <v>0.0183820229498063</v>
       </c>
       <c r="P135" s="16" t="n">
-        <v>0.0705769238770269</v>
+        <v>0.0705769238770162</v>
       </c>
       <c r="Q135" s="17" t="n">
-        <v>0.0185520123190195</v>
+        <v>0.018552012319013</v>
       </c>
       <c r="R135" s="18" t="n">
-        <v>0.994866469688968</v>
+        <v>0.994866469689009</v>
       </c>
       <c r="S135" s="19" t="n">
-        <v>0.939556695464598</v>
+        <v>0.939556816965222</v>
       </c>
     </row>
     <row r="136">
@@ -9845,46 +9845,46 @@
         <v>471537.267275214</v>
       </c>
       <c r="F136" s="6" t="n">
-        <v>257.786206066049</v>
+        <v>257.786205980255</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>471107.283701152</v>
+        <v>471107.283701629</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>481353.809523014</v>
+        <v>481353.728481221</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>462748.727032585</v>
+        <v>462748.727246203</v>
       </c>
       <c r="K136" s="11" t="n">
-        <v>471279.481069148</v>
+        <v>471279.481069234</v>
       </c>
       <c r="L136" s="12" t="n">
-        <v>471279.481069148</v>
+        <v>471279.481069234</v>
       </c>
       <c r="M136" s="13" t="n">
-        <v>471279.481069148</v>
+        <v>471279.481069234</v>
       </c>
       <c r="N136" s="14" t="n">
-        <v>471279.481069148</v>
+        <v>471279.481069234</v>
       </c>
       <c r="O136" s="15" t="n">
-        <v>0.0489054168904779</v>
+        <v>0.0489054168906675</v>
       </c>
       <c r="P136" s="16" t="n">
-        <v>0.108191826173372</v>
+        <v>0.108191826173575</v>
       </c>
       <c r="Q136" s="17" t="n">
-        <v>0.0501210223310407</v>
+        <v>0.0501210223312398</v>
       </c>
       <c r="R136" s="18" t="n">
-        <v>1.00036551625066</v>
+        <v>1.00036551624983</v>
       </c>
       <c r="S136" s="19" t="n">
-        <v>0.979070845073712</v>
+        <v>0.979071009912453</v>
       </c>
     </row>
     <row r="137">
@@ -9904,46 +9904,46 @@
         <v>484205.691494541</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>-5183.34740344839</v>
+        <v>-5183.34740406769</v>
       </c>
       <c r="G137" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>487083.26434693</v>
+        <v>487083.264347252</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>485794.941458497</v>
+        <v>485794.838575121</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>469122.011599809</v>
+        <v>469122.011958085</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>489389.038897989</v>
+        <v>489389.038898608</v>
       </c>
       <c r="L137" s="12" t="n">
-        <v>489389.038897989</v>
+        <v>489389.038898608</v>
       </c>
       <c r="M137" s="13" t="n">
-        <v>489389.038897989</v>
+        <v>489389.038898608</v>
       </c>
       <c r="N137" s="14" t="n">
-        <v>489389.038897989</v>
+        <v>489389.038898608</v>
       </c>
       <c r="O137" s="15" t="n">
-        <v>0.0377064576334936</v>
+        <v>0.0377064576345771</v>
       </c>
       <c r="P137" s="16" t="n">
-        <v>0.127827260069435</v>
+        <v>0.127827260070868</v>
       </c>
       <c r="Q137" s="17" t="n">
-        <v>0.0384263660020958</v>
+        <v>0.0384263660032209</v>
       </c>
       <c r="R137" s="18" t="n">
-        <v>1.00473384063842</v>
+        <v>1.00473384063903</v>
       </c>
       <c r="S137" s="19" t="n">
-        <v>1.00739838382981</v>
+        <v>1.00739859718154</v>
       </c>
     </row>
     <row r="138">
@@ -9963,46 +9963,46 @@
         <v>460369.442232949</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>-26386.8464352325</v>
+        <v>-26386.8464318527</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>486395.455465753</v>
+        <v>486395.455457912</v>
       </c>
       <c r="I138" s="9" t="n">
-        <v>490932.300060925</v>
+        <v>490932.172733253</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>476403.493420693</v>
+        <v>476403.493959309</v>
       </c>
       <c r="K138" s="11" t="n">
-        <v>486756.288668181</v>
+        <v>486756.288664801</v>
       </c>
       <c r="L138" s="12" t="n">
-        <v>486756.288668181</v>
+        <v>486756.288664801</v>
       </c>
       <c r="M138" s="13" t="n">
-        <v>486756.288668181</v>
+        <v>486756.288664801</v>
       </c>
       <c r="N138" s="14" t="n">
-        <v>486756.288668181</v>
+        <v>486756.288664801</v>
       </c>
       <c r="O138" s="15" t="n">
-        <v>-0.00539418985939831</v>
+        <v>-0.00539418986760727</v>
       </c>
       <c r="P138" s="16" t="n">
-        <v>0.104728615103502</v>
+        <v>0.104728615095832</v>
       </c>
       <c r="Q138" s="17" t="n">
-        <v>-0.00537966734141881</v>
+        <v>-0.00537966734958362</v>
       </c>
       <c r="R138" s="18" t="n">
-        <v>1.00074185150863</v>
+        <v>1.00074185151781</v>
       </c>
       <c r="S138" s="19" t="n">
-        <v>0.991493712285328</v>
+        <v>0.99149396943125</v>
       </c>
     </row>
     <row r="139">
@@ -10022,46 +10022,46 @@
         <v>514395.681772362</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>35970.2570456107</v>
+        <v>35970.2570584442</v>
       </c>
       <c r="G139" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>480597.138119865</v>
+        <v>480597.138116516</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>496719.9914505</v>
+        <v>496719.837106354</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>484489.979065637</v>
+        <v>484489.979821228</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>478425.424726751</v>
+        <v>478425.424713917</v>
       </c>
       <c r="L139" s="12" t="n">
-        <v>478425.424726751</v>
+        <v>478425.424713917</v>
       </c>
       <c r="M139" s="13" t="n">
-        <v>478425.424726751</v>
+        <v>478425.424713917</v>
       </c>
       <c r="N139" s="14" t="n">
-        <v>478425.424726751</v>
+        <v>478425.424713917</v>
       </c>
       <c r="O139" s="15" t="n">
-        <v>-0.0172632173213955</v>
+        <v>-0.0172632173412766</v>
       </c>
       <c r="P139" s="16" t="n">
-        <v>0.0660438578472784</v>
+        <v>0.0660438578186902</v>
       </c>
       <c r="Q139" s="17" t="n">
-        <v>-0.0171150617575468</v>
+        <v>-0.0171150617770877</v>
       </c>
       <c r="R139" s="18" t="n">
-        <v>0.995481218632283</v>
+        <v>0.995481218612517</v>
       </c>
       <c r="S139" s="19" t="n">
-        <v>0.963169256243691</v>
+        <v>0.963169555500317</v>
       </c>
     </row>
     <row r="140">
@@ -10081,46 +10081,46 @@
         <v>481151.979943508</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>-3202.86604362778</v>
+        <v>-3202.86607571982</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>483033.808082254</v>
+        <v>483033.808127038</v>
       </c>
       <c r="I140" s="9" t="n">
-        <v>503109.511740305</v>
+        <v>503109.327917619</v>
       </c>
       <c r="J140" s="10" t="n">
-        <v>493330.039081282</v>
+        <v>493330.040088724</v>
       </c>
       <c r="K140" s="11" t="n">
-        <v>484354.845987136</v>
+        <v>484354.846019228</v>
       </c>
       <c r="L140" s="12" t="n">
-        <v>484354.845987136</v>
+        <v>484354.846019228</v>
       </c>
       <c r="M140" s="13" t="n">
-        <v>484354.845987136</v>
+        <v>484354.846019228</v>
       </c>
       <c r="N140" s="14" t="n">
-        <v>484354.845987136</v>
+        <v>484354.846019228</v>
       </c>
       <c r="O140" s="15" t="n">
-        <v>0.0123174444012439</v>
+        <v>0.0123174444943256</v>
       </c>
       <c r="P140" s="16" t="n">
-        <v>0.027744396781979</v>
+        <v>0.0277443968498876</v>
       </c>
       <c r="Q140" s="17" t="n">
-        <v>0.0123936165469707</v>
+        <v>0.012393616641206</v>
       </c>
       <c r="R140" s="18" t="n">
-        <v>1.00273487669554</v>
+        <v>1.00273487666901</v>
       </c>
       <c r="S140" s="19" t="n">
-        <v>0.962722498152948</v>
+        <v>0.962722849969774</v>
       </c>
     </row>
     <row r="141">
@@ -10140,46 +10140,46 @@
         <v>484543.676876562</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>-10382.6063704655</v>
+        <v>-10382.6064325374</v>
       </c>
       <c r="G141" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>497199.618960435</v>
+        <v>497199.618962258</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>510040.922939217</v>
+        <v>510040.707382497</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>502841.921242572</v>
+        <v>502841.92253114</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>494926.283247028</v>
+        <v>494926.2833091</v>
       </c>
       <c r="L141" s="12" t="n">
-        <v>494926.283247028</v>
+        <v>494926.2833091</v>
       </c>
       <c r="M141" s="13" t="n">
-        <v>494926.283247028</v>
+        <v>494926.2833091</v>
       </c>
       <c r="N141" s="14" t="n">
-        <v>494926.283247028</v>
+        <v>494926.2833091</v>
       </c>
       <c r="O141" s="15" t="n">
-        <v>0.0215910377879816</v>
+        <v>0.0215910378471409</v>
       </c>
       <c r="P141" s="16" t="n">
-        <v>0.011314606394756</v>
+        <v>0.0113146065203116</v>
       </c>
       <c r="Q141" s="17" t="n">
-        <v>0.0218258108646499</v>
+        <v>0.0218258109251004</v>
       </c>
       <c r="R141" s="18" t="n">
-        <v>0.995427720322553</v>
+        <v>0.995427720443746</v>
       </c>
       <c r="S141" s="19" t="n">
-        <v>0.970365829461118</v>
+        <v>0.970366239685134</v>
       </c>
     </row>
     <row r="142">
@@ -10199,46 +10199,46 @@
         <v>493602.530577855</v>
       </c>
       <c r="F142" s="6" t="n">
-        <v>-24910.2148594123</v>
+        <v>-24910.2146943474</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>517466.951677594</v>
+        <v>517466.951558454</v>
       </c>
       <c r="I142" s="9" t="n">
-        <v>517442.565390022</v>
+        <v>517442.316165251</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>512898.99735898</v>
+        <v>512898.998947476</v>
       </c>
       <c r="K142" s="11" t="n">
-        <v>518512.745437267</v>
+        <v>518512.745272202</v>
       </c>
       <c r="L142" s="12" t="n">
-        <v>518512.745437267</v>
+        <v>518512.745272202</v>
       </c>
       <c r="M142" s="13" t="n">
-        <v>518512.745437267</v>
+        <v>518512.745272202</v>
       </c>
       <c r="N142" s="14" t="n">
-        <v>518512.745437267</v>
+        <v>518512.745272202</v>
       </c>
       <c r="O142" s="15" t="n">
-        <v>0.0465557799862075</v>
+        <v>0.0465557795424481</v>
       </c>
       <c r="P142" s="16" t="n">
-        <v>0.0652409789218649</v>
+        <v>0.0652409785901493</v>
       </c>
       <c r="Q142" s="17" t="n">
-        <v>0.0476565157047175</v>
+        <v>0.0476565152398101</v>
       </c>
       <c r="R142" s="18" t="n">
-        <v>1.00202098656983</v>
+        <v>1.00202098648155</v>
       </c>
       <c r="S142" s="19" t="n">
-        <v>1.00206821030744</v>
+        <v>1.00206869263203</v>
       </c>
     </row>
     <row r="143">
@@ -10258,46 +10258,46 @@
         <v>581668.249879602</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>43713.7494283927</v>
+        <v>43713.7494992862</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>0.445514726382966</v>
+        <v>0.445514726377023</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>529792.920794053</v>
+        <v>529792.920769097</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>525233.332785695</v>
+        <v>525233.048415098</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>523335.061050004</v>
+        <v>523335.062940617</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>537954.50045121</v>
+        <v>537954.500380316</v>
       </c>
       <c r="L143" s="12" t="n">
-        <v>533429.024721864</v>
+        <v>533429.024676394</v>
       </c>
       <c r="M143" s="13" t="n">
-        <v>533429.024721864</v>
+        <v>533429.024676394</v>
       </c>
       <c r="N143" s="14" t="n">
-        <v>533429.024721864</v>
+        <v>533429.024676394</v>
       </c>
       <c r="O143" s="15" t="n">
-        <v>0.0283614160876424</v>
+        <v>0.0283614163207441</v>
       </c>
       <c r="P143" s="16" t="n">
-        <v>0.114967970246414</v>
+        <v>0.114967970181281</v>
       </c>
       <c r="Q143" s="17" t="n">
-        <v>0.0287674303396681</v>
+        <v>0.0287674305794756</v>
       </c>
       <c r="R143" s="18" t="n">
-        <v>1.0068632550287</v>
+        <v>1.0068632549903</v>
       </c>
       <c r="S143" s="19" t="n">
-        <v>1.0156039067298</v>
+        <v>1.01560445650941</v>
       </c>
     </row>
     <row r="144">
@@ -10317,46 +10317,46 @@
         <v>514697.789505428</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>-7732.82682662774</v>
+        <v>-7732.82712388564</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>0.385417569093625</v>
+        <v>0.385417569087655</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>530456.531542601</v>
+        <v>530456.531837088</v>
       </c>
       <c r="I144" s="9" t="n">
-        <v>533332.787681742</v>
+        <v>533332.467299446</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>534011.97467553</v>
+        <v>534011.976845074</v>
       </c>
       <c r="K144" s="11" t="n">
-        <v>522430.616332056</v>
+        <v>522430.616629314</v>
       </c>
       <c r="L144" s="12" t="n">
-        <v>527363.202812401</v>
+        <v>527363.203108004</v>
       </c>
       <c r="M144" s="13" t="n">
-        <v>527363.202812401</v>
+        <v>527363.203108004</v>
       </c>
       <c r="N144" s="14" t="n">
-        <v>527363.202812401</v>
+        <v>527363.203108004</v>
       </c>
       <c r="O144" s="15" t="n">
-        <v>-0.0114365242624155</v>
+        <v>-0.0114365236166439</v>
       </c>
       <c r="P144" s="16" t="n">
-        <v>0.088795140962433</v>
+        <v>0.0887951415005948</v>
       </c>
       <c r="Q144" s="17" t="n">
-        <v>-0.0113713758126034</v>
+        <v>-0.0113713751741752</v>
       </c>
       <c r="R144" s="18" t="n">
-        <v>0.994168553790441</v>
+        <v>0.994168553795782</v>
       </c>
       <c r="S144" s="19" t="n">
-        <v>0.988807016918482</v>
+        <v>0.988807611466695</v>
       </c>
     </row>
     <row r="145">
@@ -10376,46 +10376,46 @@
         <v>522255.200050771</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>-13431.1128278505</v>
+        <v>-13431.1130940792</v>
       </c>
       <c r="G145" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>538178.201509874</v>
+        <v>538178.201529416</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>541665.614941129</v>
+        <v>541665.258470868</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>544842.070413806</v>
+        <v>544842.072804038</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>535686.312878622</v>
+        <v>535686.313144851</v>
       </c>
       <c r="L145" s="12" t="n">
-        <v>535686.312878622</v>
+        <v>535686.313144851</v>
       </c>
       <c r="M145" s="13" t="n">
-        <v>535686.312878622</v>
+        <v>535686.313144851</v>
       </c>
       <c r="N145" s="14" t="n">
-        <v>535686.312878622</v>
+        <v>535686.313144851</v>
       </c>
       <c r="O145" s="15" t="n">
-        <v>0.0156592520291805</v>
+        <v>0.0156592519656366</v>
       </c>
       <c r="P145" s="16" t="n">
-        <v>0.0823557588499499</v>
+        <v>0.0823557592521205</v>
       </c>
       <c r="Q145" s="17" t="n">
-        <v>0.0157825006026855</v>
+        <v>0.0157825005381387</v>
       </c>
       <c r="R145" s="18" t="n">
-        <v>0.99536977041385</v>
+        <v>0.995369770872392</v>
       </c>
       <c r="S145" s="19" t="n">
-        <v>0.988961267066663</v>
+        <v>0.98896191839422</v>
       </c>
     </row>
     <row r="146">
@@ -10435,46 +10435,46 @@
         <v>532348.212016917</v>
       </c>
       <c r="F146" s="6" t="n">
-        <v>-25280.3116086524</v>
+        <v>-25280.3108094755</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>554181.291979931</v>
+        <v>554181.291459919</v>
       </c>
       <c r="I146" s="9" t="n">
-        <v>550152.768436278</v>
+        <v>550152.376791816</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>555704.436583764</v>
+        <v>555704.439092011</v>
       </c>
       <c r="K146" s="11" t="n">
-        <v>557628.52362557</v>
+        <v>557628.522826393</v>
       </c>
       <c r="L146" s="12" t="n">
-        <v>557628.52362557</v>
+        <v>557628.522826393</v>
       </c>
       <c r="M146" s="13" t="n">
-        <v>557628.52362557</v>
+        <v>557628.522826393</v>
       </c>
       <c r="N146" s="14" t="n">
-        <v>557628.52362557</v>
+        <v>557628.522826393</v>
       </c>
       <c r="O146" s="15" t="n">
-        <v>0.0401442598303232</v>
+        <v>0.0401442579001663</v>
       </c>
       <c r="P146" s="16" t="n">
-        <v>0.0754384121364571</v>
+        <v>0.0754384109375286</v>
       </c>
       <c r="Q146" s="17" t="n">
-        <v>0.0409609322086963</v>
+        <v>0.0409609301994784</v>
       </c>
       <c r="R146" s="18" t="n">
-        <v>1.00622040421704</v>
+        <v>1.00622040371914</v>
       </c>
       <c r="S146" s="19" t="n">
-        <v>1.01358850780764</v>
+        <v>1.01358922791204</v>
       </c>
     </row>
     <row r="147">
@@ -10494,46 +10494,46 @@
         <v>614076.392608544</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>49652.5954424188</v>
+        <v>49652.5956166299</v>
       </c>
       <c r="G147" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>565360.865119452</v>
+        <v>565360.865006791</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>558711.464975823</v>
+        <v>558711.040283914</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>566432.382716657</v>
+        <v>566432.385185203</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>564423.797166125</v>
+        <v>564423.796991914</v>
       </c>
       <c r="L147" s="12" t="n">
-        <v>564423.797166125</v>
+        <v>564423.796991914</v>
       </c>
       <c r="M147" s="13" t="n">
-        <v>564423.797166125</v>
+        <v>564423.796991914</v>
       </c>
       <c r="N147" s="14" t="n">
-        <v>564423.797166125</v>
+        <v>564423.796991914</v>
       </c>
       <c r="O147" s="15" t="n">
-        <v>0.012112370327196</v>
+        <v>0.0121123714517137</v>
       </c>
       <c r="P147" s="16" t="n">
-        <v>0.0581047730959563</v>
+        <v>0.0581047728595632</v>
       </c>
       <c r="Q147" s="17" t="n">
-        <v>0.0121860221503272</v>
+        <v>0.0121860232885482</v>
       </c>
       <c r="R147" s="18" t="n">
-        <v>0.998342531273138</v>
+        <v>0.998342531163939</v>
       </c>
       <c r="S147" s="19" t="n">
-        <v>1.0102241184375</v>
+        <v>1.01022488602534</v>
       </c>
     </row>
     <row r="148">
@@ -10553,46 +10553,46 @@
         <v>562978.965626877</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>-10015.5187296057</v>
+        <v>-10015.519793463</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>573563.744063941</v>
+        <v>573563.745137868</v>
       </c>
       <c r="I148" s="9" t="n">
-        <v>567263.59371539</v>
+        <v>567263.139560056</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>576868.838778952</v>
+        <v>576868.840978494</v>
       </c>
       <c r="K148" s="11" t="n">
-        <v>572994.484356482</v>
+        <v>572994.48542034</v>
       </c>
       <c r="L148" s="12" t="n">
-        <v>572994.484356482</v>
+        <v>572994.48542034</v>
       </c>
       <c r="M148" s="13" t="n">
-        <v>572994.484356482</v>
+        <v>572994.48542034</v>
       </c>
       <c r="N148" s="14" t="n">
-        <v>572994.484356482</v>
+        <v>572994.48542034</v>
       </c>
       <c r="O148" s="15" t="n">
-        <v>0.0150707080200368</v>
+        <v>0.0150707101853524</v>
       </c>
       <c r="P148" s="16" t="n">
-        <v>0.0865272383449052</v>
+        <v>0.0865272397531882</v>
       </c>
       <c r="Q148" s="17" t="n">
-        <v>0.0151848437882831</v>
+        <v>0.0151848459864787</v>
       </c>
       <c r="R148" s="18" t="n">
-        <v>0.999007504024879</v>
+        <v>0.999007504009181</v>
       </c>
       <c r="S148" s="19" t="n">
-        <v>1.01010269424053</v>
+        <v>1.01010350481212</v>
       </c>
     </row>
     <row r="149">
@@ -10612,46 +10612,46 @@
         <v>572794.046630588</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>-14706.9163436076</v>
+        <v>-14706.9173431168</v>
       </c>
       <c r="G149" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>587400.451010496</v>
+        <v>587400.451465045</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>575734.614018224</v>
+        <v>575734.135706082</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>586846.691809359</v>
+        <v>586846.693425797</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>587500.962974196</v>
+        <v>587500.963973705</v>
       </c>
       <c r="L149" s="12" t="n">
-        <v>587500.962974196</v>
+        <v>587500.963973705</v>
       </c>
       <c r="M149" s="13" t="n">
-        <v>587500.962974196</v>
+        <v>587500.963973705</v>
       </c>
       <c r="N149" s="14" t="n">
-        <v>587500.962974196</v>
+        <v>587500.963973705</v>
       </c>
       <c r="O149" s="15" t="n">
-        <v>0.0250017943584924</v>
+        <v>0.0250017942031194</v>
       </c>
       <c r="P149" s="16" t="n">
-        <v>0.0967257308052862</v>
+        <v>0.0967257321260768</v>
       </c>
       <c r="Q149" s="17" t="n">
-        <v>0.0253169603089733</v>
+        <v>0.0253169601496668</v>
       </c>
       <c r="R149" s="18" t="n">
-        <v>1.00017111318782</v>
+        <v>1.00017111411544</v>
       </c>
       <c r="S149" s="19" t="n">
-        <v>1.02043710534243</v>
+        <v>1.02043795484385</v>
       </c>
     </row>
     <row r="150">
@@ -10671,46 +10671,46 @@
         <v>576846.885699427</v>
       </c>
       <c r="F150" s="6" t="n">
-        <v>-27503.9500339087</v>
+        <v>-27503.9476139948</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>605487.572889423</v>
+        <v>605487.569889498</v>
       </c>
       <c r="I150" s="9" t="n">
-        <v>584053.567054223</v>
+        <v>584053.071898991</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>596179.457074478</v>
+        <v>596179.457703235</v>
       </c>
       <c r="K150" s="11" t="n">
-        <v>604350.835733336</v>
+        <v>604350.833313422</v>
       </c>
       <c r="L150" s="12" t="n">
-        <v>604350.835733336</v>
+        <v>604350.833313422</v>
       </c>
       <c r="M150" s="13" t="n">
-        <v>604350.835733336</v>
+        <v>604350.833313422</v>
       </c>
       <c r="N150" s="14" t="n">
-        <v>604350.835733336</v>
+        <v>604350.833313422</v>
       </c>
       <c r="O150" s="15" t="n">
-        <v>0.0282769980456602</v>
+        <v>0.0282769923402166</v>
       </c>
       <c r="P150" s="16" t="n">
-        <v>0.0837875218505482</v>
+        <v>0.0837875190641484</v>
       </c>
       <c r="Q150" s="17" t="n">
-        <v>0.0286805874731477</v>
+        <v>0.0286805816040687</v>
       </c>
       <c r="R150" s="18" t="n">
-        <v>0.998122608610012</v>
+        <v>0.998122609558635</v>
       </c>
       <c r="S150" s="19" t="n">
-        <v>1.0347524094091</v>
+        <v>1.03475328252009</v>
       </c>
     </row>
     <row r="151">
@@ -10730,46 +10730,46 @@
         <v>674620.563006485</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>53299.9804386019</v>
+        <v>53299.9842638258</v>
       </c>
       <c r="G151" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>617255.463969821</v>
+        <v>617255.464033304</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>592156.847961379</v>
+        <v>592156.345583451</v>
       </c>
       <c r="J151" s="10" t="n">
-        <v>604683.921196733</v>
+        <v>604683.920339671</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>621320.582567883</v>
+        <v>621320.578742659</v>
       </c>
       <c r="L151" s="12" t="n">
-        <v>621320.582567883</v>
+        <v>621320.578742659</v>
       </c>
       <c r="M151" s="13" t="n">
-        <v>621320.582567883</v>
+        <v>621320.578742659</v>
       </c>
       <c r="N151" s="14" t="n">
-        <v>621320.582567883</v>
+        <v>621320.578742659</v>
       </c>
       <c r="O151" s="15" t="n">
-        <v>0.027692301580996</v>
+        <v>0.0276922994285476</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>0.100805078891831</v>
+        <v>0.100805072454378</v>
       </c>
       <c r="Q151" s="17" t="n">
-        <v>0.0280792973736115</v>
+        <v>0.0280792951607238</v>
       </c>
       <c r="R151" s="18" t="n">
-        <v>1.00658579605261</v>
+        <v>1.00658578975193</v>
       </c>
       <c r="S151" s="19" t="n">
-        <v>1.04925001662466</v>
+        <v>1.04925090033524</v>
       </c>
     </row>
     <row r="152">
@@ -10789,46 +10789,46 @@
         <v>610425.694014854</v>
       </c>
       <c r="F152" s="6" t="n">
-        <v>-10279.7119378741</v>
+        <v>-10279.7219898311</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>625833.642556101</v>
+        <v>625833.647832496</v>
       </c>
       <c r="I152" s="9" t="n">
-        <v>599993.537670612</v>
+        <v>599993.040305013</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>612217.727691842</v>
+        <v>612217.724742018</v>
       </c>
       <c r="K152" s="11" t="n">
-        <v>620705.405952728</v>
+        <v>620705.416004685</v>
       </c>
       <c r="L152" s="12" t="n">
-        <v>620705.405952728</v>
+        <v>620705.416004685</v>
       </c>
       <c r="M152" s="13" t="n">
-        <v>620705.405952728</v>
+        <v>620705.416004685</v>
       </c>
       <c r="N152" s="14" t="n">
-        <v>620705.405952728</v>
+        <v>620705.416004685</v>
       </c>
       <c r="O152" s="15" t="n">
-        <v>-0.000990601921613066</v>
+        <v>-0.000990579570602025</v>
       </c>
       <c r="P152" s="16" t="n">
-        <v>0.0832659351857958</v>
+        <v>0.0832659507173878</v>
       </c>
       <c r="Q152" s="17" t="n">
-        <v>-0.000990111437501051</v>
+        <v>-0.000990089108619752</v>
       </c>
       <c r="R152" s="18" t="n">
-        <v>0.991805751153888</v>
+        <v>0.991805758853695</v>
       </c>
       <c r="S152" s="19" t="n">
-        <v>1.03452015227118</v>
+        <v>1.03452102659248</v>
       </c>
     </row>
     <row r="153">
@@ -10848,46 +10848,46 @@
         <v>625876.867863597</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>-14286.6842632449</v>
+        <v>-14286.6837827625</v>
       </c>
       <c r="G153" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>636769.948527675</v>
+        <v>636769.949186498</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>607530.944446968</v>
+        <v>607530.467254955</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>618721.703382377</v>
+        <v>618721.697609205</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>640163.552126842</v>
+        <v>640163.551646359</v>
       </c>
       <c r="L153" s="12" t="n">
-        <v>640163.552126842</v>
+        <v>640163.551646359</v>
       </c>
       <c r="M153" s="13" t="n">
-        <v>640163.552126842</v>
+        <v>640163.551646359</v>
       </c>
       <c r="N153" s="14" t="n">
-        <v>640163.552126842</v>
+        <v>640163.551646359</v>
       </c>
       <c r="O153" s="15" t="n">
-        <v>0.0308671110774896</v>
+        <v>0.0308670941325191</v>
       </c>
       <c r="P153" s="16" t="n">
-        <v>0.0896383026949332</v>
+        <v>0.0896383000233021</v>
       </c>
       <c r="Q153" s="17" t="n">
-        <v>0.0313484399966641</v>
+        <v>0.0313484225204954</v>
       </c>
       <c r="R153" s="18" t="n">
-        <v>1.00532940288249</v>
+        <v>1.00532940108778</v>
       </c>
       <c r="S153" s="19" t="n">
-        <v>1.05371349061006</v>
+        <v>1.05371431747095</v>
       </c>
     </row>
     <row r="154">
@@ -10907,46 +10907,46 @@
         <v>616720.357064478</v>
       </c>
       <c r="F154" s="6" t="n">
-        <v>-30791.2117616402</v>
+        <v>-30791.2016855936</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>649481.510245762</v>
+        <v>649481.498822842</v>
       </c>
       <c r="I154" s="9" t="n">
-        <v>614749.321473171</v>
+        <v>614748.882859363</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>624179.113482218</v>
+        <v>624179.104096474</v>
       </c>
       <c r="K154" s="11" t="n">
-        <v>647511.568826118</v>
+        <v>647511.558750072</v>
       </c>
       <c r="L154" s="12" t="n">
-        <v>647511.568826118</v>
+        <v>647511.558750072</v>
       </c>
       <c r="M154" s="13" t="n">
-        <v>647511.568826118</v>
+        <v>647511.558750072</v>
       </c>
       <c r="N154" s="14" t="n">
-        <v>647511.568826118</v>
+        <v>647511.558750072</v>
       </c>
       <c r="O154" s="15" t="n">
-        <v>0.011412966422488</v>
+        <v>0.0114129516118659</v>
       </c>
       <c r="P154" s="16" t="n">
-        <v>0.0714166847149473</v>
+        <v>0.0714166723325527</v>
       </c>
       <c r="Q154" s="17" t="n">
-        <v>0.0114783427998426</v>
+        <v>0.0114783278192192</v>
       </c>
       <c r="R154" s="18" t="n">
-        <v>0.996966901461293</v>
+        <v>0.996966903481715</v>
       </c>
       <c r="S154" s="19" t="n">
-        <v>1.05329366980745</v>
+        <v>1.05329440492567</v>
       </c>
     </row>
     <row r="155">
@@ -10966,46 +10966,46 @@
         <v>711405.500455233</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>54621.8476515583</v>
+        <v>54621.856556046</v>
       </c>
       <c r="G155" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>656917.25720046</v>
+        <v>656917.258752203</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>621649.317311744</v>
+        <v>621648.939222072</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>628680.432448965</v>
+        <v>628680.418629251</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>656783.652803675</v>
+        <v>656783.643899187</v>
       </c>
       <c r="L155" s="12" t="n">
-        <v>656783.652803675</v>
+        <v>656783.643899187</v>
       </c>
       <c r="M155" s="13" t="n">
-        <v>656783.652803675</v>
+        <v>656783.643899187</v>
       </c>
       <c r="N155" s="14" t="n">
-        <v>656783.652803675</v>
+        <v>656783.643899187</v>
       </c>
       <c r="O155" s="15" t="n">
-        <v>0.0142180083475058</v>
+        <v>0.0142180103509715</v>
       </c>
       <c r="P155" s="16" t="n">
-        <v>0.0570769281281891</v>
+        <v>0.0570769203046406</v>
       </c>
       <c r="Q155" s="17" t="n">
-        <v>0.0143195649683381</v>
+        <v>0.0143195670004925</v>
       </c>
       <c r="R155" s="18" t="n">
-        <v>0.999796619139898</v>
+        <v>0.999796603223259</v>
       </c>
       <c r="S155" s="19" t="n">
-        <v>1.05651793465143</v>
+        <v>1.05651856290639</v>
       </c>
     </row>
     <row r="156">
@@ -11025,46 +11025,46 @@
         <v>647087.959742494</v>
       </c>
       <c r="F156" s="6" t="n">
-        <v>-8097.31506926742</v>
+        <v>-8097.34627684548</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>651444.874429754</v>
+        <v>651444.890896325</v>
       </c>
       <c r="I156" s="9" t="n">
-        <v>628252.056929806</v>
+        <v>628251.765119347</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>632432.797016937</v>
+        <v>632432.777906232</v>
       </c>
       <c r="K156" s="11" t="n">
-        <v>655185.274811762</v>
+        <v>655185.30601934</v>
       </c>
       <c r="L156" s="12" t="n">
-        <v>655185.274811762</v>
+        <v>655185.30601934</v>
       </c>
       <c r="M156" s="13" t="n">
-        <v>655185.274811762</v>
+        <v>655185.30601934</v>
       </c>
       <c r="N156" s="14" t="n">
-        <v>655185.274811762</v>
+        <v>655185.30601934</v>
       </c>
       <c r="O156" s="15" t="n">
-        <v>-0.0024366107292268</v>
+        <v>-0.00243654953982575</v>
       </c>
       <c r="P156" s="16" t="n">
-        <v>0.0555494901902946</v>
+        <v>0.0555495233738943</v>
       </c>
       <c r="Q156" s="17" t="n">
-        <v>-0.00243364460289142</v>
+        <v>-0.00243358356240175</v>
       </c>
       <c r="R156" s="18" t="n">
-        <v>1.00574169899684</v>
+        <v>1.00574172147988</v>
       </c>
       <c r="S156" s="19" t="n">
-        <v>1.04287008308986</v>
+        <v>1.04287061715597</v>
       </c>
     </row>
     <row r="157">
@@ -11084,46 +11084,46 @@
         <v>613490.821702641</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>-14611.5192580515</v>
+        <v>-14611.5152876867</v>
       </c>
       <c r="G157" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>631536.038540045</v>
+        <v>631536.038903274</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>634600.62425416</v>
+        <v>634600.448517875</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>635783.860022228</v>
+        <v>635783.834752464</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>628102.340960692</v>
+        <v>628102.336990328</v>
       </c>
       <c r="L157" s="12" t="n">
-        <v>628102.340960692</v>
+        <v>628102.336990328</v>
       </c>
       <c r="M157" s="13" t="n">
-        <v>628102.340960692</v>
+        <v>628102.336990328</v>
       </c>
       <c r="N157" s="14" t="n">
-        <v>628102.340960692</v>
+        <v>628102.336990328</v>
       </c>
       <c r="O157" s="15" t="n">
-        <v>-0.0422149414409596</v>
+        <v>-0.0422149953938494</v>
       </c>
       <c r="P157" s="16" t="n">
-        <v>-0.0188408276698631</v>
+        <v>-0.0188408331355525</v>
       </c>
       <c r="Q157" s="17" t="n">
-        <v>-0.0413362981316241</v>
+        <v>-0.0413363498542998</v>
       </c>
       <c r="R157" s="18" t="n">
-        <v>0.994562942777913</v>
+        <v>0.99456293591905</v>
       </c>
       <c r="S157" s="19" t="n">
-        <v>0.989760042702283</v>
+        <v>0.989760310534409</v>
       </c>
     </row>
     <row r="158">
@@ -11143,46 +11143,46 @@
         <v>578553.044242405</v>
       </c>
       <c r="F158" s="6" t="n">
-        <v>-33308.404035247</v>
+        <v>-33308.3761248875</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>608928.07279804</v>
+        <v>608928.050142077</v>
       </c>
       <c r="I158" s="9" t="n">
-        <v>640754.936472782</v>
+        <v>640754.910847407</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>639195.036689906</v>
+        <v>639195.004633555</v>
       </c>
       <c r="K158" s="11" t="n">
-        <v>611861.448277652</v>
+        <v>611861.420367292</v>
       </c>
       <c r="L158" s="12" t="n">
-        <v>611861.448277652</v>
+        <v>611861.420367292</v>
       </c>
       <c r="M158" s="13" t="n">
-        <v>611861.448277652</v>
+        <v>611861.420367292</v>
       </c>
       <c r="N158" s="14" t="n">
-        <v>611861.448277652</v>
+        <v>611861.420367292</v>
       </c>
       <c r="O158" s="15" t="n">
-        <v>-0.0261972513256527</v>
+        <v>-0.0261972906199365</v>
       </c>
       <c r="P158" s="16" t="n">
-        <v>-0.0550571175324287</v>
+        <v>-0.0550571459320315</v>
       </c>
       <c r="Q158" s="17" t="n">
-        <v>-0.0258570803257957</v>
+        <v>-0.0258571186040433</v>
       </c>
       <c r="R158" s="18" t="n">
-        <v>1.00481727745961</v>
+        <v>1.00481726900991</v>
       </c>
       <c r="S158" s="19" t="n">
-        <v>0.954907115731043</v>
+        <v>0.954907110361584</v>
       </c>
     </row>
     <row r="159">
@@ -11202,46 +11202,46 @@
         <v>631197.751860069</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>55272.877849202</v>
+        <v>55272.8968699426</v>
       </c>
       <c r="G159" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>600012.409319093</v>
+        <v>600012.389469185</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>646770.849346592</v>
+        <v>646771.012217989</v>
       </c>
       <c r="J159" s="10" t="n">
-        <v>643089.334649731</v>
+        <v>643089.295526307</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>575924.874010867</v>
+        <v>575924.854990126</v>
       </c>
       <c r="L159" s="12" t="n">
-        <v>600012.409319093</v>
+        <v>600012.389469185</v>
       </c>
       <c r="M159" s="13" t="n">
-        <v>600012.409319093</v>
+        <v>600012.389469185</v>
       </c>
       <c r="N159" s="14" t="n">
-        <v>600012.409319093</v>
+        <v>600012.389469185</v>
       </c>
       <c r="O159" s="15" t="n">
-        <v>-0.0195555279779114</v>
+        <v>-0.0195555154449169</v>
       </c>
       <c r="P159" s="16" t="n">
-        <v>-0.086438271175351</v>
+        <v>-0.0864382890124409</v>
       </c>
       <c r="Q159" s="17" t="n">
-        <v>-0.0193655589707651</v>
+        <v>-0.019365546680479</v>
       </c>
       <c r="R159" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S159" s="19" t="n">
-        <v>0.927704781261034</v>
+        <v>0.927704516953452</v>
       </c>
     </row>
     <row r="160">
@@ -11261,46 +11261,46 @@
         <v>610519.854611727</v>
       </c>
       <c r="F160" s="6" t="n">
-        <v>-6724.05351037027</v>
+        <v>-6724.11379717165</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>0.283989969893299</v>
+        <v>0.283985119508559</v>
       </c>
       <c r="H160" s="8" t="n">
-        <v>608782.531969486</v>
+        <v>608782.554253957</v>
       </c>
       <c r="I160" s="9" t="n">
-        <v>652686.160206388</v>
+        <v>652686.554308117</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>647753.0935894</v>
+        <v>647753.047486188</v>
       </c>
       <c r="K160" s="11" t="n">
-        <v>617243.908122098</v>
+        <v>617243.968408899</v>
       </c>
       <c r="L160" s="12" t="n">
-        <v>611185.477928322</v>
+        <v>611185.46996396</v>
       </c>
       <c r="M160" s="13" t="n">
-        <v>611185.477928322</v>
+        <v>611185.46996396</v>
       </c>
       <c r="N160" s="14" t="n">
-        <v>611185.477928322</v>
+        <v>611185.46996396</v>
       </c>
       <c r="O160" s="15" t="n">
-        <v>0.0184501404352501</v>
+        <v>0.018450160486739</v>
       </c>
       <c r="P160" s="16" t="n">
-        <v>-0.0671562664409405</v>
+        <v>-0.0671563230297494</v>
       </c>
       <c r="Q160" s="17" t="n">
-        <v>0.018621395883976</v>
+        <v>0.0186214163088518</v>
       </c>
       <c r="R160" s="18" t="n">
-        <v>1.00394713355369</v>
+        <v>1.00394708372179</v>
       </c>
       <c r="S160" s="19" t="n">
-        <v>0.936415562626695</v>
+        <v>0.936414985002793</v>
       </c>
     </row>
     <row r="161">
@@ -11320,46 +11320,46 @@
         <v>615220.854937297</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>-14100.47777926</v>
+        <v>-14100.5261971292</v>
       </c>
       <c r="G161" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>627978.278432199</v>
+        <v>627978.255752507</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>658509.44235795</v>
+        <v>658510.114657068</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>653257.26856996</v>
+        <v>653257.21603838</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>629321.332716557</v>
+        <v>629321.381134426</v>
       </c>
       <c r="L161" s="12" t="n">
-        <v>629321.332716557</v>
+        <v>629321.381134426</v>
       </c>
       <c r="M161" s="13" t="n">
-        <v>629321.332716557</v>
+        <v>629321.381134426</v>
       </c>
       <c r="N161" s="14" t="n">
-        <v>629321.332716557</v>
+        <v>629321.381134426</v>
       </c>
       <c r="O161" s="15" t="n">
-        <v>0.0292415114428569</v>
+        <v>0.0292416014105018</v>
       </c>
       <c r="P161" s="16" t="n">
-        <v>0.0019407534033391</v>
+        <v>0.0019408368227698</v>
       </c>
       <c r="Q161" s="17" t="n">
-        <v>0.0296732423186961</v>
+        <v>0.0296733349559768</v>
       </c>
       <c r="R161" s="18" t="n">
-        <v>1.00213869544614</v>
+        <v>1.00213880873998</v>
       </c>
       <c r="S161" s="19" t="n">
-        <v>0.955675488058489</v>
+        <v>0.95567458589783</v>
       </c>
     </row>
     <row r="162">
@@ -11379,46 +11379,46 @@
         <v>611607.33658973</v>
       </c>
       <c r="F162" s="6" t="n">
-        <v>-35316.0099770902</v>
+        <v>-35315.8482046555</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H162" s="8" t="n">
-        <v>650522.981671719</v>
+        <v>650522.904825959</v>
       </c>
       <c r="I162" s="9" t="n">
-        <v>664223.331180633</v>
+        <v>664224.332626406</v>
       </c>
       <c r="J162" s="10" t="n">
-        <v>659489.97657415</v>
+        <v>659489.918820457</v>
       </c>
       <c r="K162" s="11" t="n">
-        <v>646923.34656682</v>
+        <v>646923.184794385</v>
       </c>
       <c r="L162" s="12" t="n">
-        <v>646923.34656682</v>
+        <v>646923.184794385</v>
       </c>
       <c r="M162" s="13" t="n">
-        <v>646923.34656682</v>
+        <v>646923.184794385</v>
       </c>
       <c r="N162" s="14" t="n">
-        <v>646923.34656682</v>
+        <v>646923.184794385</v>
       </c>
       <c r="O162" s="15" t="n">
-        <v>0.0275858232360934</v>
+        <v>0.0275854962351232</v>
       </c>
       <c r="P162" s="16" t="n">
-        <v>0.0573036565514391</v>
+        <v>0.0573034403869528</v>
       </c>
       <c r="Q162" s="17" t="n">
-        <v>0.0279698350193871</v>
+        <v>0.0279694988723087</v>
       </c>
       <c r="R162" s="18" t="n">
-        <v>0.994466551979995</v>
+        <v>0.994466420774936</v>
       </c>
       <c r="S162" s="19" t="n">
-        <v>0.973954566481332</v>
+        <v>0.973952854506835</v>
       </c>
     </row>
     <row r="163">
@@ -11438,46 +11438,46 @@
         <v>733730.773968903</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>55499.9049506251</v>
+        <v>55499.8793821011</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>0.562012863089362</v>
+        <v>0.562012120444692</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>669164.072876947</v>
+        <v>669164.067715763</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>669792.21948527</v>
+        <v>669793.60461924</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>666219.654905444</v>
+        <v>666219.59429547</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>678230.869018278</v>
+        <v>678230.894586802</v>
       </c>
       <c r="L163" s="12" t="n">
-        <v>674259.728935384</v>
+        <v>674259.734311261</v>
       </c>
       <c r="M163" s="13" t="n">
-        <v>674259.728935384</v>
+        <v>674259.734311261</v>
       </c>
       <c r="N163" s="14" t="n">
-        <v>674259.728935384</v>
+        <v>674259.734311261</v>
       </c>
       <c r="O163" s="15" t="n">
-        <v>0.0413875788709055</v>
+        <v>0.0413878369082439</v>
       </c>
       <c r="P163" s="16" t="n">
-        <v>0.123742973417081</v>
+        <v>0.123743019552913</v>
       </c>
       <c r="Q163" s="17" t="n">
-        <v>0.0422559836704555</v>
+        <v>0.0422562526114501</v>
       </c>
       <c r="R163" s="18" t="n">
-        <v>1.00761495762396</v>
+        <v>1.0076149734293</v>
       </c>
       <c r="S163" s="19" t="n">
-        <v>1.0066699930518</v>
+        <v>1.00666791928322</v>
       </c>
     </row>
     <row r="164">
@@ -11497,46 +11497,46 @@
         <v>668566.509488986</v>
       </c>
       <c r="F164" s="6" t="n">
-        <v>-5887.04159871633</v>
+        <v>-5887.17040290788</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H164" s="8" t="n">
-        <v>676786.898237781</v>
+        <v>676787.052208101</v>
       </c>
       <c r="I164" s="9" t="n">
-        <v>675169.687592306</v>
+        <v>675171.513821288</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>673151.907717278</v>
+        <v>673151.847256342</v>
       </c>
       <c r="K164" s="11" t="n">
-        <v>674453.551087702</v>
+        <v>674453.679891894</v>
       </c>
       <c r="L164" s="12" t="n">
-        <v>674453.551087702</v>
+        <v>674453.679891894</v>
       </c>
       <c r="M164" s="13" t="n">
-        <v>674453.551087702</v>
+        <v>674453.679891894</v>
       </c>
       <c r="N164" s="14" t="n">
-        <v>674453.551087702</v>
+        <v>674453.679891894</v>
       </c>
       <c r="O164" s="15" t="n">
-        <v>0.000287417876761649</v>
+        <v>0.00028760087936765</v>
       </c>
       <c r="P164" s="16" t="n">
-        <v>0.103516977160246</v>
+        <v>0.103517202285036</v>
       </c>
       <c r="Q164" s="17" t="n">
-        <v>0.000287459185237093</v>
+        <v>0.000287642240465624</v>
       </c>
       <c r="R164" s="18" t="n">
-        <v>0.996552316310859</v>
+        <v>0.996552279910506</v>
       </c>
       <c r="S164" s="19" t="n">
-        <v>0.998939323672604</v>
+        <v>0.998936812476979</v>
       </c>
     </row>
     <row r="165">
@@ -11556,46 +11556,46 @@
         <v>668190.097719574</v>
       </c>
       <c r="F165" s="6" t="n">
-        <v>-13359.9162816858</v>
+        <v>-13360.0301218416</v>
       </c>
       <c r="G165" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>682784.437379384</v>
+        <v>682784.42276886</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>680312.108015596</v>
+        <v>680314.434749322</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>680032.539533239</v>
+        <v>680032.483196072</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>681550.01400126</v>
+        <v>681550.127841415</v>
       </c>
       <c r="L165" s="12" t="n">
-        <v>681550.01400126</v>
+        <v>681550.127841415</v>
       </c>
       <c r="M165" s="13" t="n">
-        <v>681550.01400126</v>
+        <v>681550.127841415</v>
       </c>
       <c r="N165" s="14" t="n">
-        <v>681550.01400126</v>
+        <v>681550.127841415</v>
       </c>
       <c r="O165" s="15" t="n">
-        <v>0.0104668274974843</v>
+        <v>0.0104668035531164</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>0.0829920718867891</v>
+        <v>0.0829921694585374</v>
       </c>
       <c r="Q165" s="17" t="n">
-        <v>0.010521796352192</v>
+        <v>0.0105217721558866</v>
       </c>
       <c r="R165" s="18" t="n">
-        <v>0.998192074525216</v>
+        <v>0.998192262614254</v>
       </c>
       <c r="S165" s="19" t="n">
-        <v>1.00181961480779</v>
+        <v>1.00181635583339</v>
       </c>
     </row>
     <row r="166">
@@ -11615,46 +11615,46 @@
         <v>662325.585972695</v>
       </c>
       <c r="F166" s="6" t="n">
-        <v>-36290.944013146</v>
+        <v>-36290.5630986634</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H166" s="8" t="n">
-        <v>697896.17786606</v>
+        <v>697895.971374004</v>
       </c>
       <c r="I166" s="9" t="n">
-        <v>685175.405683676</v>
+        <v>685178.293273911</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>686613.863093763</v>
+        <v>686613.816770839</v>
       </c>
       <c r="K166" s="11" t="n">
-        <v>698616.529985841</v>
+        <v>698616.149071358</v>
       </c>
       <c r="L166" s="12" t="n">
-        <v>698616.529985841</v>
+        <v>698616.149071358</v>
       </c>
       <c r="M166" s="13" t="n">
-        <v>698616.529985841</v>
+        <v>698616.149071358</v>
       </c>
       <c r="N166" s="14" t="n">
-        <v>698616.529985841</v>
+        <v>698616.149071358</v>
       </c>
       <c r="O166" s="15" t="n">
-        <v>0.0247323571213522</v>
+        <v>0.0247316448488067</v>
       </c>
       <c r="P166" s="16" t="n">
-        <v>0.0799061955227822</v>
+        <v>0.0799058767593912</v>
       </c>
       <c r="Q166" s="17" t="n">
-        <v>0.0250407389538252</v>
+        <v>0.0250400088457088</v>
       </c>
       <c r="R166" s="18" t="n">
-        <v>1.00103217662258</v>
+        <v>1.00103192700187</v>
       </c>
       <c r="S166" s="19" t="n">
-        <v>1.01961705599861</v>
+        <v>1.0196122030271</v>
       </c>
     </row>
     <row r="167">
@@ -11674,46 +11674,46 @@
         <v>766332.954571613</v>
       </c>
       <c r="F167" s="6" t="n">
-        <v>54624.1583093704</v>
+        <v>54624.1297946173</v>
       </c>
       <c r="G167" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>711303.983742948</v>
+        <v>711303.967836026</v>
       </c>
       <c r="I167" s="9" t="n">
-        <v>689716.279216326</v>
+        <v>689719.787573804</v>
       </c>
       <c r="J167" s="10" t="n">
-        <v>692655.778511629</v>
+        <v>692655.750860049</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>711708.796262242</v>
+        <v>711708.824776995</v>
       </c>
       <c r="L167" s="12" t="n">
-        <v>711708.796262242</v>
+        <v>711708.824776995</v>
       </c>
       <c r="M167" s="13" t="n">
-        <v>711708.796262242</v>
+        <v>711708.824776995</v>
       </c>
       <c r="N167" s="14" t="n">
-        <v>711708.796262242</v>
+        <v>711708.824776995</v>
       </c>
       <c r="O167" s="15" t="n">
-        <v>0.0185668400559421</v>
+        <v>0.0185674253624404</v>
       </c>
       <c r="P167" s="16" t="n">
-        <v>0.0555410114526458</v>
+        <v>0.0555410453272698</v>
       </c>
       <c r="Q167" s="17" t="n">
-        <v>0.0187402755509756</v>
+        <v>0.0187408718264535</v>
       </c>
       <c r="R167" s="18" t="n">
-        <v>1.0005691132463</v>
+        <v>1.00056917571007</v>
       </c>
       <c r="S167" s="19" t="n">
-        <v>1.03188632443315</v>
+        <v>1.03188111693959</v>
       </c>
     </row>
     <row r="168">
@@ -11733,46 +11733,46 @@
         <v>711417.391930105</v>
       </c>
       <c r="F168" s="6" t="n">
-        <v>-5275.62794293304</v>
+        <v>-5275.97857794412</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H168" s="8" t="n">
-        <v>716563.021735347</v>
+        <v>716563.248963284</v>
       </c>
       <c r="I168" s="9" t="n">
-        <v>693899.827936014</v>
+        <v>693904.014487625</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>697978.199234077</v>
+        <v>697978.20000461</v>
       </c>
       <c r="K168" s="11" t="n">
-        <v>716693.019873038</v>
+        <v>716693.370508049</v>
       </c>
       <c r="L168" s="12" t="n">
-        <v>716693.019873038</v>
+        <v>716693.370508049</v>
       </c>
       <c r="M168" s="13" t="n">
-        <v>716693.019873038</v>
+        <v>716693.370508049</v>
       </c>
       <c r="N168" s="14" t="n">
-        <v>716693.019873038</v>
+        <v>716693.370508049</v>
       </c>
       <c r="O168" s="15" t="n">
-        <v>0.00697876995598783</v>
+        <v>0.00697921913083676</v>
       </c>
       <c r="P168" s="16" t="n">
-        <v>0.0626276912875845</v>
+        <v>0.0626280082316784</v>
       </c>
       <c r="Q168" s="17" t="n">
-        <v>0.00700317831811526</v>
+        <v>0.00700363063871734</v>
       </c>
       <c r="R168" s="18" t="n">
-        <v>1.00018141898723</v>
+        <v>1.00018159115047</v>
       </c>
       <c r="S168" s="19" t="n">
-        <v>1.03284795732667</v>
+        <v>1.0328422311222</v>
       </c>
     </row>
     <row r="169">
@@ -11792,46 +11792,46 @@
         <v>703050.456407993</v>
       </c>
       <c r="F169" s="6" t="n">
-        <v>-11898.112429874</v>
+        <v>-11898.311364214</v>
       </c>
       <c r="G169" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>715431.78287868</v>
+        <v>715432.269652633</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>697704.896488361</v>
+        <v>697709.81400225</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>702496.303797098</v>
+        <v>702496.344115013</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>714948.568837867</v>
+        <v>714948.767772207</v>
       </c>
       <c r="L169" s="12" t="n">
-        <v>714948.568837867</v>
+        <v>714948.767772207</v>
       </c>
       <c r="M169" s="13" t="n">
-        <v>714948.568837867</v>
+        <v>714948.767772207</v>
       </c>
       <c r="N169" s="14" t="n">
-        <v>714948.568837867</v>
+        <v>714948.767772207</v>
       </c>
       <c r="O169" s="15" t="n">
-        <v>-0.00243699528188768</v>
+        <v>-0.00243720627211026</v>
       </c>
       <c r="P169" s="16" t="n">
-        <v>0.0490038209236177</v>
+        <v>0.0490039375923386</v>
       </c>
       <c r="Q169" s="17" t="n">
-        <v>-0.00243402821961403</v>
+        <v>-0.00243423869625825</v>
       </c>
       <c r="R169" s="18" t="n">
-        <v>0.99932458404508</v>
+        <v>0.999324182174979</v>
       </c>
       <c r="S169" s="19" t="n">
-        <v>1.0247148507002</v>
+        <v>1.02470791355373</v>
       </c>
     </row>
     <row r="170">
@@ -11851,46 +11851,46 @@
         <v>672685.993630504</v>
       </c>
       <c r="F170" s="6" t="n">
-        <v>-37502.3259685763</v>
+        <v>-37501.5869142363</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>0.900456265482922</v>
+        <v>0.900728657550881</v>
       </c>
       <c r="H170" s="8" t="n">
-        <v>707157.988826543</v>
+        <v>707158.380931803</v>
       </c>
       <c r="I170" s="9" t="n">
-        <v>701124.575263948</v>
+        <v>701130.269452067</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>706218.844839878</v>
+        <v>706218.938954269</v>
       </c>
       <c r="K170" s="11" t="n">
-        <v>710188.31959908</v>
+        <v>710187.580544741</v>
       </c>
       <c r="L170" s="12" t="n">
-        <v>709886.66915716</v>
+        <v>709886.867832618</v>
       </c>
       <c r="M170" s="13" t="n">
-        <v>709886.66915716</v>
+        <v>709886.867832618</v>
       </c>
       <c r="N170" s="14" t="n">
-        <v>709886.66915716</v>
+        <v>709886.867832618</v>
       </c>
       <c r="O170" s="15" t="n">
-        <v>-0.00710527202232742</v>
+        <v>-0.00710527040292747</v>
       </c>
       <c r="P170" s="16" t="n">
-        <v>0.0161320820329678</v>
+        <v>0.0161329204545888</v>
       </c>
       <c r="Q170" s="17" t="n">
-        <v>-0.00708008925583903</v>
+        <v>-0.00708008764790458</v>
       </c>
       <c r="R170" s="18" t="n">
-        <v>1.00385865729262</v>
+        <v>1.00385838162198</v>
       </c>
       <c r="S170" s="19" t="n">
-        <v>1.0124971997878</v>
+        <v>1.01248926021607</v>
       </c>
     </row>
     <row r="171">
@@ -11910,46 +11910,46 @@
         <v>730838.272592776</v>
       </c>
       <c r="F171" s="6" t="n">
-        <v>54045.7394249439</v>
+        <v>54045.8114452843</v>
       </c>
       <c r="G171" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>701246.431415367</v>
+        <v>701246.637380567</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>704162.731948577</v>
+        <v>704169.23851757</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>709216.836326808</v>
+        <v>709217.002403674</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>676792.533167832</v>
+        <v>676792.461147492</v>
       </c>
       <c r="L171" s="12" t="n">
-        <v>701246.431415367</v>
+        <v>701246.637380567</v>
       </c>
       <c r="M171" s="13" t="n">
-        <v>701246.431415367</v>
+        <v>701246.637380567</v>
       </c>
       <c r="N171" s="14" t="n">
-        <v>701246.431415367</v>
+        <v>701246.637380567</v>
       </c>
       <c r="O171" s="15" t="n">
-        <v>-0.0122459684559648</v>
+        <v>-0.0122459546122205</v>
       </c>
       <c r="P171" s="16" t="n">
-        <v>-0.0147003450032113</v>
+        <v>-0.0147000950841188</v>
       </c>
       <c r="Q171" s="17" t="n">
-        <v>-0.012171291724708</v>
+        <v>-0.0121712780494598</v>
       </c>
       <c r="R171" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S171" s="19" t="n">
-        <v>0.995858484976704</v>
+        <v>0.995849575674229</v>
       </c>
     </row>
     <row r="172">
@@ -11969,46 +11969,46 @@
         <v>703461.652530196</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>-4657.95456327896</v>
+        <v>-4658.59242974422</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H172" s="8" t="n">
-        <v>707331.253584538</v>
+        <v>707331.911214434</v>
       </c>
       <c r="I172" s="9" t="n">
-        <v>706828.710536733</v>
+        <v>706836.051753242</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>711579.631343865</v>
+        <v>711579.891988916</v>
       </c>
       <c r="K172" s="11" t="n">
-        <v>708119.607093475</v>
+        <v>708120.24495994</v>
       </c>
       <c r="L172" s="12" t="n">
-        <v>708119.607093475</v>
+        <v>708120.24495994</v>
       </c>
       <c r="M172" s="13" t="n">
-        <v>708119.607093475</v>
+        <v>708120.24495994</v>
       </c>
       <c r="N172" s="14" t="n">
-        <v>708119.607093475</v>
+        <v>708120.24495994</v>
       </c>
       <c r="O172" s="15" t="n">
-        <v>0.00975364806503355</v>
+        <v>0.00975425514082008</v>
       </c>
       <c r="P172" s="16" t="n">
-        <v>-0.0119624616702442</v>
+        <v>-0.011962055044588</v>
       </c>
       <c r="Q172" s="17" t="n">
-        <v>0.00980136991818359</v>
+        <v>0.00980198294433055</v>
       </c>
       <c r="R172" s="18" t="n">
-        <v>1.0011145464094</v>
+        <v>1.00111451743235</v>
       </c>
       <c r="S172" s="19" t="n">
-        <v>1.00182632162149</v>
+        <v>1.00181681905374</v>
       </c>
     </row>
     <row r="173">
@@ -12028,46 +12028,46 @@
         <v>706958.039082319</v>
       </c>
       <c r="F173" s="6" t="n">
-        <v>-11465.302996061</v>
+        <v>-11466.2687768384</v>
       </c>
       <c r="G173" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>715749.203219501</v>
+        <v>715749.28847516</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>709130.032335064</v>
+        <v>709138.213087855</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>713356.730952468</v>
+        <v>713357.113410565</v>
       </c>
       <c r="K173" s="11" t="n">
-        <v>718423.34207838</v>
+        <v>718424.307859157</v>
       </c>
       <c r="L173" s="12" t="n">
-        <v>718423.34207838</v>
+        <v>718424.307859157</v>
       </c>
       <c r="M173" s="13" t="n">
-        <v>718423.34207838</v>
+        <v>718424.307859157</v>
       </c>
       <c r="N173" s="14" t="n">
-        <v>718423.34207838</v>
+        <v>718424.307859157</v>
       </c>
       <c r="O173" s="15" t="n">
-        <v>0.0144459922191054</v>
+        <v>0.0144464357354043</v>
       </c>
       <c r="P173" s="16" t="n">
-        <v>0.00486017231443858</v>
+        <v>0.00486124355145123</v>
       </c>
       <c r="Q173" s="17" t="n">
-        <v>0.0145508398322665</v>
+        <v>0.0145512898021998</v>
       </c>
       <c r="R173" s="18" t="n">
-        <v>1.00373613948412</v>
+        <v>1.00373736925355</v>
       </c>
       <c r="S173" s="19" t="n">
-        <v>1.01310522657278</v>
+        <v>1.01309490110661</v>
       </c>
     </row>
     <row r="174">
@@ -12087,46 +12087,46 @@
         <v>677085.529173151</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>-38169.5713006668</v>
+        <v>-38167.3931513521</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H174" s="8" t="n">
-        <v>717929.353259878</v>
+        <v>717928.38581569</v>
       </c>
       <c r="I174" s="9" t="n">
-        <v>711075.025460569</v>
+        <v>711084.029070935</v>
       </c>
       <c r="J174" s="10" t="n">
-        <v>714580.336092785</v>
+        <v>714580.874134049</v>
       </c>
       <c r="K174" s="11" t="n">
-        <v>715255.100473818</v>
+        <v>715252.922324503</v>
       </c>
       <c r="L174" s="12" t="n">
-        <v>715255.100473818</v>
+        <v>715252.922324503</v>
       </c>
       <c r="M174" s="13" t="n">
-        <v>715255.100473818</v>
+        <v>715252.922324503</v>
       </c>
       <c r="N174" s="14" t="n">
-        <v>715255.100473818</v>
+        <v>715252.922324503</v>
       </c>
       <c r="O174" s="15" t="n">
-        <v>-0.00441974527611492</v>
+        <v>-0.00442413486197623</v>
       </c>
       <c r="P174" s="16" t="n">
-        <v>0.00756237798215231</v>
+        <v>0.00755902769164929</v>
       </c>
       <c r="Q174" s="17" t="n">
-        <v>-0.00440999257540342</v>
+        <v>-0.00441436279363194</v>
       </c>
       <c r="R174" s="18" t="n">
-        <v>0.996275047434796</v>
+        <v>0.996273356028196</v>
       </c>
       <c r="S174" s="19" t="n">
-        <v>1.00587852879595</v>
+        <v>1.00586272941471</v>
       </c>
     </row>
     <row r="175">
@@ -12146,46 +12146,46 @@
         <v>776486.60279942</v>
       </c>
       <c r="F175" s="6" t="n">
-        <v>54400.6037280793</v>
+        <v>54400.2982988863</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>721718.710580521</v>
+        <v>721718.352545025</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>712677.826348837</v>
+        <v>712687.61006124</v>
       </c>
       <c r="J175" s="10" t="n">
-        <v>715307.980760613</v>
+        <v>715308.717597039</v>
       </c>
       <c r="K175" s="11" t="n">
-        <v>722085.999071341</v>
+        <v>722086.304500534</v>
       </c>
       <c r="L175" s="12" t="n">
-        <v>722085.999071341</v>
+        <v>722086.304500534</v>
       </c>
       <c r="M175" s="13" t="n">
-        <v>722085.999071341</v>
+        <v>722086.304500534</v>
       </c>
       <c r="N175" s="14" t="n">
-        <v>722085.999071341</v>
+        <v>722086.304500534</v>
       </c>
       <c r="O175" s="15" t="n">
-        <v>0.00950498114545707</v>
+        <v>0.00950844940791782</v>
       </c>
       <c r="P175" s="16" t="n">
-        <v>0.0297178947690497</v>
+        <v>0.0297180278793365</v>
       </c>
       <c r="Q175" s="17" t="n">
-        <v>0.0095502969402077</v>
+        <v>0.00955379833167669</v>
       </c>
       <c r="R175" s="18" t="n">
-        <v>1.00050890809042</v>
+        <v>1.00050982762765</v>
       </c>
       <c r="S175" s="19" t="n">
-        <v>1.01320115818771</v>
+        <v>1.01318767761163</v>
       </c>
     </row>
     <row r="176">
@@ -12205,46 +12205,46 @@
         <v>721458.944216182</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>-4507.43440759956</v>
+        <v>-4508.46162613054</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H176" s="8" t="n">
-        <v>724817.620305716</v>
+        <v>724819.188434669</v>
       </c>
       <c r="I176" s="9" t="n">
-        <v>713955.183982339</v>
+        <v>713965.67197581</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>715600.572773655</v>
+        <v>715601.547478157</v>
       </c>
       <c r="K176" s="11" t="n">
-        <v>725966.378623782</v>
+        <v>725967.405842313</v>
       </c>
       <c r="L176" s="12" t="n">
-        <v>725966.378623782</v>
+        <v>725967.405842313</v>
       </c>
       <c r="M176" s="13" t="n">
-        <v>725966.378623782</v>
+        <v>725967.405842313</v>
       </c>
       <c r="N176" s="14" t="n">
-        <v>725966.378623782</v>
+        <v>725967.405842313</v>
       </c>
       <c r="O176" s="15" t="n">
-        <v>0.00535945923017619</v>
+        <v>0.00536045121460915</v>
       </c>
       <c r="P176" s="16" t="n">
-        <v>0.0252030467050051</v>
+        <v>0.0252035738413072</v>
       </c>
       <c r="Q176" s="17" t="n">
-        <v>0.00537384682355246</v>
+        <v>0.00537484413925249</v>
       </c>
       <c r="R176" s="18" t="n">
-        <v>1.00158489292462</v>
+        <v>1.00158414322629</v>
       </c>
       <c r="S176" s="19" t="n">
-        <v>1.0168234574255</v>
+        <v>1.01680995927058</v>
       </c>
     </row>
     <row r="177">
@@ -12264,46 +12264,46 @@
         <v>706597.345022507</v>
       </c>
       <c r="F177" s="6" t="n">
-        <v>-12351.3543078666</v>
+        <v>-12352.9879859905</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>718805.759224064</v>
+        <v>718805.841866072</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>714929.727451497</v>
+        <v>714940.804915713</v>
       </c>
       <c r="J177" s="10" t="n">
-        <v>715552.910041166</v>
+        <v>715554.155390541</v>
       </c>
       <c r="K177" s="11" t="n">
-        <v>718948.699330374</v>
+        <v>718950.333008497</v>
       </c>
       <c r="L177" s="12" t="n">
-        <v>718948.699330374</v>
+        <v>718950.333008497</v>
       </c>
       <c r="M177" s="13" t="n">
-        <v>718948.699330374</v>
+        <v>718950.333008497</v>
       </c>
       <c r="N177" s="14" t="n">
-        <v>718948.699330374</v>
+        <v>718950.333008497</v>
       </c>
       <c r="O177" s="15" t="n">
-        <v>-0.00971369816865704</v>
+        <v>-0.00971284082203102</v>
       </c>
       <c r="P177" s="16" t="n">
-        <v>0.000731264174231638</v>
+        <v>0.00073219286093984</v>
       </c>
       <c r="Q177" s="17" t="n">
-        <v>-0.00966667258986809</v>
+        <v>-0.00966582353056722</v>
       </c>
       <c r="R177" s="18" t="n">
-        <v>1.00019885776439</v>
+        <v>1.00020101553717</v>
       </c>
       <c r="S177" s="19" t="n">
-        <v>1.00562149218945</v>
+        <v>1.00560819590268</v>
       </c>
     </row>
     <row r="178">
@@ -12323,46 +12323,46 @@
         <v>671066.046635063</v>
       </c>
       <c r="F178" s="6" t="n">
-        <v>-37664.368991795</v>
+        <v>-37660.7735744018</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H178" s="8" t="n">
-        <v>710246.392083369</v>
+        <v>710244.912495338</v>
       </c>
       <c r="I178" s="9" t="n">
-        <v>715631.592843386</v>
+        <v>715643.100065681</v>
       </c>
       <c r="J178" s="10" t="n">
-        <v>715311.619501653</v>
+        <v>715313.162239154</v>
       </c>
       <c r="K178" s="11" t="n">
-        <v>708730.415626858</v>
+        <v>708726.820209465</v>
       </c>
       <c r="L178" s="12" t="n">
-        <v>708730.415626858</v>
+        <v>708726.820209465</v>
       </c>
       <c r="M178" s="13" t="n">
-        <v>708730.415626858</v>
+        <v>708726.820209465</v>
       </c>
       <c r="N178" s="14" t="n">
-        <v>708730.415626858</v>
+        <v>708726.820209465</v>
       </c>
       <c r="O178" s="15" t="n">
-        <v>-0.0143147827605432</v>
+        <v>-0.0143221281256214</v>
       </c>
       <c r="P178" s="16" t="n">
-        <v>-0.00912217870608367</v>
+        <v>-0.00912418797791026</v>
       </c>
       <c r="Q178" s="17" t="n">
-        <v>-0.0142128133941033</v>
+        <v>-0.0142200543342846</v>
       </c>
       <c r="R178" s="18" t="n">
-        <v>0.997865562608401</v>
+        <v>0.99786257914817</v>
       </c>
       <c r="S178" s="19" t="n">
-        <v>0.990356522426424</v>
+        <v>0.990335573897685</v>
       </c>
     </row>
     <row r="179">
@@ -12382,46 +12382,46 @@
         <v>760576.868348004</v>
       </c>
       <c r="F179" s="6" t="n">
-        <v>55621.1782845195</v>
+        <v>55620.434943186</v>
       </c>
       <c r="G179" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>702938.776970415</v>
+        <v>702938.214791941</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>716093.428102503</v>
+        <v>716105.154565505</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>715040.30704007</v>
+        <v>715042.169817044</v>
       </c>
       <c r="K179" s="11" t="n">
-        <v>704955.690063485</v>
+        <v>704956.433404818</v>
       </c>
       <c r="L179" s="12" t="n">
-        <v>704955.690063485</v>
+        <v>704956.433404818</v>
       </c>
       <c r="M179" s="13" t="n">
-        <v>704955.690063485</v>
+        <v>704956.433404818</v>
       </c>
       <c r="N179" s="14" t="n">
-        <v>704955.690063485</v>
+        <v>704956.433404818</v>
       </c>
       <c r="O179" s="15" t="n">
-        <v>-0.00534027252438956</v>
+        <v>-0.0053341450214344</v>
       </c>
       <c r="P179" s="16" t="n">
-        <v>-0.0237233640174259</v>
+        <v>-0.0237227475288627</v>
       </c>
       <c r="Q179" s="17" t="n">
-        <v>-0.00532603861799041</v>
+        <v>-0.00531994373167943</v>
       </c>
       <c r="R179" s="18" t="n">
-        <v>1.0028692585459</v>
+        <v>1.00287111807326</v>
       </c>
       <c r="S179" s="19" t="n">
-        <v>0.98444652945841</v>
+        <v>0.98443144684882</v>
       </c>
     </row>
     <row r="180">
@@ -12441,46 +12441,46 @@
         <v>690879.798251683</v>
       </c>
       <c r="F180" s="6" t="n">
-        <v>-5742.73138823935</v>
+        <v>-5743.96917105721</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H180" s="8" t="n">
-        <v>697901.538508668</v>
+        <v>697902.012992723</v>
       </c>
       <c r="I180" s="9" t="n">
-        <v>716343.567937587</v>
+        <v>716355.242880064</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>714869.672521994</v>
+        <v>714871.848207115</v>
       </c>
       <c r="K180" s="11" t="n">
-        <v>696622.529639923</v>
+        <v>696623.767422741</v>
       </c>
       <c r="L180" s="12" t="n">
-        <v>696622.529639923</v>
+        <v>696623.767422741</v>
       </c>
       <c r="M180" s="13" t="n">
-        <v>696622.529639923</v>
+        <v>696623.767422741</v>
       </c>
       <c r="N180" s="14" t="n">
-        <v>696622.529639923</v>
+        <v>696623.767422741</v>
       </c>
       <c r="O180" s="15" t="n">
-        <v>-0.0118912501633652</v>
+        <v>-0.0118905277812125</v>
       </c>
       <c r="P180" s="16" t="n">
-        <v>-0.0404203966573307</v>
+        <v>-0.040420049417406</v>
       </c>
       <c r="Q180" s="17" t="n">
-        <v>-0.0118208286577721</v>
+        <v>-0.0118201148145172</v>
       </c>
       <c r="R180" s="18" t="n">
-        <v>0.998167350552804</v>
+        <v>0.998168445503544</v>
       </c>
       <c r="S180" s="19" t="n">
-        <v>0.972469860580388</v>
+        <v>0.972455739448497</v>
       </c>
     </row>
     <row r="181">
@@ -12500,46 +12500,46 @@
         <v>686701.470618711</v>
       </c>
       <c r="F181" s="6" t="n">
-        <v>-13495.906195128</v>
+        <v>-13498.1618671241</v>
       </c>
       <c r="G181" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>701404.263479165</v>
+        <v>701410.935372427</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>716403.385971101</v>
+        <v>716414.671523515</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>714879.992728121</v>
+        <v>714882.438810207</v>
       </c>
       <c r="K181" s="11" t="n">
-        <v>700197.376813838</v>
+        <v>700199.632485835</v>
       </c>
       <c r="L181" s="12" t="n">
-        <v>700197.376813838</v>
+        <v>700199.632485835</v>
       </c>
       <c r="M181" s="13" t="n">
-        <v>700197.376813838</v>
+        <v>700199.632485835</v>
       </c>
       <c r="N181" s="14" t="n">
-        <v>700197.376813838</v>
+        <v>700199.632485835</v>
       </c>
       <c r="O181" s="15" t="n">
-        <v>0.00511856247521053</v>
+        <v>0.00512000711749645</v>
       </c>
       <c r="P181" s="16" t="n">
-        <v>-0.0260815862578234</v>
+        <v>-0.0260806618507278</v>
       </c>
       <c r="Q181" s="17" t="n">
-        <v>0.00513168469553182</v>
+        <v>0.0051331367523153</v>
       </c>
       <c r="R181" s="18" t="n">
-        <v>0.998279328016428</v>
+        <v>0.998273048186868</v>
       </c>
       <c r="S181" s="19" t="n">
-        <v>0.977378653598497</v>
+        <v>0.97736640568346</v>
       </c>
     </row>
     <row r="182">
@@ -12559,46 +12559,46 @@
         <v>672749.811391699</v>
       </c>
       <c r="F182" s="6" t="n">
-        <v>-35838.8889536653</v>
+        <v>-35834.149244058</v>
       </c>
       <c r="G182" s="7" t="n">
-        <v>0.062712646304365</v>
+        <v>0.0603254534895203</v>
       </c>
       <c r="H182" s="8" t="n">
-        <v>713359.858035176</v>
+        <v>713372.133442918</v>
       </c>
       <c r="I182" s="9" t="n">
-        <v>716281.930176572</v>
+        <v>716292.414837852</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>715060.308724738</v>
+        <v>715062.942623239</v>
       </c>
       <c r="K182" s="11" t="n">
-        <v>708588.700345365</v>
+        <v>708583.960635757</v>
       </c>
       <c r="L182" s="12" t="n">
-        <v>713060.646110512</v>
+        <v>713083.28474694</v>
       </c>
       <c r="M182" s="13" t="n">
-        <v>713060.646110512</v>
+        <v>713083.28474694</v>
       </c>
       <c r="N182" s="14" t="n">
-        <v>713060.646110512</v>
+        <v>713083.28474694</v>
       </c>
       <c r="O182" s="15" t="n">
-        <v>0.018204212280473</v>
+        <v>0.0182327388442518</v>
       </c>
       <c r="P182" s="16" t="n">
-        <v>0.00610984146888183</v>
+        <v>0.00614688821313059</v>
       </c>
       <c r="Q182" s="17" t="n">
-        <v>0.0183709190045906</v>
+        <v>0.0183999700419233</v>
       </c>
       <c r="R182" s="18" t="n">
-        <v>0.999580559627384</v>
+        <v>0.99959509394545</v>
       </c>
       <c r="S182" s="19" t="n">
-        <v>0.99550277072428</v>
+        <v>0.995519804447967</v>
       </c>
     </row>
     <row r="183">
@@ -12618,46 +12618,46 @@
         <v>791235.96554167</v>
       </c>
       <c r="F183" s="6" t="n">
-        <v>56035.9632560903</v>
+        <v>56034.5698284097</v>
       </c>
       <c r="G183" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>723341.474300222</v>
+        <v>723349.635015566</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>715978.119771804</v>
+        <v>715987.312765669</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>715326.248498557</v>
+        <v>715328.946611508</v>
       </c>
       <c r="K183" s="11" t="n">
-        <v>735200.00228558</v>
+        <v>735201.395713261</v>
       </c>
       <c r="L183" s="12" t="n">
-        <v>723341.474300222</v>
+        <v>723349.635015566</v>
       </c>
       <c r="M183" s="13" t="n">
-        <v>723341.474300222</v>
+        <v>723349.635015566</v>
       </c>
       <c r="N183" s="14" t="n">
-        <v>723341.474300222</v>
+        <v>723349.635015566</v>
       </c>
       <c r="O183" s="15" t="n">
-        <v>0.0143149381403933</v>
+        <v>0.014294472005917</v>
       </c>
       <c r="P183" s="16" t="n">
-        <v>0.0260807657784585</v>
+        <v>0.0260912600256897</v>
       </c>
       <c r="Q183" s="17" t="n">
-        <v>0.0144178875188075</v>
+        <v>0.0143971265183558</v>
       </c>
       <c r="R183" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S183" s="19" t="n">
-        <v>1.01028432898308</v>
+        <v>1.01028275518104</v>
       </c>
     </row>
     <row r="184">
@@ -12677,46 +12677,46 @@
         <v>718281.265449782</v>
       </c>
       <c r="F184" s="6" t="n">
-        <v>-7447.65730990614</v>
+        <v>-7448.75265458197</v>
       </c>
       <c r="G184" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H184" s="8" t="n">
-        <v>724458.236475064</v>
+        <v>724459.573002908</v>
       </c>
       <c r="I184" s="9" t="n">
-        <v>715488.860672061</v>
+        <v>715496.199543257</v>
       </c>
       <c r="J184" s="10" t="n">
-        <v>715583.441723222</v>
+        <v>715586.139450929</v>
       </c>
       <c r="K184" s="11" t="n">
-        <v>725728.922759688</v>
+        <v>725730.018104364</v>
       </c>
       <c r="L184" s="12" t="n">
-        <v>725728.922759688</v>
+        <v>725730.018104364</v>
       </c>
       <c r="M184" s="13" t="n">
-        <v>725728.922759688</v>
+        <v>725730.018104364</v>
       </c>
       <c r="N184" s="14" t="n">
-        <v>725728.922759688</v>
+        <v>725730.018104364</v>
       </c>
       <c r="O184" s="15" t="n">
-        <v>0.0032951478748752</v>
+        <v>0.00328537527218102</v>
       </c>
       <c r="P184" s="16" t="n">
-        <v>0.0417821587464446</v>
+        <v>0.0417818800373488</v>
       </c>
       <c r="Q184" s="17" t="n">
-        <v>0.00330058284266843</v>
+        <v>0.00329077803259881</v>
       </c>
       <c r="R184" s="18" t="n">
-        <v>1.00175398141763</v>
+        <v>1.00175364526717</v>
       </c>
       <c r="S184" s="19" t="n">
-        <v>1.01431197975327</v>
+        <v>1.01430310680565</v>
       </c>
     </row>
     <row r="185">
@@ -12736,46 +12736,46 @@
         <v>703681.544169008</v>
       </c>
       <c r="F185" s="6" t="n">
-        <v>-13961.6554937205</v>
+        <v>-13963.2215664077</v>
       </c>
       <c r="G185" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>718178.019065748</v>
+        <v>718177.91565239</v>
       </c>
       <c r="I185" s="9" t="n">
-        <v>714815.660889185</v>
+        <v>714820.51085831</v>
       </c>
       <c r="J185" s="10" t="n">
-        <v>715777.594201384</v>
+        <v>715780.313259438</v>
       </c>
       <c r="K185" s="11" t="n">
-        <v>717643.199662729</v>
+        <v>717644.765735416</v>
       </c>
       <c r="L185" s="12" t="n">
-        <v>717643.199662729</v>
+        <v>717644.765735416</v>
       </c>
       <c r="M185" s="13" t="n">
-        <v>717643.199662729</v>
+        <v>717644.765735416</v>
       </c>
       <c r="N185" s="14" t="n">
-        <v>717643.199662729</v>
+        <v>717644.765735416</v>
       </c>
       <c r="O185" s="15" t="n">
-        <v>-0.0112040513393454</v>
+        <v>-0.0112033783991928</v>
       </c>
       <c r="P185" s="16" t="n">
-        <v>0.02491557870193</v>
+        <v>0.0249145135761464</v>
       </c>
       <c r="Q185" s="17" t="n">
-        <v>-0.011141519709883</v>
+        <v>-0.0111408542670824</v>
       </c>
       <c r="R185" s="18" t="n">
-        <v>0.999255310815952</v>
+        <v>0.999257635322175</v>
       </c>
       <c r="S185" s="19" t="n">
-        <v>1.00395561950899</v>
+        <v>1.00395099865519</v>
       </c>
     </row>
     <row r="186">
@@ -12795,46 +12795,46 @@
         <v>677652.089115703</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>-32423.6628994577</v>
+        <v>-32420.5891983173</v>
       </c>
       <c r="G186" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H186" s="8" t="n">
-        <v>710866.358617014</v>
+        <v>710865.217481718</v>
       </c>
       <c r="I186" s="9" t="n">
-        <v>713966.428473824</v>
+        <v>713968.078535124</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>715905.139140877</v>
+        <v>715907.979548238</v>
       </c>
       <c r="K186" s="11" t="n">
-        <v>710075.75201516</v>
+        <v>710072.67831402</v>
       </c>
       <c r="L186" s="12" t="n">
-        <v>710075.75201516</v>
+        <v>710072.67831402</v>
       </c>
       <c r="M186" s="13" t="n">
-        <v>710075.75201516</v>
+        <v>710072.67831402</v>
       </c>
       <c r="N186" s="14" t="n">
-        <v>710075.75201516</v>
+        <v>710072.67831402</v>
       </c>
       <c r="O186" s="15" t="n">
-        <v>-0.0106008518083551</v>
+        <v>-0.0106073627542054</v>
       </c>
       <c r="P186" s="16" t="n">
-        <v>-0.00418603117649752</v>
+        <v>-0.00422195625296162</v>
       </c>
       <c r="Q186" s="17" t="n">
-        <v>-0.0105448608042613</v>
+        <v>-0.0105513030721213</v>
       </c>
       <c r="R186" s="18" t="n">
-        <v>0.998887826674775</v>
+        <v>0.998885106278648</v>
       </c>
       <c r="S186" s="19" t="n">
-        <v>0.994550617082962</v>
+        <v>0.994544013467526</v>
       </c>
     </row>
     <row r="187">
@@ -12854,46 +12854,46 @@
         <v>760703.280151656</v>
       </c>
       <c r="F187" s="6" t="n">
-        <v>53452.1960103145</v>
+        <v>53451.5387966492</v>
       </c>
       <c r="G187" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>706020.915662084</v>
+        <v>706020.110042293</v>
       </c>
       <c r="I187" s="9" t="n">
-        <v>712950.838688359</v>
+        <v>712948.499557293</v>
       </c>
       <c r="J187" s="10" t="n">
-        <v>715971.83777684</v>
+        <v>715974.972090913</v>
       </c>
       <c r="K187" s="11" t="n">
-        <v>707251.084141342</v>
+        <v>707251.741355007</v>
       </c>
       <c r="L187" s="12" t="n">
-        <v>707251.084141342</v>
+        <v>707251.741355007</v>
       </c>
       <c r="M187" s="13" t="n">
-        <v>707251.084141342</v>
+        <v>707251.741355007</v>
       </c>
       <c r="N187" s="14" t="n">
-        <v>707251.084141342</v>
+        <v>707251.741355007</v>
       </c>
       <c r="O187" s="15" t="n">
-        <v>-0.00398591424575426</v>
+        <v>-0.00398065629128082</v>
       </c>
       <c r="P187" s="16" t="n">
-        <v>-0.0222445286639292</v>
+        <v>-0.0222546509755444</v>
       </c>
       <c r="Q187" s="17" t="n">
-        <v>-0.00397798103343516</v>
+        <v>-0.00397274398123681</v>
       </c>
       <c r="R187" s="18" t="n">
-        <v>1.00174239665139</v>
+        <v>1.00174447058263</v>
       </c>
       <c r="S187" s="19" t="n">
-        <v>0.992005403124985</v>
+        <v>0.992009579645903</v>
       </c>
     </row>
     <row r="188">
@@ -12913,46 +12913,46 @@
         <v>694382.47577623</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>-8243.91563082002</v>
+        <v>-8243.83593214328</v>
       </c>
       <c r="G188" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H188" s="8" t="n">
-        <v>703937.925411706</v>
+        <v>703938.879751923</v>
       </c>
       <c r="I188" s="9" t="n">
-        <v>711776.135122386</v>
+        <v>711768.936283272</v>
       </c>
       <c r="J188" s="10" t="n">
-        <v>715954.304408786</v>
+        <v>715957.948154874</v>
       </c>
       <c r="K188" s="11" t="n">
-        <v>702626.39140705</v>
+        <v>702626.311708374</v>
       </c>
       <c r="L188" s="12" t="n">
-        <v>702626.39140705</v>
+        <v>702626.311708374</v>
       </c>
       <c r="M188" s="13" t="n">
-        <v>702626.39140705</v>
+        <v>702626.311708374</v>
       </c>
       <c r="N188" s="14" t="n">
-        <v>702626.39140705</v>
+        <v>702626.311708374</v>
       </c>
       <c r="O188" s="15" t="n">
-        <v>-0.00656044145889723</v>
+        <v>-0.00656148413897943</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>-0.0318335546897961</v>
+        <v>-0.0318351257625221</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>-0.00653896874531645</v>
+        <v>-0.00654000460680615</v>
       </c>
       <c r="R188" s="18" t="n">
-        <v>0.998136861280931</v>
+        <v>0.998135394874038</v>
       </c>
       <c r="S188" s="19" t="n">
-        <v>0.987145194585989</v>
+        <v>0.987155066611027</v>
       </c>
     </row>
     <row r="189">
@@ -12972,46 +12972,46 @@
         <v>693173.549347058</v>
       </c>
       <c r="F189" s="6" t="n">
-        <v>-13239.0429294613</v>
+        <v>-13240.8423740206</v>
       </c>
       <c r="G189" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H189" s="8" t="n">
-        <v>704954.833303221</v>
+        <v>704955.593645882</v>
       </c>
       <c r="I189" s="9" t="n">
-        <v>710445.999018906</v>
+        <v>710432.990597642</v>
       </c>
       <c r="J189" s="10" t="n">
-        <v>715785.549568048</v>
+        <v>715789.948853852</v>
       </c>
       <c r="K189" s="11" t="n">
-        <v>706412.592276519</v>
+        <v>706414.391721078</v>
       </c>
       <c r="L189" s="12" t="n">
-        <v>706412.592276519</v>
+        <v>706414.391721078</v>
       </c>
       <c r="M189" s="13" t="n">
-        <v>706412.592276519</v>
+        <v>706414.391721078</v>
       </c>
       <c r="N189" s="14" t="n">
-        <v>706412.592276519</v>
+        <v>706414.391721078</v>
       </c>
       <c r="O189" s="15" t="n">
-        <v>0.00537417349836396</v>
+        <v>0.00537683422445635</v>
       </c>
       <c r="P189" s="16" t="n">
-        <v>-0.0156492911679335</v>
+        <v>-0.0156489318260808</v>
       </c>
       <c r="Q189" s="17" t="n">
-        <v>0.00538864027280073</v>
+        <v>0.0053913153401477</v>
       </c>
       <c r="R189" s="18" t="n">
-        <v>1.00206787570555</v>
+        <v>1.00206934747145</v>
       </c>
       <c r="S189" s="19" t="n">
-        <v>0.994322711721994</v>
+        <v>0.994343451205464</v>
       </c>
     </row>
     <row r="190">
@@ -13031,46 +13031,46 @@
         <v>681444.766110222</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>-29513.9950403516</v>
+        <v>-29513.2909415149</v>
       </c>
       <c r="G190" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H190" s="8" t="n">
-        <v>713981.579233139</v>
+        <v>713981.756345587</v>
       </c>
       <c r="I190" s="9" t="n">
-        <v>708958.3930311</v>
+        <v>708938.550244621</v>
       </c>
       <c r="J190" s="10" t="n">
-        <v>715331.944220953</v>
+        <v>715337.357119349</v>
       </c>
       <c r="K190" s="11" t="n">
-        <v>710958.761150574</v>
+        <v>710958.057051737</v>
       </c>
       <c r="L190" s="12" t="n">
-        <v>710958.761150574</v>
+        <v>710958.057051737</v>
       </c>
       <c r="M190" s="13" t="n">
-        <v>710958.761150574</v>
+        <v>710958.057051737</v>
       </c>
       <c r="N190" s="14" t="n">
-        <v>710958.761150574</v>
+        <v>710958.057051737</v>
       </c>
       <c r="O190" s="15" t="n">
-        <v>0.00641495180953307</v>
+        <v>0.00641141416145845</v>
       </c>
       <c r="P190" s="16" t="n">
-        <v>0.001243542161393</v>
+        <v>0.00124688467076295</v>
       </c>
       <c r="Q190" s="17" t="n">
-        <v>0.00643557168113928</v>
+        <v>0.00643201127257464</v>
       </c>
       <c r="R190" s="18" t="n">
-        <v>0.995766252000771</v>
+        <v>0.995765018829996</v>
       </c>
       <c r="S190" s="19" t="n">
-        <v>1.00282155926093</v>
+        <v>1.00284863449226</v>
       </c>
     </row>
     <row r="191">
@@ -13090,46 +13090,46 @@
         <v>778401.676449317</v>
       </c>
       <c r="F191" s="6" t="n">
-        <v>49934.4151448394</v>
+        <v>49934.8526376698</v>
       </c>
       <c r="G191" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H191" s="8" t="n">
-        <v>724847.704574438</v>
+        <v>724846.48052022</v>
       </c>
       <c r="I191" s="9" t="n">
-        <v>707308.758932935</v>
+        <v>707280.991344133</v>
       </c>
       <c r="J191" s="10" t="n">
-        <v>714412.994547368</v>
+        <v>714419.6780972</v>
       </c>
       <c r="K191" s="11" t="n">
-        <v>728467.261304477</v>
+        <v>728466.823811647</v>
       </c>
       <c r="L191" s="12" t="n">
-        <v>728467.261304477</v>
+        <v>728466.823811647</v>
       </c>
       <c r="M191" s="13" t="n">
-        <v>728467.261304477</v>
+        <v>728466.823811647</v>
       </c>
       <c r="N191" s="14" t="n">
-        <v>728467.261304477</v>
+        <v>728466.823811647</v>
       </c>
       <c r="O191" s="15" t="n">
-        <v>0.0243282578287059</v>
+        <v>0.024328647613959</v>
       </c>
       <c r="P191" s="16" t="n">
-        <v>0.029998083621029</v>
+        <v>0.02999650791385</v>
       </c>
       <c r="Q191" s="17" t="n">
-        <v>0.0246266043976564</v>
+        <v>0.0246270037820746</v>
       </c>
       <c r="R191" s="18" t="n">
-        <v>1.00499354099792</v>
+        <v>1.00499463457259</v>
       </c>
       <c r="S191" s="19" t="n">
-        <v>1.02991409636078</v>
+        <v>1.02995391184945</v>
       </c>
     </row>
     <row r="192">
@@ -13149,46 +13149,46 @@
         <v>721120.426852794</v>
       </c>
       <c r="F192" s="6" t="n">
-        <v>-8852.12575052391</v>
+        <v>-8849.87659069549</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H192" s="8" t="n">
-        <v>732342.325220361</v>
+        <v>732340.112414805</v>
       </c>
       <c r="I192" s="9" t="n">
-        <v>705493.788728452</v>
+        <v>705456.952207853</v>
       </c>
       <c r="J192" s="10" t="n">
-        <v>712826.340811809</v>
+        <v>712834.520432902</v>
       </c>
       <c r="K192" s="11" t="n">
-        <v>729972.552603318</v>
+        <v>729970.30344349</v>
       </c>
       <c r="L192" s="12" t="n">
-        <v>729972.552603318</v>
+        <v>729970.30344349</v>
       </c>
       <c r="M192" s="13" t="n">
-        <v>729972.552603318</v>
+        <v>729970.30344349</v>
       </c>
       <c r="N192" s="14" t="n">
-        <v>729972.552603318</v>
+        <v>729970.30344349</v>
       </c>
       <c r="O192" s="15" t="n">
-        <v>0.00206424950691245</v>
+        <v>0.00206176891185745</v>
       </c>
       <c r="P192" s="16" t="n">
-        <v>0.0389199175133534</v>
+        <v>0.0389168342822679</v>
       </c>
       <c r="Q192" s="17" t="n">
-        <v>0.00206638153668726</v>
+        <v>0.00206389581885946</v>
       </c>
       <c r="R192" s="18" t="n">
-        <v>0.996764118998134</v>
+        <v>0.996764059579502</v>
       </c>
       <c r="S192" s="19" t="n">
-        <v>1.03469734853227</v>
+        <v>1.03474818861579</v>
       </c>
     </row>
     <row r="193">
@@ -13208,46 +13208,46 @@
         <v>724592.921638963</v>
       </c>
       <c r="F193" s="6" t="n">
-        <v>-11211.0887394704</v>
+        <v>-11210.8134342232</v>
       </c>
       <c r="G193" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>736532.778154151</v>
+        <v>736535.844268072</v>
       </c>
       <c r="I193" s="9" t="n">
-        <v>703523.398485676</v>
+        <v>703476.312292751</v>
       </c>
       <c r="J193" s="10" t="n">
-        <v>710439.894612577</v>
+        <v>710449.728500527</v>
       </c>
       <c r="K193" s="11" t="n">
-        <v>735804.010378433</v>
+        <v>735803.735073186</v>
       </c>
       <c r="L193" s="12" t="n">
-        <v>735804.010378433</v>
+        <v>735803.735073186</v>
       </c>
       <c r="M193" s="13" t="n">
-        <v>735804.010378433</v>
+        <v>735803.735073186</v>
       </c>
       <c r="N193" s="14" t="n">
-        <v>735804.010378433</v>
+        <v>735803.735073186</v>
       </c>
       <c r="O193" s="15" t="n">
-        <v>0.00795685875860585</v>
+        <v>0.00795956576431599</v>
       </c>
       <c r="P193" s="16" t="n">
-        <v>0.0416065885903816</v>
+        <v>0.0416035455910018</v>
       </c>
       <c r="Q193" s="17" t="n">
-        <v>0.00798859868678403</v>
+        <v>0.00799132732136965</v>
       </c>
       <c r="R193" s="18" t="n">
-        <v>0.999010542643405</v>
+        <v>0.999006010093625</v>
       </c>
       <c r="S193" s="19" t="n">
-        <v>1.04588420507725</v>
+        <v>1.04595381850893</v>
       </c>
     </row>
     <row r="194">
@@ -13267,46 +13267,46 @@
         <v>707324.268057214</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>-26692.6957861179</v>
+        <v>-26703.5485410572</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H194" s="8" t="n">
-        <v>727832.806435653</v>
+        <v>727836.848345956</v>
       </c>
       <c r="I194" s="9" t="n">
-        <v>701422.80350005</v>
+        <v>701364.271900317</v>
       </c>
       <c r="J194" s="10" t="n">
-        <v>707207.298606933</v>
+        <v>707218.825589196</v>
       </c>
       <c r="K194" s="11" t="n">
-        <v>734016.963843332</v>
+        <v>734027.816598271</v>
       </c>
       <c r="L194" s="12" t="n">
-        <v>734016.963843332</v>
+        <v>734027.816598271</v>
       </c>
       <c r="M194" s="13" t="n">
-        <v>734016.963843332</v>
+        <v>734027.816598271</v>
       </c>
       <c r="N194" s="14" t="n">
-        <v>734016.963843332</v>
+        <v>734027.816598271</v>
       </c>
       <c r="O194" s="15" t="n">
-        <v>-0.00243165317001298</v>
+        <v>-0.00241649369561148</v>
       </c>
       <c r="P194" s="16" t="n">
-        <v>0.0324325459544825</v>
+        <v>0.0324488333984168</v>
       </c>
       <c r="Q194" s="17" t="n">
-        <v>-0.00242869909635601</v>
+        <v>-0.00241357632512995</v>
       </c>
       <c r="R194" s="18" t="n">
-        <v>1.00849667307244</v>
+        <v>1.00850598354066</v>
       </c>
       <c r="S194" s="19" t="n">
-        <v>1.04646863515221</v>
+        <v>1.04657144084265</v>
       </c>
     </row>
     <row r="195">
@@ -13326,46 +13326,46 @@
         <v>747428.299954575</v>
       </c>
       <c r="F195" s="6" t="n">
-        <v>44686.6807837756</v>
+        <v>44695.6840257869</v>
       </c>
       <c r="G195" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H195" s="8" t="n">
-        <v>711075.710739738</v>
+        <v>711071.796655159</v>
       </c>
       <c r="I195" s="9" t="n">
-        <v>699237.394449454</v>
+        <v>699166.235971281</v>
       </c>
       <c r="J195" s="10" t="n">
-        <v>703209.016030963</v>
+        <v>703222.105020897</v>
       </c>
       <c r="K195" s="11" t="n">
-        <v>702741.619170799</v>
+        <v>702732.615928788</v>
       </c>
       <c r="L195" s="12" t="n">
-        <v>702741.619170799</v>
+        <v>702732.615928788</v>
       </c>
       <c r="M195" s="13" t="n">
-        <v>702741.619170799</v>
+        <v>702732.615928788</v>
       </c>
       <c r="N195" s="14" t="n">
-        <v>702741.619170799</v>
+        <v>702732.615928788</v>
       </c>
       <c r="O195" s="15" t="n">
-        <v>-0.0435428558970341</v>
+        <v>-0.0435704528941769</v>
       </c>
       <c r="P195" s="16" t="n">
-        <v>-0.03531475400502</v>
+        <v>-0.0353265338127645</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>-0.0426084766607772</v>
+        <v>-0.0426348974273427</v>
       </c>
       <c r="R195" s="18" t="n">
-        <v>0.988279600268909</v>
+        <v>0.988272378730814</v>
       </c>
       <c r="S195" s="19" t="n">
-        <v>1.00501149502181</v>
+        <v>1.00510090415415</v>
       </c>
     </row>
     <row r="196">
@@ -13385,46 +13385,46 @@
         <v>696101.583521808</v>
       </c>
       <c r="F196" s="6" t="n">
-        <v>-8228.93323067837</v>
+        <v>-8221.70888926786</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H196" s="8" t="n">
-        <v>697723.919307708</v>
+        <v>697714.059536131</v>
       </c>
       <c r="I196" s="9" t="n">
-        <v>697032.933361981</v>
+        <v>696948.024161808</v>
       </c>
       <c r="J196" s="10" t="n">
-        <v>698659.558446938</v>
+        <v>698673.90507266</v>
       </c>
       <c r="K196" s="11" t="n">
-        <v>704330.516752486</v>
+        <v>704323.292411075</v>
       </c>
       <c r="L196" s="12" t="n">
-        <v>704330.516752486</v>
+        <v>704323.292411075</v>
       </c>
       <c r="M196" s="13" t="n">
-        <v>704330.516752486</v>
+        <v>704323.292411075</v>
       </c>
       <c r="N196" s="14" t="n">
-        <v>704330.516752486</v>
+        <v>704323.292411075</v>
       </c>
       <c r="O196" s="15" t="n">
-        <v>0.00225844605472546</v>
+        <v>0.00226100064752807</v>
       </c>
       <c r="P196" s="16" t="n">
-        <v>-0.0351273972690951</v>
+        <v>-0.0351343210969398</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0.00226099826499793</v>
+        <v>0.00226355863700078</v>
       </c>
       <c r="R196" s="18" t="n">
-        <v>1.00946878451771</v>
+        <v>1.00947269556147</v>
       </c>
       <c r="S196" s="19" t="n">
-        <v>1.01046949583186</v>
+        <v>1.01058223568126</v>
       </c>
     </row>
     <row r="197">
@@ -13444,46 +13444,46 @@
         <v>678655.620384454</v>
       </c>
       <c r="F197" s="6" t="n">
-        <v>-8978.18665671191</v>
+        <v>-8977.68559073107</v>
       </c>
       <c r="G197" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H197" s="8" t="n">
-        <v>690922.323040265</v>
+        <v>690930.716784974</v>
       </c>
       <c r="I197" s="9" t="n">
-        <v>694877.372406173</v>
+        <v>694777.685115536</v>
       </c>
       <c r="J197" s="10" t="n">
-        <v>693771.100432829</v>
+        <v>693786.116576057</v>
       </c>
       <c r="K197" s="11" t="n">
-        <v>687633.807041165</v>
+        <v>687633.305975185</v>
       </c>
       <c r="L197" s="12" t="n">
-        <v>687633.807041165</v>
+        <v>687633.305975185</v>
       </c>
       <c r="M197" s="13" t="n">
-        <v>687633.807041165</v>
+        <v>687633.305975185</v>
       </c>
       <c r="N197" s="14" t="n">
-        <v>687633.807041165</v>
+        <v>687633.305975185</v>
       </c>
       <c r="O197" s="15" t="n">
-        <v>-0.0239912909817322</v>
+        <v>-0.0239817625777353</v>
       </c>
       <c r="P197" s="16" t="n">
-        <v>-0.0654660788169574</v>
+        <v>-0.0654664101334171</v>
       </c>
       <c r="Q197" s="17" t="n">
-        <v>-0.0237057877149855</v>
+        <v>-0.0236964851449918</v>
       </c>
       <c r="R197" s="18" t="n">
-        <v>0.995240396945594</v>
+        <v>0.995227581102295</v>
       </c>
       <c r="S197" s="19" t="n">
-        <v>0.989575764512341</v>
+        <v>0.989717028492124</v>
       </c>
     </row>
     <row r="198">
@@ -13503,46 +13503,46 @@
         <v>665848.715299709</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>-25628.4903902221</v>
+        <v>-25658.8585007055</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H198" s="8" t="n">
-        <v>694724.624413779</v>
+        <v>694739.350625854</v>
       </c>
       <c r="I198" s="9" t="n">
-        <v>692843.224740195</v>
+        <v>692727.877018759</v>
       </c>
       <c r="J198" s="10" t="n">
-        <v>688784.171358131</v>
+        <v>688798.877299352</v>
       </c>
       <c r="K198" s="11" t="n">
-        <v>691477.205689931</v>
+        <v>691507.573800414</v>
       </c>
       <c r="L198" s="12" t="n">
-        <v>691477.205689931</v>
+        <v>691507.573800414</v>
       </c>
       <c r="M198" s="13" t="n">
-        <v>691477.205689931</v>
+        <v>691507.573800414</v>
       </c>
       <c r="N198" s="14" t="n">
-        <v>691477.205689931</v>
+        <v>691507.573800414</v>
       </c>
       <c r="O198" s="15" t="n">
-        <v>0.00557374796287231</v>
+        <v>0.00561839341203114</v>
       </c>
       <c r="P198" s="16" t="n">
-        <v>-0.0579547343574484</v>
+        <v>-0.0579272908142771</v>
       </c>
       <c r="Q198" s="17" t="n">
-        <v>0.00558931019593611</v>
+        <v>0.00563420618455246</v>
       </c>
       <c r="R198" s="18" t="n">
-        <v>0.99532560296594</v>
+        <v>0.995348216820411</v>
       </c>
       <c r="S198" s="19" t="n">
-        <v>0.998028386507242</v>
+        <v>0.998238408964288</v>
       </c>
     </row>
     <row r="199">
@@ -13562,46 +13562,46 @@
         <v>751784.460777133</v>
       </c>
       <c r="F199" s="6" t="n">
-        <v>41884.4884129887</v>
+        <v>41901.0425491517</v>
       </c>
       <c r="G199" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H199" s="8" t="n">
-        <v>703409.714450558</v>
+        <v>703400.272051581</v>
       </c>
       <c r="I199" s="9" t="n">
-        <v>690998.476293855</v>
+        <v>690866.792820809</v>
       </c>
       <c r="J199" s="10" t="n">
-        <v>683908.614125385</v>
+        <v>683921.560957802</v>
       </c>
       <c r="K199" s="11" t="n">
-        <v>709899.972364144</v>
+        <v>709883.418227981</v>
       </c>
       <c r="L199" s="12" t="n">
-        <v>709899.972364144</v>
+        <v>709883.418227981</v>
       </c>
       <c r="M199" s="13" t="n">
-        <v>709899.972364144</v>
+        <v>709883.418227981</v>
       </c>
       <c r="N199" s="14" t="n">
-        <v>709899.972364144</v>
+        <v>709883.418227981</v>
       </c>
       <c r="O199" s="15" t="n">
-        <v>0.026293889126658</v>
+        <v>0.0262266531172894</v>
       </c>
       <c r="P199" s="16" t="n">
-        <v>0.0101863231066226</v>
+        <v>0.0101757085655434</v>
       </c>
       <c r="Q199" s="17" t="n">
-        <v>0.0266426232457386</v>
+        <v>0.0265735982132138</v>
       </c>
       <c r="R199" s="18" t="n">
-        <v>1.0092268528288</v>
+        <v>1.00921686617705</v>
       </c>
       <c r="S199" s="19" t="n">
-        <v>1.02735388965207</v>
+        <v>1.02752574824088</v>
       </c>
     </row>
     <row r="200">
@@ -13621,46 +13621,46 @@
         <v>683900.898552578</v>
       </c>
       <c r="F200" s="6" t="n">
-        <v>-8813.71793751895</v>
+        <v>-8783.54056673381</v>
       </c>
       <c r="G200" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H200" s="8" t="n">
-        <v>697796.71768964</v>
+        <v>697774.332607534</v>
       </c>
       <c r="I200" s="9" t="n">
-        <v>689410.259235056</v>
+        <v>689261.862781506</v>
       </c>
       <c r="J200" s="10" t="n">
-        <v>679367.736808788</v>
+        <v>679377.084749174</v>
       </c>
       <c r="K200" s="11" t="n">
-        <v>692714.616490097</v>
+        <v>692684.439119312</v>
       </c>
       <c r="L200" s="12" t="n">
-        <v>692714.616490097</v>
+        <v>692684.439119312</v>
       </c>
       <c r="M200" s="13" t="n">
-        <v>692714.616490097</v>
+        <v>692684.439119312</v>
       </c>
       <c r="N200" s="14" t="n">
-        <v>692714.616490097</v>
+        <v>692684.439119312</v>
       </c>
       <c r="O200" s="15" t="n">
-        <v>-0.0245059705593474</v>
+        <v>-0.0245262161959846</v>
       </c>
       <c r="P200" s="16" t="n">
-        <v>-0.0164921155424969</v>
+        <v>-0.0165248734738284</v>
       </c>
       <c r="Q200" s="17" t="n">
-        <v>-0.024208137122213</v>
+        <v>-0.0242278924497221</v>
       </c>
       <c r="R200" s="18" t="n">
-        <v>0.992716931635378</v>
+        <v>0.992705530641689</v>
       </c>
       <c r="S200" s="19" t="n">
-        <v>1.00479302013682</v>
+        <v>1.00496556754786</v>
       </c>
     </row>
     <row r="201">
@@ -13680,46 +13680,46 @@
         <v>671361.13972242</v>
       </c>
       <c r="F201" s="6" t="n">
-        <v>-6763.63935669318</v>
+        <v>-6767.373111051</v>
       </c>
       <c r="G201" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H201" s="8" t="n">
-        <v>672614.057325446</v>
+        <v>672600.588090637</v>
       </c>
       <c r="I201" s="9" t="n">
-        <v>688157.519166746</v>
+        <v>687992.402551549</v>
       </c>
       <c r="J201" s="10" t="n">
-        <v>675514.804273732</v>
+        <v>675518.17515758</v>
       </c>
       <c r="K201" s="11" t="n">
-        <v>678124.779079113</v>
+        <v>678128.512833471</v>
       </c>
       <c r="L201" s="12" t="n">
-        <v>678124.779079113</v>
+        <v>678128.512833471</v>
       </c>
       <c r="M201" s="13" t="n">
-        <v>678124.779079113</v>
+        <v>678128.512833471</v>
       </c>
       <c r="N201" s="14" t="n">
-        <v>678124.779079113</v>
+        <v>678128.512833471</v>
       </c>
       <c r="O201" s="15" t="n">
-        <v>-0.0212867946099495</v>
+        <v>-0.0212377237475692</v>
       </c>
       <c r="P201" s="16" t="n">
-        <v>-0.013828621956458</v>
+        <v>-0.0138224734885901</v>
       </c>
       <c r="Q201" s="17" t="n">
-        <v>-0.0210618298844467</v>
+        <v>-0.021013791365586</v>
       </c>
       <c r="R201" s="18" t="n">
-        <v>1.00819299224221</v>
+        <v>1.00821873313927</v>
       </c>
       <c r="S201" s="19" t="n">
-        <v>0.985420866868125</v>
+        <v>0.985662792668209</v>
       </c>
     </row>
     <row r="202">
@@ -13739,46 +13739,46 @@
         <v>632389.35353461</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>-24784.3907514822</v>
+        <v>-24850.8676971234</v>
       </c>
       <c r="G202" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H202" s="8" t="n">
-        <v>636460.279791407</v>
+        <v>636488.428571905</v>
       </c>
       <c r="I202" s="9" t="n">
-        <v>687321.266915156</v>
+        <v>687139.866891851</v>
       </c>
       <c r="J202" s="10" t="n">
-        <v>672769.815784014</v>
+        <v>672764.095438987</v>
       </c>
       <c r="K202" s="11" t="n">
-        <v>657173.744286092</v>
+        <v>657240.221231733</v>
       </c>
       <c r="L202" s="12" t="n">
-        <v>636460.279791407</v>
+        <v>636488.428571905</v>
       </c>
       <c r="M202" s="13" t="n">
-        <v>636460.279791407</v>
+        <v>636488.428571905</v>
       </c>
       <c r="N202" s="14" t="n">
-        <v>636460.279791407</v>
+        <v>636488.428571905</v>
       </c>
       <c r="O202" s="15" t="n">
-        <v>-0.0634092989949132</v>
+        <v>-0.0633705788755111</v>
       </c>
       <c r="P202" s="16" t="n">
-        <v>-0.0795643376901051</v>
+        <v>-0.0795640529663804</v>
       </c>
       <c r="Q202" s="17" t="n">
-        <v>-0.0614407562930912</v>
+        <v>-0.0614044144635335</v>
       </c>
       <c r="R202" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S202" s="19" t="n">
-        <v>0.926001144483679</v>
+        <v>0.926286567319899</v>
       </c>
     </row>
     <row r="203">
@@ -13798,46 +13798,46 @@
         <v>609379.989464801</v>
       </c>
       <c r="F203" s="6" t="n">
-        <v>39300.5771761554</v>
+        <v>39320.3322625516</v>
       </c>
       <c r="G203" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H203" s="8" t="n">
-        <v>611652.189635686</v>
+        <v>611680.291094477</v>
       </c>
       <c r="I203" s="9" t="n">
-        <v>686976.242843964</v>
+        <v>686779.545632247</v>
       </c>
       <c r="J203" s="10" t="n">
-        <v>671565.820477461</v>
+        <v>671547.160537741</v>
       </c>
       <c r="K203" s="11" t="n">
-        <v>570079.412288646</v>
+        <v>570059.65720225</v>
       </c>
       <c r="L203" s="12" t="n">
-        <v>611652.189635686</v>
+        <v>611680.291094477</v>
       </c>
       <c r="M203" s="13" t="n">
-        <v>611652.189635686</v>
+        <v>611680.291094477</v>
       </c>
       <c r="N203" s="14" t="n">
-        <v>611652.189635686</v>
+        <v>611680.291094477</v>
       </c>
       <c r="O203" s="15" t="n">
-        <v>-0.0397582085819804</v>
+        <v>-0.03975649221376</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.138396656646243</v>
+        <v>-0.138336978455758</v>
       </c>
       <c r="Q203" s="17" t="n">
-        <v>-0.0389782221191425</v>
+        <v>-0.0389765726504883</v>
       </c>
       <c r="R203" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S203" s="19" t="n">
-        <v>0.89035420948991</v>
+        <v>0.890650129265813</v>
       </c>
     </row>
     <row r="204">
@@ -13857,46 +13857,46 @@
         <v>614192.478404223</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>-7598.16575635988</v>
+        <v>-7532.38105469857</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H204" s="8" t="n">
-        <v>620878.041995616</v>
+        <v>620829.500079206</v>
       </c>
       <c r="I204" s="9" t="n">
-        <v>687165.399199893</v>
+        <v>686955.071453624</v>
       </c>
       <c r="J204" s="10" t="n">
-        <v>672154.319811935</v>
+        <v>672118.307063851</v>
       </c>
       <c r="K204" s="11" t="n">
-        <v>621790.644160583</v>
+        <v>621724.859458921</v>
       </c>
       <c r="L204" s="12" t="n">
-        <v>621790.644160583</v>
+        <v>621724.859458921</v>
       </c>
       <c r="M204" s="13" t="n">
-        <v>621790.644160583</v>
+        <v>621724.859458921</v>
       </c>
       <c r="N204" s="14" t="n">
-        <v>621790.644160583</v>
+        <v>621724.859458921</v>
       </c>
       <c r="O204" s="15" t="n">
-        <v>0.0164396477609948</v>
+        <v>0.016287900896206</v>
       </c>
       <c r="P204" s="16" t="n">
-        <v>-0.102385557690233</v>
+        <v>-0.102441423039053</v>
       </c>
       <c r="Q204" s="17" t="n">
-        <v>0.0165755223257444</v>
+        <v>0.0164212718812171</v>
       </c>
       <c r="R204" s="18" t="n">
-        <v>1.0014698573685</v>
+        <v>1.00144219850958</v>
       </c>
       <c r="S204" s="19" t="n">
-        <v>0.904863144862314</v>
+        <v>0.905044427641137</v>
       </c>
     </row>
     <row r="205">
@@ -13916,46 +13916,46 @@
         <v>642403.32319795</v>
       </c>
       <c r="F205" s="6" t="n">
-        <v>-7423.68010888921</v>
+        <v>-7363.59640730025</v>
       </c>
       <c r="G205" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H205" s="8" t="n">
-        <v>650054.934010711</v>
+        <v>650078.33746814</v>
       </c>
       <c r="I205" s="9" t="n">
-        <v>687884.610696413</v>
+        <v>687663.140002783</v>
       </c>
       <c r="J205" s="10" t="n">
-        <v>674487.247091088</v>
+        <v>674429.13728011</v>
       </c>
       <c r="K205" s="11" t="n">
-        <v>649827.003306839</v>
+        <v>649766.91960525</v>
       </c>
       <c r="L205" s="12" t="n">
-        <v>649827.003306839</v>
+        <v>649766.91960525</v>
       </c>
       <c r="M205" s="13" t="n">
-        <v>649827.003306839</v>
+        <v>649766.91960525</v>
       </c>
       <c r="N205" s="14" t="n">
-        <v>649827.003306839</v>
+        <v>649766.91960525</v>
       </c>
       <c r="O205" s="15" t="n">
-        <v>0.0441027275761884</v>
+        <v>0.0441160666223378</v>
       </c>
       <c r="P205" s="16" t="n">
-        <v>-0.0417294525215577</v>
+        <v>-0.0418233309637953</v>
       </c>
       <c r="Q205" s="17" t="n">
-        <v>0.0450897089069358</v>
+        <v>0.0451036494997701</v>
       </c>
       <c r="R205" s="18" t="n">
-        <v>0.999649367012007</v>
+        <v>0.999520953329867</v>
       </c>
       <c r="S205" s="19" t="n">
-        <v>0.944674431150532</v>
+        <v>0.944891301870013</v>
       </c>
     </row>
     <row r="206">
@@ -13975,46 +13975,46 @@
         <v>652831.976706322</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>-24014.1918165623</v>
+        <v>-24264.0222753548</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H206" s="8" t="n">
-        <v>674060.67177802</v>
+        <v>674160.702799693</v>
       </c>
       <c r="I206" s="9" t="n">
-        <v>689088.892825094</v>
+        <v>688859.678044029</v>
       </c>
       <c r="J206" s="10" t="n">
-        <v>678264.717240317</v>
+        <v>678179.286211288</v>
       </c>
       <c r="K206" s="11" t="n">
-        <v>676846.168522884</v>
+        <v>677095.998981676</v>
       </c>
       <c r="L206" s="12" t="n">
-        <v>676846.168522884</v>
+        <v>677095.998981676</v>
       </c>
       <c r="M206" s="13" t="n">
-        <v>676846.168522884</v>
+        <v>677095.998981676</v>
       </c>
       <c r="N206" s="14" t="n">
-        <v>676846.168522884</v>
+        <v>677095.998981676</v>
       </c>
       <c r="O206" s="15" t="n">
-        <v>0.0407378431609129</v>
+        <v>0.0411993500633648</v>
       </c>
       <c r="P206" s="16" t="n">
-        <v>0.0634539028024073</v>
+        <v>0.0637993851685301</v>
       </c>
       <c r="Q206" s="17" t="n">
-        <v>0.0415790126888376</v>
+        <v>0.042059819531947</v>
       </c>
       <c r="R206" s="18" t="n">
-        <v>1.00413241249859</v>
+        <v>1.00435400071495</v>
       </c>
       <c r="S206" s="19" t="n">
-        <v>0.982233461561079</v>
+        <v>0.982922967569019</v>
       </c>
     </row>
     <row r="207">
@@ -14034,46 +14034,46 @@
         <v>723516.622490675</v>
       </c>
       <c r="F207" s="6" t="n">
-        <v>38779.0834122693</v>
+        <v>38900.3083697183</v>
       </c>
       <c r="G207" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H207" s="8" t="n">
-        <v>686049.83016221</v>
+        <v>686030.485925913</v>
       </c>
       <c r="I207" s="9" t="n">
-        <v>690709.475072887</v>
+        <v>690476.927203918</v>
       </c>
       <c r="J207" s="10" t="n">
-        <v>683063.543966098</v>
+        <v>682945.077793779</v>
       </c>
       <c r="K207" s="11" t="n">
-        <v>684737.539078406</v>
+        <v>684616.314120957</v>
       </c>
       <c r="L207" s="12" t="n">
-        <v>684737.539078406</v>
+        <v>684616.314120957</v>
       </c>
       <c r="M207" s="13" t="n">
-        <v>684737.539078406</v>
+        <v>684616.314120957</v>
       </c>
       <c r="N207" s="14" t="n">
-        <v>684737.539078406</v>
+        <v>684616.314120957</v>
       </c>
       <c r="O207" s="15" t="n">
-        <v>0.011591588341649</v>
+        <v>0.0110454925392393</v>
       </c>
       <c r="P207" s="16" t="n">
-        <v>0.119488412992114</v>
+        <v>0.119238798582141</v>
       </c>
       <c r="Q207" s="17" t="n">
-        <v>0.0116590311395919</v>
+        <v>0.0111067192105556</v>
       </c>
       <c r="R207" s="18" t="n">
-        <v>0.998087178181366</v>
+        <v>0.997938616673794</v>
       </c>
       <c r="S207" s="19" t="n">
-        <v>0.991353910421091</v>
+        <v>0.99151222459135</v>
       </c>
     </row>
     <row r="208">
@@ -14093,46 +14093,46 @@
         <v>686756.467826674</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>-6569.85922742374</v>
+        <v>-6451.55220761719</v>
       </c>
       <c r="G208" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H208" s="8" t="n">
-        <v>693253.840382607</v>
+        <v>693078.765057151</v>
       </c>
       <c r="I208" s="9" t="n">
-        <v>692669.935224054</v>
+        <v>692439.77680959</v>
       </c>
       <c r="J208" s="10" t="n">
-        <v>688453.448231319</v>
+        <v>688297.419527829</v>
       </c>
       <c r="K208" s="11" t="n">
-        <v>693326.327054098</v>
+        <v>693208.020034291</v>
       </c>
       <c r="L208" s="12" t="n">
-        <v>693326.327054098</v>
+        <v>693208.020034291</v>
       </c>
       <c r="M208" s="13" t="n">
-        <v>693326.327054098</v>
+        <v>693208.020034291</v>
       </c>
       <c r="N208" s="14" t="n">
-        <v>693326.327054098</v>
+        <v>693208.020034291</v>
       </c>
       <c r="O208" s="15" t="n">
-        <v>0.0124651685560905</v>
+        <v>0.0124715713940539</v>
       </c>
       <c r="P208" s="16" t="n">
-        <v>0.115047859863006</v>
+        <v>0.114975554681183</v>
       </c>
       <c r="Q208" s="17" t="n">
-        <v>0.0125431825853335</v>
+        <v>0.0125496657560178</v>
       </c>
       <c r="R208" s="18" t="n">
-        <v>1.00010456007204</v>
+        <v>1.00018649392199</v>
       </c>
       <c r="S208" s="19" t="n">
-        <v>1.00094762569684</v>
+        <v>1.00110947298297</v>
       </c>
     </row>
     <row r="209">
@@ -14152,46 +14152,46 @@
         <v>696134.669112115</v>
       </c>
       <c r="F209" s="6" t="n">
-        <v>-8430.92065816327</v>
+        <v>-8356.92946754972</v>
       </c>
       <c r="G209" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H209" s="8" t="n">
-        <v>704712.695102046</v>
+        <v>704798.643435543</v>
       </c>
       <c r="I209" s="9" t="n">
-        <v>694890.11860286</v>
+        <v>694669.453305011</v>
       </c>
       <c r="J209" s="10" t="n">
-        <v>694012.520974429</v>
+        <v>693815.575095322</v>
       </c>
       <c r="K209" s="11" t="n">
-        <v>704565.589770278</v>
+        <v>704491.598579665</v>
       </c>
       <c r="L209" s="12" t="n">
-        <v>704565.589770278</v>
+        <v>704491.598579665</v>
       </c>
       <c r="M209" s="13" t="n">
-        <v>704565.589770278</v>
+        <v>704491.598579665</v>
       </c>
       <c r="N209" s="14" t="n">
-        <v>704565.589770278</v>
+        <v>704491.598579665</v>
       </c>
       <c r="O209" s="15" t="n">
-        <v>0.0160806494036712</v>
+        <v>0.0161462785450492</v>
       </c>
       <c r="P209" s="16" t="n">
-        <v>0.0842356291518898</v>
+        <v>0.0842220145766437</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>0.0162106388833312</v>
+        <v>0.0162773341035714</v>
       </c>
       <c r="R209" s="18" t="n">
-        <v>0.999791254886154</v>
+        <v>0.999564350955073</v>
       </c>
       <c r="S209" s="19" t="n">
-        <v>1.0139237426298</v>
+        <v>1.01413930787934</v>
       </c>
     </row>
     <row r="210">
@@ -14211,46 +14211,46 @@
         <v>697625.284666358</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>-23770.2993116839</v>
+        <v>-24222.5766373811</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H210" s="8" t="n">
-        <v>724249.319584369</v>
+        <v>724422.805362892</v>
       </c>
       <c r="I210" s="9" t="n">
-        <v>697290.280778465</v>
+        <v>697087.663286161</v>
       </c>
       <c r="J210" s="10" t="n">
-        <v>699343.217527992</v>
+        <v>699103.36118067</v>
       </c>
       <c r="K210" s="11" t="n">
-        <v>721395.583978042</v>
+        <v>721847.861303739</v>
       </c>
       <c r="L210" s="12" t="n">
-        <v>721395.583978042</v>
+        <v>721847.861303739</v>
       </c>
       <c r="M210" s="13" t="n">
-        <v>721395.583978042</v>
+        <v>721847.861303739</v>
       </c>
       <c r="N210" s="14" t="n">
-        <v>721395.583978042</v>
+        <v>721847.861303739</v>
       </c>
       <c r="O210" s="15" t="n">
-        <v>0.023606218820281</v>
+        <v>0.0243379923710642</v>
       </c>
       <c r="P210" s="16" t="n">
-        <v>0.0658191144856157</v>
+        <v>0.0660938218352607</v>
       </c>
       <c r="Q210" s="17" t="n">
-        <v>0.0238870510455258</v>
+        <v>0.024636578717286</v>
       </c>
       <c r="R210" s="18" t="n">
-        <v>0.996059733120682</v>
+        <v>0.996445523194341</v>
       </c>
       <c r="S210" s="19" t="n">
-        <v>1.03456996872617</v>
+        <v>1.03551948961606</v>
       </c>
     </row>
     <row r="211">
@@ -14270,46 +14270,46 @@
         <v>782338.628533735</v>
       </c>
       <c r="F211" s="6" t="n">
-        <v>37585.4966236147</v>
+        <v>37862.667293942</v>
       </c>
       <c r="G211" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H211" s="8" t="n">
-        <v>740118.467724703</v>
+        <v>740041.865749016</v>
       </c>
       <c r="I211" s="9" t="n">
-        <v>699796.72448951</v>
+        <v>699622.252189817</v>
       </c>
       <c r="J211" s="10" t="n">
-        <v>704100.75856855</v>
+        <v>703817.974585712</v>
       </c>
       <c r="K211" s="11" t="n">
-        <v>744753.13191012</v>
+        <v>744475.961239793</v>
       </c>
       <c r="L211" s="12" t="n">
-        <v>744753.13191012</v>
+        <v>744475.961239793</v>
       </c>
       <c r="M211" s="13" t="n">
-        <v>744753.13191012</v>
+        <v>744475.961239793</v>
       </c>
       <c r="N211" s="14" t="n">
-        <v>744753.13191012</v>
+        <v>744475.961239793</v>
       </c>
       <c r="O211" s="15" t="n">
-        <v>0.0318651499122189</v>
+        <v>0.0308661648677392</v>
       </c>
       <c r="P211" s="16" t="n">
-        <v>0.087647586712553</v>
+        <v>0.0874353209004317</v>
       </c>
       <c r="Q211" s="17" t="n">
-        <v>0.0323782796164016</v>
+        <v>0.0313474641251759</v>
       </c>
       <c r="R211" s="18" t="n">
-        <v>1.00626205720777</v>
+        <v>1.00599168195206</v>
       </c>
       <c r="S211" s="19" t="n">
-        <v>1.06424209466457</v>
+        <v>1.06411132423188</v>
       </c>
     </row>
     <row r="212">
@@ -14329,46 +14329,46 @@
         <v>732662.163875501</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>-4047.73080899796</v>
+        <v>-3844.60178761598</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H212" s="8" t="n">
-        <v>736715.669667693</v>
+        <v>736601.93470848</v>
       </c>
       <c r="I212" s="9" t="n">
-        <v>702350.818289131</v>
+        <v>702216.540576517</v>
       </c>
       <c r="J212" s="10" t="n">
-        <v>708050.626604898</v>
+        <v>707730.334612898</v>
       </c>
       <c r="K212" s="11" t="n">
-        <v>736709.894684499</v>
+        <v>736506.765663117</v>
       </c>
       <c r="L212" s="12" t="n">
-        <v>736709.894684499</v>
+        <v>736506.765663117</v>
       </c>
       <c r="M212" s="13" t="n">
-        <v>736709.894684499</v>
+        <v>736506.765663117</v>
       </c>
       <c r="N212" s="14" t="n">
-        <v>736709.894684499</v>
+        <v>736506.765663117</v>
       </c>
       <c r="O212" s="15" t="n">
-        <v>-0.0108586122126863</v>
+        <v>-0.0107621410435435</v>
       </c>
       <c r="P212" s="16" t="n">
-        <v>0.0625730856272766</v>
+        <v>0.0624614031826751</v>
       </c>
       <c r="Q212" s="17" t="n">
-        <v>-0.0107998702939215</v>
+        <v>-0.0107044363976568</v>
       </c>
       <c r="R212" s="18" t="n">
-        <v>0.999992161177736</v>
+        <v>0.99987079989764</v>
       </c>
       <c r="S212" s="19" t="n">
-        <v>1.04892010587966</v>
+        <v>1.04883141182982</v>
       </c>
     </row>
     <row r="213">
@@ -14388,46 +14388,46 @@
         <v>712740.457828738</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>-9716.78782991864</v>
+        <v>-9718.84165656306</v>
       </c>
       <c r="G213" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H213" s="8" t="n">
-        <v>726702.901032187</v>
+        <v>726196.776750968</v>
       </c>
       <c r="I213" s="9" t="n">
-        <v>704922.028485107</v>
+        <v>704841.882574955</v>
       </c>
       <c r="J213" s="10" t="n">
-        <v>711161.566012534</v>
+        <v>710814.65049795</v>
       </c>
       <c r="K213" s="11" t="n">
-        <v>722457.245658657</v>
+        <v>722459.299485301</v>
       </c>
       <c r="L213" s="12" t="n">
-        <v>722457.245658657</v>
+        <v>722459.299485301</v>
       </c>
       <c r="M213" s="13" t="n">
-        <v>722457.245658657</v>
+        <v>722459.299485301</v>
       </c>
       <c r="N213" s="14" t="n">
-        <v>722457.245658657</v>
+        <v>722459.299485301</v>
       </c>
       <c r="O213" s="15" t="n">
-        <v>-0.0195359420125528</v>
+        <v>-0.0192573365893897</v>
       </c>
       <c r="P213" s="16" t="n">
-        <v>0.0253938826251963</v>
+        <v>0.0255044928028405</v>
       </c>
       <c r="Q213" s="17" t="n">
-        <v>-0.0193463521104819</v>
+        <v>-0.0190730986227509</v>
       </c>
       <c r="R213" s="18" t="n">
-        <v>0.994157646312544</v>
+        <v>0.99485335464805</v>
       </c>
       <c r="S213" s="19" t="n">
-        <v>1.02487539963992</v>
+        <v>1.02499484969024</v>
       </c>
     </row>
     <row r="214">
@@ -14447,46 +14447,46 @@
         <v>704009.035177002</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>-23774.7852016269</v>
+        <v>-24465.0932651202</v>
       </c>
       <c r="G214" s="7" t="n">
-        <v>0.869053298505175</v>
+        <v>0.522557559289899</v>
       </c>
       <c r="H214" s="8" t="n">
-        <v>723218.513252464</v>
+        <v>722414.699634174</v>
       </c>
       <c r="I214" s="9" t="n">
-        <v>707501.295807962</v>
+        <v>707491.063704505</v>
       </c>
       <c r="J214" s="10" t="n">
-        <v>713545.617507359</v>
+        <v>713189.013631843</v>
       </c>
       <c r="K214" s="11" t="n">
-        <v>727783.820378629</v>
+        <v>728474.128442122</v>
       </c>
       <c r="L214" s="12" t="n">
-        <v>727186.008469146</v>
+        <v>725581.099962746</v>
       </c>
       <c r="M214" s="13" t="n">
-        <v>727186.008469146</v>
+        <v>725581.099962746</v>
       </c>
       <c r="N214" s="14" t="n">
-        <v>727186.008469146</v>
+        <v>725581.099962746</v>
       </c>
       <c r="O214" s="15" t="n">
-        <v>0.00652405972252856</v>
+        <v>0.00431176549378908</v>
       </c>
       <c r="P214" s="16" t="n">
-        <v>0.00802669799997102</v>
+        <v>0.00517178045282862</v>
       </c>
       <c r="Q214" s="17" t="n">
-        <v>0.00654538775672231</v>
+        <v>0.00432107452927633</v>
       </c>
       <c r="R214" s="18" t="n">
-        <v>1.00548588724428</v>
+        <v>1.00438307848688</v>
       </c>
       <c r="S214" s="19" t="n">
-        <v>1.02782286446374</v>
+        <v>1.02556927880265</v>
       </c>
     </row>
     <row r="215">
@@ -14506,46 +14506,46 @@
         <v>738128.411227304</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>36356.6531931205</v>
+        <v>36906.8099044793</v>
       </c>
       <c r="G215" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H215" s="8" t="n">
-        <v>720154.442326776</v>
+        <v>719773.981436848</v>
       </c>
       <c r="I215" s="9" t="n">
-        <v>710090.520498951</v>
+        <v>710167.880370109</v>
       </c>
       <c r="J215" s="10" t="n">
-        <v>715371.300203503</v>
+        <v>715029.738650486</v>
       </c>
       <c r="K215" s="11" t="n">
-        <v>701771.758034184</v>
+        <v>701221.601322825</v>
       </c>
       <c r="L215" s="12" t="n">
-        <v>720154.442326776</v>
+        <v>719773.981436848</v>
       </c>
       <c r="M215" s="13" t="n">
-        <v>720154.442326776</v>
+        <v>719773.981436848</v>
       </c>
       <c r="N215" s="14" t="n">
-        <v>720154.442326776</v>
+        <v>719773.981436848</v>
       </c>
       <c r="O215" s="15" t="n">
-        <v>-0.00971661016001555</v>
+        <v>-0.00803560294377058</v>
       </c>
       <c r="P215" s="16" t="n">
-        <v>-0.0330293200919537</v>
+        <v>-0.0331803591909245</v>
       </c>
       <c r="Q215" s="17" t="n">
-        <v>-0.00966955642776068</v>
+        <v>-0.00800340379069464</v>
       </c>
       <c r="R215" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S215" s="19" t="n">
-        <v>1.01417273085233</v>
+        <v>1.01352652144973</v>
       </c>
     </row>
     <row r="216">
@@ -14565,46 +14565,46 @@
         <v>728542.255847487</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>-2707.0112646247</v>
+        <v>-2323.58521245017</v>
       </c>
       <c r="G216" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H216" s="8" t="n">
-        <v>715064.600498318</v>
+        <v>715234.995357302</v>
       </c>
       <c r="I216" s="9" t="n">
-        <v>712703.905744747</v>
+        <v>712887.435249371</v>
       </c>
       <c r="J216" s="10" t="n">
-        <v>716875.335169902</v>
+        <v>716575.100621443</v>
       </c>
       <c r="K216" s="11" t="n">
-        <v>731249.267112111</v>
+        <v>730865.841059937</v>
       </c>
       <c r="L216" s="12" t="n">
-        <v>715064.600498318</v>
+        <v>715234.995357302</v>
       </c>
       <c r="M216" s="13" t="n">
-        <v>715064.600498318</v>
+        <v>715234.995357302</v>
       </c>
       <c r="N216" s="14" t="n">
-        <v>715064.600498318</v>
+        <v>715234.995357302</v>
       </c>
       <c r="O216" s="15" t="n">
-        <v>-0.00709280327924673</v>
+        <v>-0.00632609452659308</v>
       </c>
       <c r="P216" s="16" t="n">
-        <v>-0.0293810281935347</v>
+        <v>-0.028881975424439</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>-0.00706770871538753</v>
+        <v>-0.00630612691845989</v>
       </c>
       <c r="R216" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S216" s="19" t="n">
-        <v>1.00331230786662</v>
+        <v>1.00329303055694</v>
       </c>
     </row>
     <row r="217">
@@ -14624,46 +14624,46 @@
         <v>700543.19869756</v>
       </c>
       <c r="F217" s="6" t="n">
-        <v>-8741.46251282303</v>
+        <v>-9023.78696891078</v>
       </c>
       <c r="G217" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H217" s="8" t="n">
-        <v>706639.758366907</v>
+        <v>707198.826247949</v>
       </c>
       <c r="I217" s="9" t="n">
-        <v>715361.944683163</v>
+        <v>715670.834833061</v>
       </c>
       <c r="J217" s="10" t="n">
-        <v>718318.359186113</v>
+        <v>718087.09582621</v>
       </c>
       <c r="K217" s="11" t="n">
-        <v>709284.661210383</v>
+        <v>709566.985666471</v>
       </c>
       <c r="L217" s="12" t="n">
-        <v>709284.661210383</v>
+        <v>709566.985666471</v>
       </c>
       <c r="M217" s="13" t="n">
-        <v>709284.661210383</v>
+        <v>709566.985666471</v>
       </c>
       <c r="N217" s="14" t="n">
-        <v>709284.661210383</v>
+        <v>709566.985666471</v>
       </c>
       <c r="O217" s="15" t="n">
-        <v>-0.00811594623545336</v>
+        <v>-0.00795624889063359</v>
       </c>
       <c r="P217" s="16" t="n">
-        <v>-0.0182330297431851</v>
+        <v>-0.0178450382298565</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>-0.00808310086096686</v>
+        <v>-0.00792468171667082</v>
       </c>
       <c r="R217" s="18" t="n">
-        <v>1.00374292956511</v>
+        <v>1.00334864726952</v>
       </c>
       <c r="S217" s="19" t="n">
-        <v>0.991504603343876</v>
+        <v>0.991471150046217</v>
       </c>
     </row>
     <row r="218">
@@ -14683,46 +14683,46 @@
         <v>668219.630827054</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>-24668.6288602371</v>
+        <v>-25760.4297561751</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H218" s="8" t="n">
-        <v>694961.657825744</v>
+        <v>695328.052539111</v>
       </c>
       <c r="I218" s="9" t="n">
-        <v>718086.605886232</v>
+        <v>718540.652837017</v>
       </c>
       <c r="J218" s="10" t="n">
-        <v>719951.955358332</v>
+        <v>719821.020019964</v>
       </c>
       <c r="K218" s="11" t="n">
-        <v>692888.259687291</v>
+        <v>693980.060583229</v>
       </c>
       <c r="L218" s="12" t="n">
-        <v>692888.259687291</v>
+        <v>693980.060583229</v>
       </c>
       <c r="M218" s="13" t="n">
-        <v>692888.259687291</v>
+        <v>693980.060583229</v>
       </c>
       <c r="N218" s="14" t="n">
-        <v>692888.259687291</v>
+        <v>693980.060583229</v>
       </c>
       <c r="O218" s="15" t="n">
-        <v>-0.0233881979678801</v>
+        <v>-0.0222116756943337</v>
       </c>
       <c r="P218" s="16" t="n">
-        <v>-0.0471650284554543</v>
+        <v>-0.0435527322598944</v>
       </c>
       <c r="Q218" s="17" t="n">
-        <v>-0.0231168139109508</v>
+        <v>-0.0219668127155066</v>
       </c>
       <c r="R218" s="18" t="n">
-        <v>0.997016528732045</v>
+        <v>0.998061358302805</v>
       </c>
       <c r="S218" s="19" t="n">
-        <v>0.964909043014607</v>
+        <v>0.965818785399525</v>
       </c>
     </row>
     <row r="219">
@@ -14742,46 +14742,46 @@
         <v>729909.368719823</v>
       </c>
       <c r="F219" s="6" t="n">
-        <v>34984.9001041864</v>
+        <v>36215.7498876742</v>
       </c>
       <c r="G219" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H219" s="8" t="n">
-        <v>697055.009120445</v>
+        <v>696478.864667685</v>
       </c>
       <c r="I219" s="9" t="n">
-        <v>720896.059623817</v>
+        <v>721515.648071347</v>
       </c>
       <c r="J219" s="10" t="n">
-        <v>721982.538302877</v>
+        <v>721989.568407082</v>
       </c>
       <c r="K219" s="11" t="n">
-        <v>694924.468615637</v>
+        <v>693693.618832149</v>
       </c>
       <c r="L219" s="12" t="n">
-        <v>694924.468615637</v>
+        <v>693693.618832149</v>
       </c>
       <c r="M219" s="13" t="n">
-        <v>694924.468615637</v>
+        <v>693693.618832149</v>
       </c>
       <c r="N219" s="14" t="n">
-        <v>694924.468615637</v>
+        <v>693693.618832149</v>
       </c>
       <c r="O219" s="15" t="n">
-        <v>0.00293441665137571</v>
+        <v>-0.000412837339782936</v>
       </c>
       <c r="P219" s="16" t="n">
-        <v>-0.0350341152234271</v>
+        <v>-0.036234100255522</v>
       </c>
       <c r="Q219" s="17" t="n">
-        <v>0.00293872626628855</v>
+        <v>-0.000412752134174132</v>
       </c>
       <c r="R219" s="18" t="n">
-        <v>0.996943511664171</v>
+        <v>0.996000961440711</v>
       </c>
       <c r="S219" s="19" t="n">
-        <v>0.963973182178672</v>
+        <v>0.961439465223564</v>
       </c>
     </row>
     <row r="220">
@@ -14801,46 +14801,46 @@
         <v>714299.21795624</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>-1717.24444294311</v>
+        <v>-1243.58448125037</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H220" s="8" t="n">
-        <v>713684.271579094</v>
+        <v>713049.948935239</v>
       </c>
       <c r="I220" s="9" t="n">
-        <v>723792.727199408</v>
+        <v>724599.228976003</v>
       </c>
       <c r="J220" s="10" t="n">
-        <v>724481.204157712</v>
+        <v>724676.231394756</v>
       </c>
       <c r="K220" s="11" t="n">
-        <v>716016.462399183</v>
+        <v>715542.802437491</v>
       </c>
       <c r="L220" s="12" t="n">
-        <v>716016.462399183</v>
+        <v>715542.802437491</v>
       </c>
       <c r="M220" s="13" t="n">
-        <v>716016.462399183</v>
+        <v>715542.802437491</v>
       </c>
       <c r="N220" s="14" t="n">
-        <v>716016.462399183</v>
+        <v>715542.802437491</v>
       </c>
       <c r="O220" s="15" t="n">
-        <v>0.0298999974659591</v>
+        <v>0.0310110273166393</v>
       </c>
       <c r="P220" s="16" t="n">
-        <v>0.00133115511549886</v>
+        <v>0.000430357969320116</v>
       </c>
       <c r="Q220" s="17" t="n">
-        <v>0.0303514910412697</v>
+        <v>0.0314968784664984</v>
       </c>
       <c r="R220" s="18" t="n">
-        <v>1.00326781871615</v>
+        <v>1.00349604330801</v>
       </c>
       <c r="S220" s="19" t="n">
-        <v>0.989256226944537</v>
+        <v>0.987501468154596</v>
       </c>
     </row>
     <row r="221">
@@ -14860,46 +14860,46 @@
         <v>719523.320730935</v>
       </c>
       <c r="F221" s="6" t="n">
-        <v>-8248.16212145605</v>
+        <v>-8907.03702766135</v>
       </c>
       <c r="G221" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H221" s="8" t="n">
-        <v>727292.617624648</v>
+        <v>728255.298955587</v>
       </c>
       <c r="I221" s="9" t="n">
-        <v>726762.797672115</v>
+        <v>727777.415222659</v>
       </c>
       <c r="J221" s="10" t="n">
-        <v>727383.758712363</v>
+        <v>727823.019642305</v>
       </c>
       <c r="K221" s="11" t="n">
-        <v>727771.482852391</v>
+        <v>728430.357758596</v>
       </c>
       <c r="L221" s="12" t="n">
-        <v>727771.482852391</v>
+        <v>728430.357758596</v>
       </c>
       <c r="M221" s="13" t="n">
-        <v>727771.482852391</v>
+        <v>728430.357758596</v>
       </c>
       <c r="N221" s="14" t="n">
-        <v>727771.482852391</v>
+        <v>728430.357758596</v>
       </c>
       <c r="O221" s="15" t="n">
-        <v>0.0162839428659121</v>
+        <v>0.0178506053803755</v>
       </c>
       <c r="P221" s="16" t="n">
-        <v>0.0260640369840515</v>
+        <v>0.0265843429488306</v>
       </c>
       <c r="Q221" s="17" t="n">
-        <v>0.0164172488629932</v>
+        <v>0.0180108796807181</v>
       </c>
       <c r="R221" s="18" t="n">
-        <v>1.00065842168082</v>
+        <v>1.00024038109062</v>
       </c>
       <c r="S221" s="19" t="n">
-        <v>1.00138791526411</v>
+        <v>1.00089717339709</v>
       </c>
     </row>
     <row r="222">
@@ -14919,46 +14919,46 @@
         <v>709095.124696624</v>
       </c>
       <c r="F222" s="6" t="n">
-        <v>-24463.8649285938</v>
+        <v>-26114.1970126563</v>
       </c>
       <c r="G222" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H222" s="8" t="n">
-        <v>735593.981896699</v>
+        <v>736148.546085375</v>
       </c>
       <c r="I222" s="9" t="n">
-        <v>729787.599935545</v>
+        <v>731030.566216404</v>
       </c>
       <c r="J222" s="10" t="n">
-        <v>730583.684047564</v>
+        <v>731326.276664261</v>
       </c>
       <c r="K222" s="11" t="n">
-        <v>733558.989625218</v>
+        <v>735209.32170928</v>
       </c>
       <c r="L222" s="12" t="n">
-        <v>733558.989625218</v>
+        <v>735209.32170928</v>
       </c>
       <c r="M222" s="13" t="n">
-        <v>733558.989625218</v>
+        <v>735209.32170928</v>
       </c>
       <c r="N222" s="14" t="n">
-        <v>733558.989625218</v>
+        <v>735209.32170928</v>
       </c>
       <c r="O222" s="15" t="n">
-        <v>0.00792091472974912</v>
+        <v>0.00926322580544576</v>
       </c>
       <c r="P222" s="16" t="n">
-        <v>0.0586973864390232</v>
+        <v>0.0594098641557539</v>
       </c>
       <c r="Q222" s="17" t="n">
-        <v>0.00795236816664491</v>
+        <v>0.00930626226444398</v>
       </c>
       <c r="R222" s="18" t="n">
-        <v>0.997233538716244</v>
+        <v>0.99872413742975</v>
       </c>
       <c r="S222" s="19" t="n">
-        <v>1.00516779086135</v>
+        <v>1.0057162527615</v>
       </c>
     </row>
     <row r="223">
@@ -14978,46 +14978,46 @@
         <v>777482.5556069</v>
       </c>
       <c r="F223" s="6" t="n">
-        <v>34212.4248995394</v>
+        <v>36365.6902292211</v>
       </c>
       <c r="G223" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H223" s="8" t="n">
-        <v>740335.789408632</v>
+        <v>739357.086024473</v>
       </c>
       <c r="I223" s="9" t="n">
-        <v>732849.093311545</v>
+        <v>734339.449451413</v>
       </c>
       <c r="J223" s="10" t="n">
-        <v>733976.40086475</v>
+        <v>735085.382665739</v>
       </c>
       <c r="K223" s="11" t="n">
-        <v>743270.130707361</v>
+        <v>741116.865377679</v>
       </c>
       <c r="L223" s="12" t="n">
-        <v>743270.130707361</v>
+        <v>741116.865377679</v>
       </c>
       <c r="M223" s="13" t="n">
-        <v>743270.130707361</v>
+        <v>741116.865377679</v>
       </c>
       <c r="N223" s="14" t="n">
-        <v>743270.130707361</v>
+        <v>741116.865377679</v>
       </c>
       <c r="O223" s="15" t="n">
-        <v>0.013151529747299</v>
+        <v>0.0080030758123352</v>
       </c>
       <c r="P223" s="16" t="n">
-        <v>0.0695696644385448</v>
+        <v>0.0683633887614079</v>
       </c>
       <c r="Q223" s="17" t="n">
-        <v>0.0132383914851948</v>
+        <v>0.00803518602656461</v>
       </c>
       <c r="R223" s="18" t="n">
-        <v>1.00396352755156</v>
+        <v>1.00238014808605</v>
       </c>
       <c r="S223" s="19" t="n">
-        <v>1.01421989532487</v>
+        <v>1.00922926846886</v>
       </c>
     </row>
     <row r="224">
@@ -15037,46 +15037,46 @@
         <v>737135.067677709</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>-1946.32976111565</v>
+        <v>-1463.7506712142</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H224" s="8" t="n">
-        <v>741138.849011826</v>
+        <v>740180.674798215</v>
       </c>
       <c r="I224" s="9" t="n">
-        <v>735931.594240519</v>
+        <v>737687.444144043</v>
       </c>
       <c r="J224" s="10" t="n">
-        <v>737472.206393244</v>
+        <v>739019.133077076</v>
       </c>
       <c r="K224" s="11" t="n">
-        <v>739081.397438825</v>
+        <v>738598.818348924</v>
       </c>
       <c r="L224" s="12" t="n">
-        <v>739081.397438825</v>
+        <v>738598.818348924</v>
       </c>
       <c r="M224" s="13" t="n">
-        <v>739081.397438825</v>
+        <v>738598.818348924</v>
       </c>
       <c r="N224" s="14" t="n">
-        <v>739081.397438825</v>
+        <v>738598.818348924</v>
       </c>
       <c r="O224" s="15" t="n">
-        <v>-0.0056514859502095</v>
+        <v>-0.00340342335632908</v>
       </c>
       <c r="P224" s="16" t="n">
-        <v>0.0322128557803782</v>
+        <v>0.0322217145262209</v>
       </c>
       <c r="Q224" s="17" t="n">
-        <v>-0.00563554634510788</v>
+        <v>-0.00339763827594475</v>
       </c>
       <c r="R224" s="18" t="n">
-        <v>0.997223932363356</v>
+        <v>0.997862877938927</v>
       </c>
       <c r="S224" s="19" t="n">
-        <v>1.00428002170712</v>
+        <v>1.00123544763045</v>
       </c>
     </row>
     <row r="225">
@@ -15096,46 +15096,46 @@
         <v>735202.105508002</v>
       </c>
       <c r="F225" s="6" t="n">
-        <v>-7930.10952953862</v>
+        <v>-8865.42351046695</v>
       </c>
       <c r="G225" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H225" s="8" t="n">
-        <v>743791.699829468</v>
+        <v>744261.06446847</v>
       </c>
       <c r="I225" s="9" t="n">
-        <v>739025.932311241</v>
+        <v>741062.165395605</v>
       </c>
       <c r="J225" s="10" t="n">
-        <v>741027.866511581</v>
+        <v>743076.480742172</v>
       </c>
       <c r="K225" s="11" t="n">
-        <v>743132.21503754</v>
+        <v>744067.529018468</v>
       </c>
       <c r="L225" s="12" t="n">
-        <v>743132.21503754</v>
+        <v>744067.529018468</v>
       </c>
       <c r="M225" s="13" t="n">
-        <v>743132.21503754</v>
+        <v>744067.529018468</v>
       </c>
       <c r="N225" s="14" t="n">
-        <v>743132.21503754</v>
+        <v>744067.529018468</v>
       </c>
       <c r="O225" s="15" t="n">
-        <v>0.00546591618087863</v>
+        <v>0.00737689295932909</v>
       </c>
       <c r="P225" s="16" t="n">
-        <v>0.0211065321286639</v>
+        <v>0.0214669406530341</v>
       </c>
       <c r="Q225" s="17" t="n">
-        <v>0.00548088155479576</v>
+        <v>0.0074041692644049</v>
       </c>
       <c r="R225" s="18" t="n">
-        <v>0.999113347470698</v>
+        <v>0.999739962952194</v>
       </c>
       <c r="S225" s="19" t="n">
-        <v>1.00555634457029</v>
+        <v>1.00405548112318</v>
       </c>
     </row>
     <row r="226">
@@ -15143,92 +15143,118 @@
         <v>277</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>725600.244568253</v>
+        <v>726163.281251173</v>
       </c>
       <c r="C226" s="3" t="n">
-        <v>725600.244568253</v>
+        <v>726163.281251173</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>725600.244568253</v>
+        <v>726163.281251173</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>725600.244568253</v>
+        <v>726163.281251173</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>-23941.2332065971</v>
+        <v>-26228.6862211937</v>
       </c>
       <c r="G226" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H226" s="8" t="n">
-        <v>747334.865388655</v>
+        <v>752006.756602241</v>
       </c>
       <c r="I226" s="9" t="n">
-        <v>742124.905739485</v>
+        <v>744451.797916288</v>
       </c>
       <c r="J226" s="10" t="n">
-        <v>744608.193053524</v>
+        <v>747204.276931284</v>
       </c>
       <c r="K226" s="11" t="n">
-        <v>749541.477774851</v>
+        <v>752391.967472367</v>
       </c>
       <c r="L226" s="12" t="n">
-        <v>749541.477774851</v>
+        <v>752391.967472367</v>
       </c>
       <c r="M226" s="13" t="n">
-        <v>749541.477774851</v>
+        <v>752391.967472367</v>
       </c>
       <c r="N226" s="14" t="n">
-        <v>749541.477774851</v>
+        <v>752391.967472367</v>
       </c>
       <c r="O226" s="15" t="n">
-        <v>0.00858768015735857</v>
+        <v>0.0111256259718553</v>
       </c>
       <c r="P226" s="16" t="n">
-        <v>0.0217875976924475</v>
+        <v>0.0233710934501463</v>
       </c>
       <c r="Q226" s="17" t="n">
-        <v>0.00862466006400564</v>
+        <v>0.0111877459091374</v>
       </c>
       <c r="R226" s="18" t="n">
-        <v>1.0029526420998</v>
+        <v>1.00051224389508</v>
       </c>
       <c r="S226" s="19" t="n">
-        <v>1.0099936977967</v>
+        <v>1.01066579404913</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
         <v>278</v>
       </c>
-      <c r="B227" s="2"/>
+      <c r="B227" s="2" t="n">
+        <v>792800.341478316</v>
+      </c>
       <c r="C227" s="3" t="n">
-        <v>777449.317267898</v>
+        <v>792800.341478316</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>821981.856289926</v>
+        <v>792800.341478316</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>732916.778245871</v>
+        <v>792800.341478316</v>
       </c>
       <c r="F227" s="6" t="n">
-        <v>34002.7921310961</v>
-      </c>
-      <c r="G227" s="7"/>
-      <c r="H227" s="8"/>
-      <c r="I227" s="9"/>
-      <c r="J227" s="10"/>
-      <c r="K227" s="11"/>
-      <c r="L227" s="12"/>
-      <c r="M227" s="13"/>
+        <v>36995.0061911909</v>
+      </c>
+      <c r="G227" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" s="8" t="n">
+        <v>755149.379459014</v>
+      </c>
+      <c r="I227" s="9" t="n">
+        <v>747846.404768544</v>
+      </c>
+      <c r="J227" s="10" t="n">
+        <v>751354.328156052</v>
+      </c>
+      <c r="K227" s="11" t="n">
+        <v>755805.335287125</v>
+      </c>
+      <c r="L227" s="12" t="n">
+        <v>755805.335287125</v>
+      </c>
+      <c r="M227" s="13" t="n">
+        <v>755805.335287125</v>
+      </c>
       <c r="N227" s="14" t="n">
-        <v>743446.525136802</v>
-      </c>
-      <c r="O227" s="15"/>
-      <c r="P227" s="16"/>
-      <c r="Q227" s="17"/>
-      <c r="R227" s="18"/>
-      <c r="S227" s="19"/>
+        <v>755805.335287125</v>
+      </c>
+      <c r="O227" s="15" t="n">
+        <v>0.00452642852022814</v>
+      </c>
+      <c r="P227" s="16" t="n">
+        <v>0.0198193707303647</v>
+      </c>
+      <c r="Q227" s="17" t="n">
+        <v>0.00453668827197262</v>
+      </c>
+      <c r="R227" s="18" t="n">
+        <v>1.00086864380208</v>
+      </c>
+      <c r="S227" s="19" t="n">
+        <v>1.01064246677905</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
@@ -15236,16 +15262,16 @@
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="3" t="n">
-        <v>737794.877292727</v>
+        <v>749960.20701843</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>794006.064581993</v>
+        <v>794283.167307039</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>681583.690003462</v>
+        <v>705637.24672982</v>
       </c>
       <c r="F228" s="6" t="n">
-        <v>-2241.77848109039</v>
+        <v>-1826.8322044378</v>
       </c>
       <c r="G228" s="7"/>
       <c r="H228" s="8"/>
@@ -15255,7 +15281,7 @@
       <c r="L228" s="12"/>
       <c r="M228" s="13"/>
       <c r="N228" s="14" t="n">
-        <v>740036.655773817</v>
+        <v>751787.039222868</v>
       </c>
       <c r="O228" s="15"/>
       <c r="P228" s="16"/>
@@ -15269,16 +15295,16 @@
       </c>
       <c r="B229" s="2"/>
       <c r="C229" s="3" t="n">
-        <v>727686.53485258</v>
+        <v>737368.285725129</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>789797.041221151</v>
+        <v>793577.839925014</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>665576.028484009</v>
+        <v>681158.731525245</v>
       </c>
       <c r="F229" s="6" t="n">
-        <v>-8187.23729149833</v>
+        <v>-9381.69397362367</v>
       </c>
       <c r="G229" s="7"/>
       <c r="H229" s="8"/>
@@ -15288,7 +15314,7 @@
       <c r="L229" s="12"/>
       <c r="M229" s="13"/>
       <c r="N229" s="14" t="n">
-        <v>735873.772144078</v>
+        <v>746749.979698753</v>
       </c>
       <c r="O229" s="15"/>
       <c r="P229" s="16"/>
@@ -15302,16 +15328,16 @@
       </c>
       <c r="B230" s="2"/>
       <c r="C230" s="3" t="n">
-        <v>710342.95950772</v>
+        <v>718161.568394099</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>775702.204710127</v>
+        <v>780502.621315213</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>644983.714305314</v>
+        <v>655820.515472984</v>
       </c>
       <c r="F230" s="6" t="n">
-        <v>-23101.3641190502</v>
+        <v>-25798.1345305649</v>
       </c>
       <c r="G230" s="7"/>
       <c r="H230" s="8"/>
@@ -15321,7 +15347,7 @@
       <c r="L230" s="12"/>
       <c r="M230" s="13"/>
       <c r="N230" s="14" t="n">
-        <v>733444.32362677</v>
+        <v>743959.702924664</v>
       </c>
       <c r="O230" s="15"/>
       <c r="P230" s="16"/>
@@ -15334,10 +15360,18 @@
         <v>282</v>
       </c>
       <c r="B231" s="2"/>
-      <c r="C231" s="3"/>
-      <c r="D231" s="4"/>
-      <c r="E231" s="5"/>
-      <c r="F231" s="6"/>
+      <c r="C231" s="3" t="n">
+        <v>775834.467121655</v>
+      </c>
+      <c r="D231" s="4" t="n">
+        <v>841626.292290168</v>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>710042.641953142</v>
+      </c>
+      <c r="F231" s="6" t="n">
+        <v>37301.9947907622</v>
+      </c>
       <c r="G231" s="7"/>
       <c r="H231" s="8"/>
       <c r="I231" s="9"/>
@@ -15345,7 +15379,9 @@
       <c r="K231" s="11"/>
       <c r="L231" s="12"/>
       <c r="M231" s="13"/>
-      <c r="N231" s="14"/>
+      <c r="N231" s="14" t="n">
+        <v>738532.472330893</v>
+      </c>
       <c r="O231" s="15"/>
       <c r="P231" s="16"/>
       <c r="Q231" s="17"/>
@@ -15820,7 +15856,7 @@
         <v>318</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0000834569266478342</v>
+        <v>-0.00927490880339486</v>
       </c>
     </row>
     <row r="6">
@@ -15828,7 +15864,7 @@
         <v>319</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.129672520269508</v>
+        <v>0.125728228285431</v>
       </c>
     </row>
     <row r="7">
@@ -15836,7 +15872,7 @@
         <v>320</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.376919765488509</v>
+        <v>0.372731563800158</v>
       </c>
     </row>
     <row r="8">
@@ -15844,7 +15880,7 @@
         <v>321</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.63429963020155</v>
+        <v>0.634641684549077</v>
       </c>
     </row>
     <row r="9">
@@ -15852,7 +15888,7 @@
         <v>322</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.715931302042003</v>
+        <v>0.721975929584775</v>
       </c>
     </row>
     <row r="10">
@@ -15860,7 +15896,7 @@
         <v>323</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.511030332746107</v>
+        <v>0.512483550579467</v>
       </c>
     </row>
     <row r="11">
@@ -15868,7 +15904,7 @@
         <v>324</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.155997766141614</v>
+        <v>0.162111729649501</v>
       </c>
     </row>
     <row r="12">
@@ -15876,7 +15912,7 @@
         <v>325</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0474254193364707</v>
+        <v>-0.0409973047744464</v>
       </c>
     </row>
     <row r="13">
@@ -15884,7 +15920,7 @@
         <v>326</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.0998750673271038</v>
+        <v>-0.0861678775623498</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">18/09/2026</t>
+    <t xml:space="preserve">22/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">vcorvalan</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -1557,7 +1557,7 @@
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11" t="n">
-        <v>0.721975929584775</v>
+        <v>0.721976070980911</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -1615,7 +1615,7 @@
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15" t="n">
-        <v>0.5212492428998</v>
+        <v>0.521249447069034</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -1685,7 +1685,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.153979925743781</v>
+        <v>0.155406451165819</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1715,7 +1715,7 @@
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22" t="n">
-        <v>0.000121431265441804</v>
+        <v>0.000122214878132112</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -15856,7 +15856,7 @@
         <v>318</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.00927490880339486</v>
+        <v>-0.00927488978475926</v>
       </c>
     </row>
     <row r="6">
@@ -15864,7 +15864,7 @@
         <v>319</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.125728228285431</v>
+        <v>0.125727948774284</v>
       </c>
     </row>
     <row r="7">
@@ -15872,7 +15872,7 @@
         <v>320</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.372731563800158</v>
+        <v>0.372731159685304</v>
       </c>
     </row>
     <row r="8">
@@ -15880,7 +15880,7 @@
         <v>321</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.634641684549077</v>
+        <v>0.634641391983953</v>
       </c>
     </row>
     <row r="9">
@@ -15888,7 +15888,7 @@
         <v>322</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.721975929584775</v>
+        <v>0.721976070980911</v>
       </c>
     </row>
     <row r="10">
@@ -15896,7 +15896,7 @@
         <v>323</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.512483550579467</v>
+        <v>0.512484005675732</v>
       </c>
     </row>
     <row r="11">
@@ -15904,7 +15904,7 @@
         <v>324</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.162111729649501</v>
+        <v>0.162112305279211</v>
       </c>
     </row>
     <row r="12">
@@ -15912,7 +15912,7 @@
         <v>325</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0409973047744464</v>
+        <v>-0.040997019684774</v>
       </c>
     </row>
     <row r="13">
@@ -15920,7 +15920,7 @@
         <v>326</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.0861678775623498</v>
+        <v>-0.0861678969513603</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">22/09/2026</t>
+    <t xml:space="preserve">13/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
@@ -1557,7 +1557,7 @@
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11" t="n">
-        <v>0.721976070980911</v>
+        <v>0.72279549133684</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -1615,7 +1615,7 @@
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15" t="n">
-        <v>0.521249447069034</v>
+        <v>0.522433322296865</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -1685,7 +1685,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.155406451165819</v>
+        <v>0.15189726240943</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1715,7 +1715,7 @@
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22" t="n">
-        <v>0.000122214878132112</v>
+        <v>0.000112763772148089</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -15856,7 +15856,7 @@
         <v>318</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.00927488978475926</v>
+        <v>-0.00570770954043151</v>
       </c>
     </row>
     <row r="6">
@@ -15864,7 +15864,7 @@
         <v>319</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.125727948774284</v>
+        <v>0.125943585415831</v>
       </c>
     </row>
     <row r="7">
@@ -15872,7 +15872,7 @@
         <v>320</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.372731159685304</v>
+        <v>0.371203886025271</v>
       </c>
     </row>
     <row r="8">
@@ -15880,7 +15880,7 @@
         <v>321</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.634641391983953</v>
+        <v>0.63381822983202</v>
       </c>
     </row>
     <row r="9">
@@ -15888,7 +15888,7 @@
         <v>322</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.721976070980911</v>
+        <v>0.72279549133684</v>
       </c>
     </row>
     <row r="10">
@@ -15896,7 +15896,7 @@
         <v>323</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.512484005675732</v>
+        <v>0.513245435976576</v>
       </c>
     </row>
     <row r="11">
@@ -15904,7 +15904,7 @@
         <v>324</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.162112305279211</v>
+        <v>0.160244202673772</v>
       </c>
     </row>
     <row r="12">
@@ -15912,7 +15912,7 @@
         <v>325</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.040997019684774</v>
+        <v>-0.0415902918702597</v>
       </c>
     </row>
     <row r="13">
@@ -15920,7 +15920,7 @@
         <v>326</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.0861678969513603</v>
+        <v>-0.0886746811739005</v>
       </c>
     </row>
     <row r="14">
